--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="147">
   <si>
     <t>Dataset</t>
   </si>
@@ -457,13 +457,19 @@
   </si>
   <si>
     <t>40 Epoch</t>
+  </si>
+  <si>
+    <t>10 Epoch</t>
+  </si>
+  <si>
+    <t>Avoid Catastrophic Forgetting</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,6 +502,13 @@
     <font>
       <sz val="16"/>
       <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF92D050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -645,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -701,9 +714,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -711,6 +721,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1111,7 +1127,7 @@
     </row>
     <row r="7" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F7" s="15"/>
-      <c r="G7" s="19">
+      <c r="G7" s="22">
         <v>1</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -1173,7 +1189,7 @@
     </row>
     <row r="8" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F8" s="15"/>
-      <c r="G8" s="21">
+      <c r="G8" s="23">
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -1237,7 +1253,7 @@
     </row>
     <row r="9" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F9" s="15"/>
-      <c r="G9" s="20">
+      <c r="G9" s="23">
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
@@ -1301,7 +1317,7 @@
     </row>
     <row r="10" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F10" s="15"/>
-      <c r="G10" s="20">
+      <c r="G10" s="23">
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -1365,7 +1381,7 @@
     </row>
     <row r="11" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F11" s="15"/>
-      <c r="G11" s="20">
+      <c r="G11" s="23">
         <v>1</v>
       </c>
       <c r="H11" s="5" t="s">
@@ -1429,7 +1445,7 @@
     </row>
     <row r="12" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F12" s="15"/>
-      <c r="G12" s="20">
+      <c r="G12" s="23">
         <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
@@ -1493,7 +1509,7 @@
     </row>
     <row r="13" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F13" s="15"/>
-      <c r="G13" s="20">
+      <c r="G13" s="23">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
@@ -1557,7 +1573,7 @@
     </row>
     <row r="14" spans="2:23" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F14" s="15"/>
-      <c r="G14" s="20">
+      <c r="G14" s="23">
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
@@ -1621,7 +1637,7 @@
     </row>
     <row r="15" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F15" s="15"/>
-      <c r="G15" s="21">
+      <c r="G15" s="23">
         <v>1</v>
       </c>
       <c r="H15" s="5" t="s">
@@ -1685,7 +1701,7 @@
     </row>
     <row r="16" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F16" s="15"/>
-      <c r="G16" s="21">
+      <c r="G16" s="23">
         <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
@@ -1749,7 +1765,7 @@
     </row>
     <row r="17" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F17" s="15"/>
-      <c r="G17" s="21">
+      <c r="G17" s="23">
         <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
@@ -1813,7 +1829,7 @@
     </row>
     <row r="18" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F18" s="15"/>
-      <c r="G18" s="21">
+      <c r="G18" s="23">
         <v>1</v>
       </c>
       <c r="H18" s="5" t="s">
@@ -1897,7 +1913,7 @@
     </row>
     <row r="20" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F20" s="15"/>
-      <c r="G20" s="20">
+      <c r="G20" s="23">
         <v>1</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -1959,7 +1975,7 @@
     </row>
     <row r="21" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F21" s="15"/>
-      <c r="G21" s="21">
+      <c r="G21" s="23">
         <v>1</v>
       </c>
       <c r="H21" s="5" t="s">
@@ -2023,7 +2039,7 @@
     </row>
     <row r="22" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F22" s="15"/>
-      <c r="G22" s="20">
+      <c r="G22" s="23">
         <v>1</v>
       </c>
       <c r="H22" s="5" t="s">
@@ -2087,7 +2103,7 @@
     </row>
     <row r="23" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F23" s="15"/>
-      <c r="G23" s="20">
+      <c r="G23" s="23">
         <v>1</v>
       </c>
       <c r="H23" s="5" t="s">
@@ -2151,7 +2167,7 @@
     </row>
     <row r="24" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F24" s="15"/>
-      <c r="G24" s="20">
+      <c r="G24" s="23">
         <v>1</v>
       </c>
       <c r="H24" s="5" t="s">
@@ -2215,7 +2231,7 @@
     </row>
     <row r="25" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F25" s="15"/>
-      <c r="G25" s="20">
+      <c r="G25" s="23">
         <v>1</v>
       </c>
       <c r="H25" s="5" t="s">
@@ -2279,7 +2295,7 @@
     </row>
     <row r="26" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F26" s="15"/>
-      <c r="G26" s="20">
+      <c r="G26" s="23">
         <v>1</v>
       </c>
       <c r="H26" s="5" t="s">
@@ -2316,11 +2332,11 @@
         <f>"(2048,6,6) --&gt; (2,2,2,1024,3,3) --&gt; (10)"</f>
         <v>(2048,6,6) --&gt; (2,2,2,1024,3,3) --&gt; (10)</v>
       </c>
-      <c r="Q26" s="22">
+      <c r="Q26" s="21">
         <f>20612</f>
         <v>20612</v>
       </c>
-      <c r="R26" s="22">
+      <c r="R26" s="21">
         <f t="shared" si="8"/>
         <v>23528644</v>
       </c>
@@ -2343,7 +2359,7 @@
     </row>
     <row r="27" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F27" s="15"/>
-      <c r="G27" s="20">
+      <c r="G27" s="23">
         <v>1</v>
       </c>
       <c r="H27" s="5" t="s">
@@ -2407,7 +2423,7 @@
     </row>
     <row r="28" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F28" s="15"/>
-      <c r="G28" s="21">
+      <c r="G28" s="23">
         <v>1</v>
       </c>
       <c r="H28" s="5" t="s">
@@ -2471,7 +2487,7 @@
     </row>
     <row r="29" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F29" s="15"/>
-      <c r="G29" s="21">
+      <c r="G29" s="23">
         <v>1</v>
       </c>
       <c r="H29" s="5" t="s">
@@ -2535,7 +2551,7 @@
     </row>
     <row r="30" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F30" s="15"/>
-      <c r="G30" s="21">
+      <c r="G30" s="23">
         <v>1</v>
       </c>
       <c r="H30" s="5" t="s">
@@ -2572,11 +2588,11 @@
         <f>"(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (10)"</f>
         <v>(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (10)</v>
       </c>
-      <c r="Q30" s="22">
+      <c r="Q30" s="21">
         <f>1386</f>
         <v>1386</v>
       </c>
-      <c r="R30" s="22">
+      <c r="R30" s="21">
         <f t="shared" si="8"/>
         <v>23509418</v>
       </c>
@@ -2599,7 +2615,7 @@
     </row>
     <row r="31" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F31" s="15"/>
-      <c r="G31" s="21">
+      <c r="G31" s="23">
         <v>1</v>
       </c>
       <c r="H31" s="5" t="s">
@@ -2681,9 +2697,9 @@
       <c r="V32" s="17"/>
       <c r="W32" s="17"/>
     </row>
-    <row r="33" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F33" s="15"/>
-      <c r="G33" s="21">
+      <c r="G33" s="20">
         <v>1</v>
       </c>
       <c r="H33" s="5" t="s">
@@ -2705,8 +2721,8 @@
         <v>200</v>
       </c>
       <c r="M33" s="2" t="str">
-        <f xml:space="preserve"> "Linear"</f>
-        <v>Linear</v>
+        <f xml:space="preserve"> "Dropout+Linear"</f>
+        <v>Dropout+Linear</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>9</v>
@@ -2731,21 +2747,21 @@
         <v>18</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F34" s="15"/>
-      <c r="G34" s="21">
+      <c r="G34" s="20">
         <v>1</v>
       </c>
       <c r="H34" s="5" t="s">
@@ -2795,21 +2811,21 @@
         <v>73.006632397021519</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F35" s="15"/>
-      <c r="G35" s="21">
+      <c r="G35" s="20">
         <v>1</v>
       </c>
       <c r="H35" s="5" t="s">
@@ -2859,21 +2875,21 @@
         <v>84.071152463752384</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F36" s="15"/>
-      <c r="G36" s="21">
+      <c r="G36" s="20">
         <v>1</v>
       </c>
       <c r="H36" s="5" t="s">
@@ -2923,21 +2939,21 @@
         <v>88.274383214203368</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F37" s="15"/>
-      <c r="G37" s="21">
+      <c r="G37" s="20">
         <v>1</v>
       </c>
       <c r="H37" s="5" t="s">
@@ -2987,21 +3003,21 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F38" s="15"/>
-      <c r="G38" s="21">
+      <c r="G38" s="20">
         <v>1</v>
       </c>
       <c r="H38" s="5" t="s">
@@ -3051,21 +3067,21 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F39" s="15"/>
-      <c r="G39" s="21">
+      <c r="G39" s="20">
         <v>1</v>
       </c>
       <c r="H39" s="5" t="s">
@@ -3115,21 +3131,21 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F40" s="15"/>
-      <c r="G40" s="21">
+      <c r="G40" s="20">
         <v>1</v>
       </c>
       <c r="H40" s="5" t="s">
@@ -3179,21 +3195,21 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F41" s="15"/>
-      <c r="G41" s="21">
+      <c r="G41" s="20">
         <v>1</v>
       </c>
       <c r="H41" s="5" t="s">
@@ -3243,21 +3259,21 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F42" s="15"/>
-      <c r="G42" s="21">
+      <c r="G42" s="20">
         <v>1</v>
       </c>
       <c r="H42" s="5" t="s">
@@ -3307,21 +3323,21 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F43" s="15"/>
-      <c r="G43" s="21">
+      <c r="G43" s="20">
         <v>1</v>
       </c>
       <c r="H43" s="5" t="s">
@@ -3358,11 +3374,11 @@
         <f>"(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (200)"</f>
         <v>(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (200)</v>
       </c>
-      <c r="Q43" s="22">
+      <c r="Q43" s="21">
         <f>91274</f>
         <v>91274</v>
       </c>
-      <c r="R43" s="22">
+      <c r="R43" s="21">
         <f t="shared" si="13"/>
         <v>23599306</v>
       </c>
@@ -3370,22 +3386,22 @@
         <f xml:space="preserve"> (1-(Q43/Q33))*100</f>
         <v>99.381016967543303</v>
       </c>
-      <c r="T43" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="U43" s="7" t="s">
-        <v>12</v>
+      <c r="T43" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="V43" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="W43" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="W43" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F44" s="15"/>
-      <c r="G44" s="21">
+      <c r="G44" s="20">
         <v>1</v>
       </c>
       <c r="H44" s="5" t="s">
@@ -3435,16 +3451,16 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3469,7 +3485,7 @@
     </row>
     <row r="46" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F46" s="15"/>
-      <c r="G46" s="20">
+      <c r="G46" s="19">
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
@@ -3531,7 +3547,7 @@
     </row>
     <row r="47" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F47" s="15"/>
-      <c r="G47" s="21">
+      <c r="G47" s="20">
         <v>1</v>
       </c>
       <c r="H47" s="5" t="s">
@@ -3595,7 +3611,7 @@
     </row>
     <row r="48" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F48" s="15"/>
-      <c r="G48" s="20">
+      <c r="G48" s="19">
         <v>1</v>
       </c>
       <c r="H48" s="5" t="s">
@@ -3659,7 +3675,7 @@
     </row>
     <row r="49" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F49" s="15"/>
-      <c r="G49" s="20">
+      <c r="G49" s="19">
         <v>1</v>
       </c>
       <c r="H49" s="5" t="s">
@@ -3723,7 +3739,7 @@
     </row>
     <row r="50" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F50" s="15"/>
-      <c r="G50" s="20">
+      <c r="G50" s="19">
         <v>1</v>
       </c>
       <c r="H50" s="5" t="s">
@@ -3787,7 +3803,7 @@
     </row>
     <row r="51" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F51" s="15"/>
-      <c r="G51" s="20">
+      <c r="G51" s="19">
         <v>1</v>
       </c>
       <c r="H51" s="5" t="s">
@@ -3851,7 +3867,7 @@
     </row>
     <row r="52" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F52" s="15"/>
-      <c r="G52" s="20">
+      <c r="G52" s="19">
         <v>1</v>
       </c>
       <c r="H52" s="5" t="s">
@@ -3915,7 +3931,7 @@
     </row>
     <row r="53" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F53" s="15"/>
-      <c r="G53" s="20">
+      <c r="G53" s="19">
         <v>1</v>
       </c>
       <c r="H53" s="5" t="s">
@@ -3979,7 +3995,7 @@
     </row>
     <row r="54" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F54" s="15"/>
-      <c r="G54" s="21">
+      <c r="G54" s="20">
         <v>1</v>
       </c>
       <c r="H54" s="5" t="s">
@@ -4043,7 +4059,7 @@
     </row>
     <row r="55" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F55" s="15"/>
-      <c r="G55" s="21">
+      <c r="G55" s="20">
         <v>1</v>
       </c>
       <c r="H55" s="5" t="s">
@@ -4107,7 +4123,7 @@
     </row>
     <row r="56" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F56" s="15"/>
-      <c r="G56" s="21">
+      <c r="G56" s="20">
         <v>1</v>
       </c>
       <c r="H56" s="5" t="s">
@@ -4171,7 +4187,7 @@
     </row>
     <row r="57" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F57" s="15"/>
-      <c r="G57" s="21">
+      <c r="G57" s="20">
         <v>1</v>
       </c>
       <c r="H57" s="5" t="s">
@@ -4255,7 +4271,7 @@
     </row>
     <row r="59" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F59" s="15"/>
-      <c r="G59" s="20">
+      <c r="G59" s="19">
         <v>1</v>
       </c>
       <c r="H59" s="5" t="s">
@@ -4317,7 +4333,7 @@
     </row>
     <row r="60" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F60" s="15"/>
-      <c r="G60" s="21">
+      <c r="G60" s="20">
         <v>1</v>
       </c>
       <c r="H60" s="5" t="s">
@@ -4381,7 +4397,7 @@
     </row>
     <row r="61" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F61" s="15"/>
-      <c r="G61" s="20">
+      <c r="G61" s="19">
         <v>1</v>
       </c>
       <c r="H61" s="5" t="s">
@@ -4445,7 +4461,7 @@
     </row>
     <row r="62" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F62" s="15"/>
-      <c r="G62" s="20">
+      <c r="G62" s="19">
         <v>1</v>
       </c>
       <c r="H62" s="5" t="s">
@@ -4509,7 +4525,7 @@
     </row>
     <row r="63" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F63" s="15"/>
-      <c r="G63" s="20">
+      <c r="G63" s="19">
         <v>1</v>
       </c>
       <c r="H63" s="5" t="s">
@@ -4573,7 +4589,7 @@
     </row>
     <row r="64" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F64" s="15"/>
-      <c r="G64" s="20">
+      <c r="G64" s="19">
         <v>1</v>
       </c>
       <c r="H64" s="5" t="s">
@@ -4610,11 +4626,11 @@
         <f>"(2048,6,6) --&gt; (2,2,2,1024,3,3) --&gt; (10)"</f>
         <v>(2048,6,6) --&gt; (2,2,2,1024,3,3) --&gt; (10)</v>
       </c>
-      <c r="Q64" s="22">
+      <c r="Q64" s="21">
         <f>103512</f>
         <v>103512</v>
       </c>
-      <c r="R64" s="22">
+      <c r="R64" s="21">
         <f t="shared" si="23"/>
         <v>42603672</v>
       </c>
@@ -4637,7 +4653,7 @@
     </row>
     <row r="65" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F65" s="15"/>
-      <c r="G65" s="20">
+      <c r="G65" s="19">
         <v>1</v>
       </c>
       <c r="H65" s="5" t="s">
@@ -4701,7 +4717,7 @@
     </row>
     <row r="66" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F66" s="15"/>
-      <c r="G66" s="20">
+      <c r="G66" s="19">
         <v>1</v>
       </c>
       <c r="H66" s="5" t="s">
@@ -4765,7 +4781,7 @@
     </row>
     <row r="67" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F67" s="15"/>
-      <c r="G67" s="21">
+      <c r="G67" s="20">
         <v>1</v>
       </c>
       <c r="H67" s="5" t="s">
@@ -4829,7 +4845,7 @@
     </row>
     <row r="68" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F68" s="15"/>
-      <c r="G68" s="21">
+      <c r="G68" s="20">
         <v>1</v>
       </c>
       <c r="H68" s="5" t="s">
@@ -4893,7 +4909,7 @@
     </row>
     <row r="69" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F69" s="15"/>
-      <c r="G69" s="21">
+      <c r="G69" s="20">
         <v>1</v>
       </c>
       <c r="H69" s="5" t="s">
@@ -4957,7 +4973,7 @@
     </row>
     <row r="70" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F70" s="15"/>
-      <c r="G70" s="21">
+      <c r="G70" s="20">
         <v>1</v>
       </c>
       <c r="H70" s="5" t="s">
@@ -4994,11 +5010,11 @@
         <f>"(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (10)"</f>
         <v>(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (10)</v>
       </c>
-      <c r="Q70" s="22">
+      <c r="Q70" s="21">
         <f>1386</f>
         <v>1386</v>
       </c>
-      <c r="R70" s="22">
+      <c r="R70" s="21">
         <f t="shared" si="23"/>
         <v>42501546</v>
       </c>
@@ -5041,7 +5057,7 @@
     </row>
     <row r="72" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F72" s="15"/>
-      <c r="G72" s="21">
+      <c r="G72" s="20">
         <v>1</v>
       </c>
       <c r="H72" s="5" t="s">
@@ -5103,7 +5119,7 @@
     </row>
     <row r="73" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F73" s="15"/>
-      <c r="G73" s="21">
+      <c r="G73" s="20">
         <v>1</v>
       </c>
       <c r="H73" s="5" t="s">
@@ -5167,7 +5183,7 @@
     </row>
     <row r="74" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F74" s="15"/>
-      <c r="G74" s="21">
+      <c r="G74" s="20">
         <v>1</v>
       </c>
       <c r="H74" s="5" t="s">
@@ -5231,7 +5247,7 @@
     </row>
     <row r="75" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F75" s="15"/>
-      <c r="G75" s="21">
+      <c r="G75" s="20">
         <v>1</v>
       </c>
       <c r="H75" s="5" t="s">
@@ -5295,7 +5311,7 @@
     </row>
     <row r="76" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F76" s="15"/>
-      <c r="G76" s="21">
+      <c r="G76" s="20">
         <v>1</v>
       </c>
       <c r="H76" s="5" t="s">
@@ -5359,7 +5375,7 @@
     </row>
     <row r="77" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F77" s="15"/>
-      <c r="G77" s="21">
+      <c r="G77" s="20">
         <v>1</v>
       </c>
       <c r="H77" s="5" t="s">
@@ -5423,7 +5439,7 @@
     </row>
     <row r="78" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F78" s="15"/>
-      <c r="G78" s="21">
+      <c r="G78" s="20">
         <v>1</v>
       </c>
       <c r="H78" s="5" t="s">
@@ -5487,7 +5503,7 @@
     </row>
     <row r="79" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F79" s="15"/>
-      <c r="G79" s="21">
+      <c r="G79" s="20">
         <v>1</v>
       </c>
       <c r="H79" s="5" t="s">
@@ -5551,7 +5567,7 @@
     </row>
     <row r="80" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F80" s="15"/>
-      <c r="G80" s="21">
+      <c r="G80" s="20">
         <v>1</v>
       </c>
       <c r="H80" s="5" t="s">
@@ -5615,7 +5631,7 @@
     </row>
     <row r="81" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F81" s="15"/>
-      <c r="G81" s="21">
+      <c r="G81" s="20">
         <v>1</v>
       </c>
       <c r="H81" s="5" t="s">
@@ -5679,7 +5695,7 @@
     </row>
     <row r="82" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F82" s="15"/>
-      <c r="G82" s="21">
+      <c r="G82" s="20">
         <v>1</v>
       </c>
       <c r="H82" s="5" t="s">
@@ -5743,7 +5759,7 @@
     </row>
     <row r="83" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F83" s="15"/>
-      <c r="G83" s="21">
+      <c r="G83" s="20">
         <v>1</v>
       </c>
       <c r="H83" s="5" t="s">
@@ -5780,11 +5796,11 @@
         <f>"(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (200)"</f>
         <v>(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (200)</v>
       </c>
-      <c r="Q83" s="22">
+      <c r="Q83" s="21">
         <f>91274</f>
         <v>91274</v>
       </c>
-      <c r="R83" s="22">
+      <c r="R83" s="21">
         <f t="shared" si="28"/>
         <v>42591434</v>
       </c>
@@ -5827,7 +5843,7 @@
     </row>
     <row r="85" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F85" s="15"/>
-      <c r="G85" s="20">
+      <c r="G85" s="19">
         <v>1</v>
       </c>
       <c r="H85" s="5" t="s">
@@ -5889,7 +5905,7 @@
     </row>
     <row r="86" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F86" s="15"/>
-      <c r="G86" s="20">
+      <c r="G86" s="19">
         <v>1</v>
       </c>
       <c r="H86" s="5" t="s">
@@ -5953,7 +5969,7 @@
     </row>
     <row r="87" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F87" s="15"/>
-      <c r="G87" s="20">
+      <c r="G87" s="19">
         <v>1</v>
       </c>
       <c r="H87" s="5" t="s">
@@ -6017,7 +6033,7 @@
     </row>
     <row r="88" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F88" s="15"/>
-      <c r="G88" s="20">
+      <c r="G88" s="19">
         <v>1</v>
       </c>
       <c r="H88" s="5" t="s">
@@ -6081,7 +6097,7 @@
     </row>
     <row r="89" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F89" s="15"/>
-      <c r="G89" s="21">
+      <c r="G89" s="20">
         <v>1</v>
       </c>
       <c r="H89" s="5" t="s">
@@ -6145,7 +6161,7 @@
     </row>
     <row r="90" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F90" s="15"/>
-      <c r="G90" s="21">
+      <c r="G90" s="20">
         <v>1</v>
       </c>
       <c r="H90" s="5" t="s">
@@ -6229,7 +6245,7 @@
     </row>
     <row r="92" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F92" s="15"/>
-      <c r="G92" s="20">
+      <c r="G92" s="19">
         <v>1</v>
       </c>
       <c r="H92" s="5" t="s">
@@ -6291,7 +6307,7 @@
     </row>
     <row r="93" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F93" s="15"/>
-      <c r="G93" s="20">
+      <c r="G93" s="19">
         <v>1</v>
       </c>
       <c r="H93" s="5" t="s">
@@ -6355,7 +6371,7 @@
     </row>
     <row r="94" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F94" s="15"/>
-      <c r="G94" s="20">
+      <c r="G94" s="19">
         <v>1</v>
       </c>
       <c r="H94" s="5" t="s">
@@ -6419,7 +6435,7 @@
     </row>
     <row r="95" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F95" s="15"/>
-      <c r="G95" s="20">
+      <c r="G95" s="19">
         <v>1</v>
       </c>
       <c r="H95" s="5" t="s">
@@ -6483,7 +6499,7 @@
     </row>
     <row r="96" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F96" s="15"/>
-      <c r="G96" s="21">
+      <c r="G96" s="20">
         <v>1</v>
       </c>
       <c r="H96" s="5" t="s">
@@ -6547,7 +6563,7 @@
     </row>
     <row r="97" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F97" s="15"/>
-      <c r="G97" s="21">
+      <c r="G97" s="20">
         <v>1</v>
       </c>
       <c r="H97" s="5" t="s">
@@ -6631,7 +6647,7 @@
     </row>
     <row r="99" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F99" s="15"/>
-      <c r="G99" s="21">
+      <c r="G99" s="20">
         <v>1</v>
       </c>
       <c r="H99" s="5" t="s">
@@ -6693,7 +6709,7 @@
     </row>
     <row r="100" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F100" s="15"/>
-      <c r="G100" s="21">
+      <c r="G100" s="20">
         <v>1</v>
       </c>
       <c r="H100" s="5" t="s">
@@ -6757,7 +6773,7 @@
     </row>
     <row r="101" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F101" s="15"/>
-      <c r="G101" s="21">
+      <c r="G101" s="20">
         <v>1</v>
       </c>
       <c r="H101" s="5" t="s">
@@ -6821,7 +6837,7 @@
     </row>
     <row r="102" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F102" s="15"/>
-      <c r="G102" s="21">
+      <c r="G102" s="20">
         <v>1</v>
       </c>
       <c r="H102" s="5" t="s">
@@ -6885,7 +6901,7 @@
     </row>
     <row r="103" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F103" s="15"/>
-      <c r="G103" s="21">
+      <c r="G103" s="20">
         <v>1</v>
       </c>
       <c r="H103" s="5" t="s">
@@ -6949,7 +6965,7 @@
     </row>
     <row r="104" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F104" s="15"/>
-      <c r="G104" s="21">
+      <c r="G104" s="20">
         <v>1</v>
       </c>
       <c r="H104" s="5" t="s">
@@ -7033,7 +7049,7 @@
     </row>
     <row r="106" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F106" s="15"/>
-      <c r="G106" s="21">
+      <c r="G106" s="20">
         <v>1</v>
       </c>
       <c r="H106" s="5" t="s">
@@ -7095,7 +7111,7 @@
     </row>
     <row r="107" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F107" s="15"/>
-      <c r="G107" s="21">
+      <c r="G107" s="20">
         <v>1</v>
       </c>
       <c r="H107" s="5" t="s">
@@ -7159,7 +7175,7 @@
     </row>
     <row r="108" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F108" s="15"/>
-      <c r="G108" s="21">
+      <c r="G108" s="20">
         <v>1</v>
       </c>
       <c r="H108" s="5" t="s">
@@ -7223,7 +7239,7 @@
     </row>
     <row r="109" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F109" s="15"/>
-      <c r="G109" s="21">
+      <c r="G109" s="20">
         <v>1</v>
       </c>
       <c r="H109" s="5" t="s">
@@ -7287,7 +7303,7 @@
     </row>
     <row r="110" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F110" s="15"/>
-      <c r="G110" s="21">
+      <c r="G110" s="20">
         <v>1</v>
       </c>
       <c r="H110" s="5" t="s">
@@ -7351,7 +7367,7 @@
     </row>
     <row r="111" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F111" s="15"/>
-      <c r="G111" s="21">
+      <c r="G111" s="20">
         <v>1</v>
       </c>
       <c r="H111" s="5" t="s">
@@ -7435,7 +7451,7 @@
     </row>
     <row r="113" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F113" s="15"/>
-      <c r="G113" s="21">
+      <c r="G113" s="20">
         <v>1</v>
       </c>
       <c r="H113" s="5" t="s">
@@ -7497,7 +7513,7 @@
     </row>
     <row r="114" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F114" s="15"/>
-      <c r="G114" s="21">
+      <c r="G114" s="20">
         <v>1</v>
       </c>
       <c r="H114" s="5" t="s">
@@ -7561,7 +7577,7 @@
     </row>
     <row r="115" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F115" s="15"/>
-      <c r="G115" s="21">
+      <c r="G115" s="20">
         <v>1</v>
       </c>
       <c r="H115" s="5" t="s">
@@ -7625,7 +7641,7 @@
     </row>
     <row r="116" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F116" s="15"/>
-      <c r="G116" s="21">
+      <c r="G116" s="20">
         <v>1</v>
       </c>
       <c r="H116" s="5" t="s">
@@ -7689,7 +7705,7 @@
     </row>
     <row r="117" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F117" s="15"/>
-      <c r="G117" s="21">
+      <c r="G117" s="20">
         <v>1</v>
       </c>
       <c r="H117" s="5" t="s">
@@ -7753,7 +7769,7 @@
     </row>
     <row r="118" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F118" s="15"/>
-      <c r="G118" s="21">
+      <c r="G118" s="20">
         <v>1</v>
       </c>
       <c r="H118" s="5" t="s">
@@ -7837,7 +7853,7 @@
     </row>
     <row r="120" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F120" s="15"/>
-      <c r="G120" s="20">
+      <c r="G120" s="19">
         <v>1</v>
       </c>
       <c r="H120" s="5" t="s">
@@ -7899,7 +7915,7 @@
     </row>
     <row r="121" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F121" s="15"/>
-      <c r="G121" s="20">
+      <c r="G121" s="19">
         <v>1</v>
       </c>
       <c r="H121" s="5" t="s">
@@ -7963,7 +7979,7 @@
     </row>
     <row r="122" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F122" s="15"/>
-      <c r="G122" s="20">
+      <c r="G122" s="19">
         <v>1</v>
       </c>
       <c r="H122" s="5" t="s">
@@ -8027,7 +8043,7 @@
     </row>
     <row r="123" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F123" s="15"/>
-      <c r="G123" s="20">
+      <c r="G123" s="19">
         <v>1</v>
       </c>
       <c r="H123" s="5" t="s">
@@ -8091,7 +8107,7 @@
     </row>
     <row r="124" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F124" s="15"/>
-      <c r="G124" s="21">
+      <c r="G124" s="20">
         <v>1</v>
       </c>
       <c r="H124" s="5" t="s">
@@ -8155,7 +8171,7 @@
     </row>
     <row r="125" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F125" s="15"/>
-      <c r="G125" s="21">
+      <c r="G125" s="20">
         <v>1</v>
       </c>
       <c r="H125" s="5" t="s">

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="148">
   <si>
     <t>Dataset</t>
   </si>
@@ -463,6 +463,9 @@
   </si>
   <si>
     <t>Avoid Catastrophic Forgetting</t>
+  </si>
+  <si>
+    <t>???</t>
   </si>
 </sst>
 </file>
@@ -1048,8 +1051,8 @@
         <v>23</v>
       </c>
       <c r="D3" s="14">
-        <f>0</f>
-        <v>0</v>
+        <f>72</f>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1057,9 +1060,8 @@
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="14">
-        <f>40</f>
-        <v>40</v>
+      <c r="D4" s="14" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1067,9 +1069,8 @@
       <c r="C5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="14">
-        <f>68</f>
-        <v>68</v>
+      <c r="D5" s="14" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="2:23" s="1" customFormat="1" ht="43.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2699,7 +2700,7 @@
     </row>
     <row r="33" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F33" s="15"/>
-      <c r="G33" s="20">
+      <c r="G33" s="23">
         <v>1</v>
       </c>
       <c r="H33" s="5" t="s">
@@ -2761,7 +2762,7 @@
     </row>
     <row r="34" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F34" s="15"/>
-      <c r="G34" s="20">
+      <c r="G34" s="23">
         <v>1</v>
       </c>
       <c r="H34" s="5" t="s">
@@ -2825,7 +2826,7 @@
     </row>
     <row r="35" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F35" s="15"/>
-      <c r="G35" s="20">
+      <c r="G35" s="23">
         <v>1</v>
       </c>
       <c r="H35" s="5" t="s">
@@ -2889,7 +2890,7 @@
     </row>
     <row r="36" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F36" s="15"/>
-      <c r="G36" s="20">
+      <c r="G36" s="23">
         <v>1</v>
       </c>
       <c r="H36" s="5" t="s">
@@ -2953,7 +2954,7 @@
     </row>
     <row r="37" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F37" s="15"/>
-      <c r="G37" s="20">
+      <c r="G37" s="23">
         <v>1</v>
       </c>
       <c r="H37" s="5" t="s">
@@ -3017,7 +3018,7 @@
     </row>
     <row r="38" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F38" s="15"/>
-      <c r="G38" s="20">
+      <c r="G38" s="23">
         <v>1</v>
       </c>
       <c r="H38" s="5" t="s">
@@ -3081,7 +3082,7 @@
     </row>
     <row r="39" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F39" s="15"/>
-      <c r="G39" s="20">
+      <c r="G39" s="23">
         <v>1</v>
       </c>
       <c r="H39" s="5" t="s">
@@ -3145,7 +3146,7 @@
     </row>
     <row r="40" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F40" s="15"/>
-      <c r="G40" s="20">
+      <c r="G40" s="23">
         <v>1</v>
       </c>
       <c r="H40" s="5" t="s">
@@ -3209,7 +3210,7 @@
     </row>
     <row r="41" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F41" s="15"/>
-      <c r="G41" s="20">
+      <c r="G41" s="23">
         <v>1</v>
       </c>
       <c r="H41" s="5" t="s">
@@ -3273,7 +3274,7 @@
     </row>
     <row r="42" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F42" s="15"/>
-      <c r="G42" s="20">
+      <c r="G42" s="23">
         <v>1</v>
       </c>
       <c r="H42" s="5" t="s">
@@ -3337,7 +3338,7 @@
     </row>
     <row r="43" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F43" s="15"/>
-      <c r="G43" s="20">
+      <c r="G43" s="23">
         <v>1</v>
       </c>
       <c r="H43" s="5" t="s">
@@ -3401,7 +3402,7 @@
     </row>
     <row r="44" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F44" s="15"/>
-      <c r="G44" s="20">
+      <c r="G44" s="23">
         <v>1</v>
       </c>
       <c r="H44" s="5" t="s">
@@ -3485,7 +3486,7 @@
     </row>
     <row r="46" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F46" s="15"/>
-      <c r="G46" s="19">
+      <c r="G46" s="23">
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
@@ -3547,7 +3548,7 @@
     </row>
     <row r="47" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F47" s="15"/>
-      <c r="G47" s="20">
+      <c r="G47" s="23">
         <v>1</v>
       </c>
       <c r="H47" s="5" t="s">
@@ -3611,7 +3612,7 @@
     </row>
     <row r="48" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F48" s="15"/>
-      <c r="G48" s="19">
+      <c r="G48" s="23">
         <v>1</v>
       </c>
       <c r="H48" s="5" t="s">
@@ -3675,7 +3676,7 @@
     </row>
     <row r="49" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F49" s="15"/>
-      <c r="G49" s="19">
+      <c r="G49" s="23">
         <v>1</v>
       </c>
       <c r="H49" s="5" t="s">
@@ -3739,7 +3740,7 @@
     </row>
     <row r="50" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F50" s="15"/>
-      <c r="G50" s="19">
+      <c r="G50" s="23">
         <v>1</v>
       </c>
       <c r="H50" s="5" t="s">
@@ -3803,7 +3804,7 @@
     </row>
     <row r="51" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F51" s="15"/>
-      <c r="G51" s="19">
+      <c r="G51" s="23">
         <v>1</v>
       </c>
       <c r="H51" s="5" t="s">
@@ -3867,7 +3868,7 @@
     </row>
     <row r="52" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F52" s="15"/>
-      <c r="G52" s="19">
+      <c r="G52" s="23">
         <v>1</v>
       </c>
       <c r="H52" s="5" t="s">
@@ -3931,7 +3932,7 @@
     </row>
     <row r="53" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F53" s="15"/>
-      <c r="G53" s="19">
+      <c r="G53" s="23">
         <v>1</v>
       </c>
       <c r="H53" s="5" t="s">
@@ -3995,7 +3996,7 @@
     </row>
     <row r="54" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F54" s="15"/>
-      <c r="G54" s="20">
+      <c r="G54" s="23">
         <v>1</v>
       </c>
       <c r="H54" s="5" t="s">
@@ -4059,7 +4060,7 @@
     </row>
     <row r="55" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F55" s="15"/>
-      <c r="G55" s="20">
+      <c r="G55" s="23">
         <v>1</v>
       </c>
       <c r="H55" s="5" t="s">
@@ -4123,7 +4124,7 @@
     </row>
     <row r="56" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F56" s="15"/>
-      <c r="G56" s="20">
+      <c r="G56" s="23">
         <v>1</v>
       </c>
       <c r="H56" s="5" t="s">
@@ -4187,7 +4188,7 @@
     </row>
     <row r="57" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F57" s="15"/>
-      <c r="G57" s="20">
+      <c r="G57" s="23">
         <v>1</v>
       </c>
       <c r="H57" s="5" t="s">
@@ -4271,7 +4272,7 @@
     </row>
     <row r="59" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F59" s="15"/>
-      <c r="G59" s="19">
+      <c r="G59" s="23">
         <v>1</v>
       </c>
       <c r="H59" s="5" t="s">
@@ -4333,7 +4334,7 @@
     </row>
     <row r="60" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F60" s="15"/>
-      <c r="G60" s="20">
+      <c r="G60" s="23">
         <v>1</v>
       </c>
       <c r="H60" s="5" t="s">
@@ -4397,7 +4398,7 @@
     </row>
     <row r="61" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F61" s="15"/>
-      <c r="G61" s="19">
+      <c r="G61" s="23">
         <v>1</v>
       </c>
       <c r="H61" s="5" t="s">
@@ -4461,7 +4462,7 @@
     </row>
     <row r="62" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F62" s="15"/>
-      <c r="G62" s="19">
+      <c r="G62" s="23">
         <v>1</v>
       </c>
       <c r="H62" s="5" t="s">
@@ -4525,7 +4526,7 @@
     </row>
     <row r="63" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F63" s="15"/>
-      <c r="G63" s="19">
+      <c r="G63" s="23">
         <v>1</v>
       </c>
       <c r="H63" s="5" t="s">
@@ -4589,7 +4590,7 @@
     </row>
     <row r="64" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F64" s="15"/>
-      <c r="G64" s="19">
+      <c r="G64" s="23">
         <v>1</v>
       </c>
       <c r="H64" s="5" t="s">
@@ -4653,7 +4654,7 @@
     </row>
     <row r="65" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F65" s="15"/>
-      <c r="G65" s="19">
+      <c r="G65" s="23">
         <v>1</v>
       </c>
       <c r="H65" s="5" t="s">
@@ -4717,7 +4718,7 @@
     </row>
     <row r="66" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F66" s="15"/>
-      <c r="G66" s="19">
+      <c r="G66" s="23">
         <v>1</v>
       </c>
       <c r="H66" s="5" t="s">
@@ -4781,7 +4782,7 @@
     </row>
     <row r="67" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F67" s="15"/>
-      <c r="G67" s="20">
+      <c r="G67" s="23">
         <v>1</v>
       </c>
       <c r="H67" s="5" t="s">
@@ -4845,7 +4846,7 @@
     </row>
     <row r="68" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F68" s="15"/>
-      <c r="G68" s="20">
+      <c r="G68" s="23">
         <v>1</v>
       </c>
       <c r="H68" s="5" t="s">
@@ -4909,7 +4910,7 @@
     </row>
     <row r="69" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F69" s="15"/>
-      <c r="G69" s="20">
+      <c r="G69" s="23">
         <v>1</v>
       </c>
       <c r="H69" s="5" t="s">
@@ -4973,7 +4974,7 @@
     </row>
     <row r="70" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F70" s="15"/>
-      <c r="G70" s="20">
+      <c r="G70" s="23">
         <v>1</v>
       </c>
       <c r="H70" s="5" t="s">
@@ -5057,7 +5058,7 @@
     </row>
     <row r="72" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F72" s="15"/>
-      <c r="G72" s="20">
+      <c r="G72" s="23">
         <v>1</v>
       </c>
       <c r="H72" s="5" t="s">
@@ -5119,7 +5120,7 @@
     </row>
     <row r="73" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F73" s="15"/>
-      <c r="G73" s="20">
+      <c r="G73" s="23">
         <v>1</v>
       </c>
       <c r="H73" s="5" t="s">
@@ -5183,7 +5184,7 @@
     </row>
     <row r="74" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F74" s="15"/>
-      <c r="G74" s="20">
+      <c r="G74" s="23">
         <v>1</v>
       </c>
       <c r="H74" s="5" t="s">
@@ -5247,7 +5248,7 @@
     </row>
     <row r="75" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F75" s="15"/>
-      <c r="G75" s="20">
+      <c r="G75" s="23">
         <v>1</v>
       </c>
       <c r="H75" s="5" t="s">
@@ -5311,7 +5312,7 @@
     </row>
     <row r="76" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F76" s="15"/>
-      <c r="G76" s="20">
+      <c r="G76" s="23">
         <v>1</v>
       </c>
       <c r="H76" s="5" t="s">
@@ -5375,7 +5376,7 @@
     </row>
     <row r="77" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F77" s="15"/>
-      <c r="G77" s="20">
+      <c r="G77" s="23">
         <v>1</v>
       </c>
       <c r="H77" s="5" t="s">
@@ -5439,7 +5440,7 @@
     </row>
     <row r="78" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F78" s="15"/>
-      <c r="G78" s="20">
+      <c r="G78" s="23">
         <v>1</v>
       </c>
       <c r="H78" s="5" t="s">
@@ -5503,7 +5504,7 @@
     </row>
     <row r="79" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F79" s="15"/>
-      <c r="G79" s="20">
+      <c r="G79" s="23">
         <v>1</v>
       </c>
       <c r="H79" s="5" t="s">
@@ -5567,7 +5568,7 @@
     </row>
     <row r="80" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F80" s="15"/>
-      <c r="G80" s="20">
+      <c r="G80" s="23">
         <v>1</v>
       </c>
       <c r="H80" s="5" t="s">
@@ -5631,7 +5632,7 @@
     </row>
     <row r="81" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F81" s="15"/>
-      <c r="G81" s="20">
+      <c r="G81" s="23">
         <v>1</v>
       </c>
       <c r="H81" s="5" t="s">
@@ -5695,7 +5696,7 @@
     </row>
     <row r="82" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F82" s="15"/>
-      <c r="G82" s="20">
+      <c r="G82" s="23">
         <v>1</v>
       </c>
       <c r="H82" s="5" t="s">
@@ -5759,7 +5760,7 @@
     </row>
     <row r="83" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F83" s="15"/>
-      <c r="G83" s="20">
+      <c r="G83" s="23">
         <v>1</v>
       </c>
       <c r="H83" s="5" t="s">

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="149">
   <si>
     <t>Dataset</t>
   </si>
@@ -466,6 +466,9 @@
   </si>
   <si>
     <t>???</t>
+  </si>
+  <si>
+    <t>50 Epoch</t>
   </si>
 </sst>
 </file>
@@ -661,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -730,6 +733,15 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5892,7 +5904,7 @@
         <v>18</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="U85" s="2" t="s">
         <v>142</v>
@@ -5932,34 +5944,34 @@
         <v>TCL + TRL</v>
       </c>
       <c r="N86" s="2" t="str">
-        <f>"tcl:: (100,4,4), trl:: (70,2,2,10)"</f>
-        <v>tcl:: (100,4,4), trl:: (70,2,2,10)</v>
+        <f>"tcl:: (128,6,6), trl:: (128,6,6,10)"</f>
+        <v>tcl:: (128,6,6), trl:: (128,6,6,10)</v>
       </c>
       <c r="O86" s="2" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
       <c r="P86" s="2" t="str">
-        <f>"(128,6,6) --&gt; (100,4,4) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (100,4,4) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (128,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (128,6,6) --&gt; (10)</v>
       </c>
       <c r="Q86" s="10">
-        <f>12848 + 9916</f>
-        <v>22764</v>
+        <f>79092</f>
+        <v>79092</v>
       </c>
       <c r="R86" s="10">
         <f xml:space="preserve"> R85 - Q85 + Q86</f>
-        <v>116460</v>
+        <v>172788</v>
       </c>
       <c r="S86" s="2">
         <f xml:space="preserve"> (1-(Q86/Q85))*100</f>
-        <v>99.518717866425817</v>
+        <v>98.327817320828956</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U86" s="2" t="s">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="V86" s="2" t="s">
         <v>15</v>
@@ -5996,34 +6008,34 @@
         <v>Reshape+TCL+TRL</v>
       </c>
       <c r="N87" s="2" t="str">
-        <f>"tcl::(1,1,1,50,2,2), trl:: (1,1,1,10,1,1,5)"</f>
-        <v>tcl::(1,1,1,50,2,2), trl:: (1,1,1,10,1,1,5)</v>
+        <f>"tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)"</f>
+        <v>tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)</v>
       </c>
       <c r="O87" s="2" t="str">
         <f xml:space="preserve"> "(2,2,2)-type1"</f>
         <v>(2,2,2)-type1</v>
       </c>
       <c r="P87" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)</v>
       </c>
       <c r="Q87" s="10">
-        <f>3218 + 1557</f>
-        <v>4775</v>
+        <f>14106</f>
+        <v>14106</v>
       </c>
       <c r="R87" s="10">
         <f>R86 -Q86 + Q87</f>
-        <v>98471</v>
+        <v>107802</v>
       </c>
       <c r="S87" s="2">
         <f xml:space="preserve"> (1-(Q87/Q85))*100</f>
-        <v>99.899045765778567</v>
+        <v>99.701767449648685</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U87" s="2" t="s">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="V87" s="2" t="s">
         <v>15</v>
@@ -6060,34 +6072,34 @@
         <v>Reshape+TCL+TRL</v>
       </c>
       <c r="N88" s="2" t="str">
-        <f>"tcl::(1,1,1,50,2,2), trl:: (1,1,1,10,1,1,5)"</f>
-        <v>tcl::(1,1,1,50,2,2), trl:: (1,1,1,10,1,1,5)</v>
+        <f>"tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)"</f>
+        <v>tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)</v>
       </c>
       <c r="O88" s="2" t="str">
         <f xml:space="preserve"> "(2,2,2)-type2"</f>
         <v>(2,2,2)-type2</v>
       </c>
       <c r="P88" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)</v>
       </c>
       <c r="Q88" s="10">
-        <f>3218 + 1557</f>
-        <v>4775</v>
+        <f>14106</f>
+        <v>14106</v>
       </c>
       <c r="R88" s="10">
         <f xml:space="preserve"> R87 - Q87 + Q88</f>
-        <v>98471</v>
+        <v>107802</v>
       </c>
       <c r="S88" s="2">
         <f xml:space="preserve"> (1-(Q88/Q85))*100</f>
-        <v>99.899045765778567</v>
+        <v>99.701767449648685</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U88" s="2" t="s">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="V88" s="2" t="s">
         <v>15</v>
@@ -6101,62 +6113,62 @@
       <c r="G89" s="20">
         <v>1</v>
       </c>
-      <c r="H89" s="5" t="s">
+      <c r="H89" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I89" s="2" t="str">
+      <c r="I89" s="25" t="str">
         <f t="shared" si="32"/>
         <v>CNN</v>
       </c>
-      <c r="J89" s="2" t="str">
+      <c r="J89" s="25" t="str">
         <f t="shared" si="30"/>
         <v>MNIST</v>
       </c>
-      <c r="K89" s="2" t="str">
+      <c r="K89" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L89" s="2">
+      <c r="L89" s="25">
         <v>10</v>
       </c>
-      <c r="M89" s="2" t="str">
+      <c r="M89" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N89" s="2" t="str">
+      <c r="N89" s="25" t="str">
         <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)"</f>
         <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)</v>
       </c>
-      <c r="O89" s="2" t="str">
+      <c r="O89" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type1"</f>
         <v>(8,2,2)-type1</v>
       </c>
-      <c r="P89" s="2" t="str">
+      <c r="P89" s="25" t="str">
         <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)"</f>
         <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q89" s="10">
+      <c r="Q89" s="26">
         <f>192 + 208</f>
         <v>400</v>
       </c>
-      <c r="R89" s="10">
+      <c r="R89" s="26">
         <f>R88 -Q88+ Q89</f>
         <v>94096</v>
       </c>
-      <c r="S89" s="2">
+      <c r="S89" s="25">
         <f xml:space="preserve"> (1-(Q89/Q85))*100</f>
         <v>99.991543100798211</v>
       </c>
-      <c r="T89" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U89" s="2" t="s">
+      <c r="T89" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U89" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="V89" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W89" s="2" t="s">
+      <c r="V89" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W89" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6165,62 +6177,62 @@
       <c r="G90" s="20">
         <v>1</v>
       </c>
-      <c r="H90" s="5" t="s">
+      <c r="H90" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I90" s="2" t="str">
+      <c r="I90" s="25" t="str">
         <f t="shared" si="32"/>
         <v>CNN</v>
       </c>
-      <c r="J90" s="2" t="str">
+      <c r="J90" s="25" t="str">
         <f t="shared" si="30"/>
         <v>MNIST</v>
       </c>
-      <c r="K90" s="2" t="str">
+      <c r="K90" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L90" s="2">
+      <c r="L90" s="25">
         <v>10</v>
       </c>
-      <c r="M90" s="2" t="str">
+      <c r="M90" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N90" s="2" t="str">
+      <c r="N90" s="25" t="str">
         <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)"</f>
         <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)</v>
       </c>
-      <c r="O90" s="2" t="str">
+      <c r="O90" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type2"</f>
         <v>(8,2,2)-type2</v>
       </c>
-      <c r="P90" s="2" t="str">
+      <c r="P90" s="25" t="str">
         <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)"</f>
         <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q90" s="10">
+      <c r="Q90" s="26">
         <f>192 + 208</f>
         <v>400</v>
       </c>
-      <c r="R90" s="10">
+      <c r="R90" s="26">
         <f t="shared" ref="R90" si="33" xml:space="preserve"> R89 - Q89 + Q90</f>
         <v>94096</v>
       </c>
-      <c r="S90" s="2">
+      <c r="S90" s="25">
         <f xml:space="preserve"> (1-(Q90/Q85))*100</f>
         <v>99.991543100798211</v>
       </c>
-      <c r="T90" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U90" s="2" t="s">
+      <c r="T90" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U90" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="V90" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W90" s="2" t="s">
+      <c r="V90" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W90" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6294,7 +6306,7 @@
         <v>18</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="U92" s="2" t="s">
         <v>142</v>
@@ -6334,34 +6346,34 @@
         <v>TCL + TRL</v>
       </c>
       <c r="N93" s="2" t="str">
-        <f>"tcl:: (100,4,4), trl:: (70,2,2,10)"</f>
-        <v>tcl:: (100,4,4), trl:: (70,2,2,10)</v>
+        <f>"tcl:: (128,6,6), trl:: (128,6,6,10)"</f>
+        <v>tcl:: (128,6,6), trl:: (128,6,6,10)</v>
       </c>
       <c r="O93" s="2" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
       <c r="P93" s="2" t="str">
-        <f>"(128,6,6) --&gt; (100,4,4) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (100,4,4) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (128,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (128,6,6) --&gt; (10)</v>
       </c>
       <c r="Q93" s="10">
-        <f>12848 + 9916</f>
-        <v>22764</v>
+        <f>79092</f>
+        <v>79092</v>
       </c>
       <c r="R93" s="10">
         <f xml:space="preserve"> R92 - Q92 + Q93</f>
-        <v>116460</v>
+        <v>172788</v>
       </c>
       <c r="S93" s="2">
         <f xml:space="preserve"> (1-(Q93/Q92))*100</f>
-        <v>99.518717866425817</v>
+        <v>98.327817320828956</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U93" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="V93" s="2" t="s">
         <v>15</v>
@@ -6398,34 +6410,34 @@
         <v>Reshape+TCL+TRL</v>
       </c>
       <c r="N94" s="2" t="str">
-        <f>"tcl::(1,1,1,50,2,2), trl:: (1,1,1,10,1,1,5)"</f>
-        <v>tcl::(1,1,1,50,2,2), trl:: (1,1,1,10,1,1,5)</v>
+        <f>"tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)"</f>
+        <v>tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)</v>
       </c>
       <c r="O94" s="2" t="str">
         <f xml:space="preserve"> "(2,2,2)-type1"</f>
         <v>(2,2,2)-type1</v>
       </c>
       <c r="P94" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)</v>
       </c>
       <c r="Q94" s="10">
-        <f>3218 + 1557</f>
-        <v>4775</v>
+        <f>14106</f>
+        <v>14106</v>
       </c>
       <c r="R94" s="10">
         <f>R93 -Q93 + Q94</f>
-        <v>98471</v>
+        <v>107802</v>
       </c>
       <c r="S94" s="2">
         <f xml:space="preserve"> (1-(Q94/Q92))*100</f>
-        <v>99.899045765778567</v>
+        <v>99.701767449648685</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U94" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="V94" s="2" t="s">
         <v>15</v>
@@ -6462,34 +6474,34 @@
         <v>Reshape+TCL+TRL</v>
       </c>
       <c r="N95" s="2" t="str">
-        <f>"tcl::(1,1,1,50,2,2), trl:: (1,1,1,10,1,1,5)"</f>
-        <v>tcl::(1,1,1,50,2,2), trl:: (1,1,1,10,1,1,5)</v>
+        <f>"tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)"</f>
+        <v>tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)</v>
       </c>
       <c r="O95" s="2" t="str">
         <f xml:space="preserve"> "(2,2,2)-type2"</f>
         <v>(2,2,2)-type2</v>
       </c>
       <c r="P95" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)</v>
       </c>
       <c r="Q95" s="10">
-        <f>3218 + 1557</f>
-        <v>4775</v>
+        <f>14106</f>
+        <v>14106</v>
       </c>
       <c r="R95" s="10">
         <f xml:space="preserve"> R94 - Q94 + Q95</f>
-        <v>98471</v>
+        <v>107802</v>
       </c>
       <c r="S95" s="2">
         <f xml:space="preserve"> (1-(Q95/Q92))*100</f>
-        <v>99.899045765778567</v>
+        <v>99.701767449648685</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="U95" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="V95" s="2" t="s">
         <v>15</v>
@@ -6503,62 +6515,62 @@
       <c r="G96" s="20">
         <v>1</v>
       </c>
-      <c r="H96" s="5" t="s">
+      <c r="H96" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="I96" s="2" t="str">
+      <c r="I96" s="25" t="str">
         <f t="shared" si="35"/>
         <v>CNN</v>
       </c>
-      <c r="J96" s="2" t="str">
+      <c r="J96" s="25" t="str">
         <f t="shared" si="34"/>
         <v>CIFAR10</v>
       </c>
-      <c r="K96" s="2" t="str">
+      <c r="K96" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L96" s="2">
+      <c r="L96" s="25">
         <v>10</v>
       </c>
-      <c r="M96" s="2" t="str">
+      <c r="M96" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N96" s="2" t="str">
+      <c r="N96" s="25" t="str">
         <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)"</f>
         <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)</v>
       </c>
-      <c r="O96" s="2" t="str">
+      <c r="O96" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type1"</f>
         <v>(8,2,2)-type1</v>
       </c>
-      <c r="P96" s="2" t="str">
+      <c r="P96" s="25" t="str">
         <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)"</f>
         <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q96" s="10">
+      <c r="Q96" s="26">
         <f>192 + 208</f>
         <v>400</v>
       </c>
-      <c r="R96" s="10">
+      <c r="R96" s="26">
         <f>R95 -Q95+ Q96</f>
         <v>94096</v>
       </c>
-      <c r="S96" s="2">
+      <c r="S96" s="25">
         <f xml:space="preserve"> (1-(Q96/Q92))*100</f>
         <v>99.991543100798211</v>
       </c>
-      <c r="T96" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U96" s="2" t="s">
+      <c r="T96" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U96" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="V96" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W96" s="2" t="s">
+      <c r="V96" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W96" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6567,62 +6579,62 @@
       <c r="G97" s="20">
         <v>1</v>
       </c>
-      <c r="H97" s="5" t="s">
+      <c r="H97" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="I97" s="2" t="str">
+      <c r="I97" s="25" t="str">
         <f t="shared" si="35"/>
         <v>CNN</v>
       </c>
-      <c r="J97" s="2" t="str">
+      <c r="J97" s="25" t="str">
         <f t="shared" si="34"/>
         <v>CIFAR10</v>
       </c>
-      <c r="K97" s="2" t="str">
+      <c r="K97" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L97" s="2">
+      <c r="L97" s="25">
         <v>10</v>
       </c>
-      <c r="M97" s="2" t="str">
+      <c r="M97" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N97" s="2" t="str">
+      <c r="N97" s="25" t="str">
         <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)"</f>
         <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)</v>
       </c>
-      <c r="O97" s="2" t="str">
+      <c r="O97" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type2"</f>
         <v>(8,2,2)-type2</v>
       </c>
-      <c r="P97" s="2" t="str">
+      <c r="P97" s="25" t="str">
         <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)"</f>
         <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q97" s="10">
+      <c r="Q97" s="26">
         <f>192 + 208</f>
         <v>400</v>
       </c>
-      <c r="R97" s="10">
+      <c r="R97" s="26">
         <f t="shared" ref="R97" si="36" xml:space="preserve"> R96 - Q96 + Q97</f>
         <v>94096</v>
       </c>
-      <c r="S97" s="2">
+      <c r="S97" s="25">
         <f xml:space="preserve"> (1-(Q97/Q92))*100</f>
         <v>99.991543100798211</v>
       </c>
-      <c r="T97" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U97" s="2" t="s">
+      <c r="T97" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U97" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="V97" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W97" s="2" t="s">
+      <c r="V97" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W97" s="25" t="s">
         <v>17</v>
       </c>
     </row>

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="150">
   <si>
     <t>Dataset</t>
   </si>
@@ -469,6 +469,9 @@
   </si>
   <si>
     <t>50 Epoch</t>
+  </si>
+  <si>
+    <t>15 Epoch</t>
   </si>
 </sst>
 </file>
@@ -6370,10 +6373,10 @@
         <v>98.327817320828956</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="U93" s="2" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="V93" s="2" t="s">
         <v>15</v>
@@ -6434,10 +6437,10 @@
         <v>99.701767449648685</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="U94" s="2" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="V94" s="2" t="s">
         <v>15</v>
@@ -6498,10 +6501,10 @@
         <v>99.701767449648685</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="U95" s="2" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="V95" s="2" t="s">
         <v>15</v>

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="147">
   <si>
     <t>Dataset</t>
   </si>
@@ -345,18 +345,6 @@
     <t>080</t>
   </si>
   <si>
-    <t>081</t>
-  </si>
-  <si>
-    <t>082</t>
-  </si>
-  <si>
-    <t>083</t>
-  </si>
-  <si>
-    <t>084</t>
-  </si>
-  <si>
     <t>085</t>
   </si>
   <si>
@@ -472,6 +460,9 @@
   </si>
   <si>
     <t>15 Epoch</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1048,7 @@
         <v>26</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1076,7 +1067,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1085,7 +1076,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="2:23" s="1" customFormat="1" ht="43.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2763,7 +2754,7 @@
         <v>18</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>13</v>
@@ -2772,7 +2763,7 @@
         <v>15</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2827,7 +2818,7 @@
         <v>73.006632397021519</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>13</v>
@@ -2836,7 +2827,7 @@
         <v>15</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2891,7 +2882,7 @@
         <v>84.071152463752384</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>13</v>
@@ -2900,7 +2891,7 @@
         <v>15</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2955,7 +2946,7 @@
         <v>88.274383214203368</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>13</v>
@@ -2964,7 +2955,7 @@
         <v>15</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3019,7 +3010,7 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>13</v>
@@ -3028,7 +3019,7 @@
         <v>15</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3083,7 +3074,7 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>13</v>
@@ -3092,7 +3083,7 @@
         <v>15</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3147,7 +3138,7 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>13</v>
@@ -3156,7 +3147,7 @@
         <v>15</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3211,7 +3202,7 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>13</v>
@@ -3220,7 +3211,7 @@
         <v>15</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3275,7 +3266,7 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>13</v>
@@ -3284,7 +3275,7 @@
         <v>15</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3339,7 +3330,7 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>13</v>
@@ -3348,7 +3339,7 @@
         <v>15</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3403,7 +3394,7 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>13</v>
@@ -3412,7 +3403,7 @@
         <v>15</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3467,7 +3458,7 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>13</v>
@@ -3476,7 +3467,7 @@
         <v>15</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5910,7 +5901,7 @@
         <v>12</v>
       </c>
       <c r="U85" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="V85" s="2" t="s">
         <v>15</v>
@@ -6007,32 +5998,32 @@
         <v>10</v>
       </c>
       <c r="M87" s="2" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N87" s="2" t="str">
-        <f>"tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)"</f>
-        <v>tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)</v>
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)</v>
       </c>
       <c r="O87" s="2" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type1"</f>
-        <v>(2,2,2)-type1</v>
+        <f xml:space="preserve"> "(2,1,1)-type1"</f>
+        <v>(2,1,1)-type1</v>
       </c>
       <c r="P87" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)</v>
       </c>
       <c r="Q87" s="10">
-        <f>14106</f>
-        <v>14106</v>
+        <f>54528</f>
+        <v>54528</v>
       </c>
       <c r="R87" s="10">
         <f>R86 -Q86 + Q87</f>
-        <v>107802</v>
+        <v>148224</v>
       </c>
       <c r="S87" s="2">
         <f xml:space="preserve"> (1-(Q87/Q85))*100</f>
-        <v>99.701767449648685</v>
+        <v>98.847155500811226</v>
       </c>
       <c r="T87" s="2" t="s">
         <v>145</v>
@@ -6071,32 +6062,32 @@
         <v>10</v>
       </c>
       <c r="M88" s="2" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N88" s="2" t="str">
-        <f>"tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)"</f>
-        <v>tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)</v>
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)</v>
       </c>
       <c r="O88" s="2" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type2"</f>
-        <v>(2,2,2)-type2</v>
+        <f xml:space="preserve"> "(2,1,1)-type2"</f>
+        <v>(2,1,1)-type2</v>
       </c>
       <c r="P88" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)</v>
       </c>
       <c r="Q88" s="10">
-        <f>14106</f>
-        <v>14106</v>
+        <f>54528</f>
+        <v>54528</v>
       </c>
       <c r="R88" s="10">
         <f xml:space="preserve"> R87 - Q87 + Q88</f>
-        <v>107802</v>
+        <v>148224</v>
       </c>
       <c r="S88" s="2">
         <f xml:space="preserve"> (1-(Q88/Q85))*100</f>
-        <v>99.701767449648685</v>
+        <v>98.847155500811226</v>
       </c>
       <c r="T88" s="2" t="s">
         <v>145</v>
@@ -6117,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="I89" s="25" t="str">
         <f t="shared" si="32"/>
@@ -6166,7 +6157,7 @@
         <v>13</v>
       </c>
       <c r="U89" s="25" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V89" s="25" t="s">
         <v>15</v>
@@ -6181,7 +6172,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="I90" s="25" t="str">
         <f t="shared" si="32"/>
@@ -6230,7 +6221,7 @@
         <v>13</v>
       </c>
       <c r="U90" s="25" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V90" s="25" t="s">
         <v>15</v>
@@ -6265,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I92" s="2" t="str">
         <f xml:space="preserve"> "CNN"</f>
@@ -6309,10 +6300,10 @@
         <v>18</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="U92" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I93" s="2" t="str">
         <f t="shared" ref="I93:I97" si="35" xml:space="preserve"> "CNN"</f>
@@ -6373,7 +6364,7 @@
         <v>98.327817320828956</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="U93" s="2" t="s">
         <v>13</v>
@@ -6391,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I94" s="2" t="str">
         <f t="shared" si="35"/>
@@ -6409,35 +6400,35 @@
         <v>10</v>
       </c>
       <c r="M94" s="2" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N94" s="2" t="str">
-        <f>"tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)"</f>
-        <v>tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)</v>
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)</v>
       </c>
       <c r="O94" s="2" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type1"</f>
-        <v>(2,2,2)-type1</v>
+        <f xml:space="preserve"> "(2,1,1)-type1"</f>
+        <v>(2,1,1)-type1</v>
       </c>
       <c r="P94" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)</v>
       </c>
       <c r="Q94" s="10">
-        <f>14106</f>
-        <v>14106</v>
+        <f>54528</f>
+        <v>54528</v>
       </c>
       <c r="R94" s="10">
         <f>R93 -Q93 + Q94</f>
-        <v>107802</v>
+        <v>148224</v>
       </c>
       <c r="S94" s="2">
         <f xml:space="preserve"> (1-(Q94/Q92))*100</f>
-        <v>99.701767449648685</v>
+        <v>98.847155500811226</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="U94" s="2" t="s">
         <v>13</v>
@@ -6455,7 +6446,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I95" s="2" t="str">
         <f t="shared" si="35"/>
@@ -6473,35 +6464,35 @@
         <v>10</v>
       </c>
       <c r="M95" s="2" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N95" s="2" t="str">
-        <f>"tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)"</f>
-        <v>tcl::(2,2,2,64,3,3), trl:: (1,1,1,64,3,3,10)</v>
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)</v>
       </c>
       <c r="O95" s="2" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type2"</f>
-        <v>(2,2,2)-type2</v>
+        <f xml:space="preserve"> "(2,1,1)-type2"</f>
+        <v>(2,1,1)-type2</v>
       </c>
       <c r="P95" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (2,2,2,64,3,3) --&gt; (10)</v>
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)</v>
       </c>
       <c r="Q95" s="10">
-        <f>14106</f>
-        <v>14106</v>
+        <f>54528</f>
+        <v>54528</v>
       </c>
       <c r="R95" s="10">
         <f xml:space="preserve"> R94 - Q94 + Q95</f>
-        <v>107802</v>
+        <v>148224</v>
       </c>
       <c r="S95" s="2">
         <f xml:space="preserve"> (1-(Q95/Q92))*100</f>
-        <v>99.701767449648685</v>
+        <v>98.847155500811226</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="U95" s="2" t="s">
         <v>13</v>
@@ -6519,7 +6510,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="I96" s="25" t="str">
         <f t="shared" si="35"/>
@@ -6568,7 +6559,7 @@
         <v>13</v>
       </c>
       <c r="U96" s="25" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V96" s="25" t="s">
         <v>15</v>
@@ -6583,7 +6574,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="I97" s="25" t="str">
         <f t="shared" si="35"/>
@@ -6632,7 +6623,7 @@
         <v>13</v>
       </c>
       <c r="U97" s="25" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V97" s="25" t="s">
         <v>15</v>
@@ -6667,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I99" s="2" t="str">
         <f xml:space="preserve"> "CNN"</f>
@@ -6711,10 +6702,10 @@
         <v>18</v>
       </c>
       <c r="T99" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="U99" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>15</v>
@@ -6729,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I100" s="2" t="str">
         <f t="shared" ref="I100:I104" si="37" xml:space="preserve"> "CNN"</f>
@@ -6778,7 +6769,7 @@
         <v>13</v>
       </c>
       <c r="U100" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V100" s="2" t="s">
         <v>15</v>
@@ -6793,7 +6784,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I101" s="2" t="str">
         <f t="shared" si="37"/>
@@ -6842,7 +6833,7 @@
         <v>13</v>
       </c>
       <c r="U101" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>15</v>
@@ -6857,7 +6848,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I102" s="2" t="str">
         <f t="shared" si="37"/>
@@ -6906,7 +6897,7 @@
         <v>13</v>
       </c>
       <c r="U102" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V102" s="2" t="s">
         <v>15</v>
@@ -6921,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I103" s="2" t="str">
         <f t="shared" si="37"/>
@@ -6970,7 +6961,7 @@
         <v>13</v>
       </c>
       <c r="U103" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V103" s="2" t="s">
         <v>15</v>
@@ -6985,7 +6976,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I104" s="2" t="str">
         <f t="shared" si="37"/>
@@ -7034,7 +7025,7 @@
         <v>13</v>
       </c>
       <c r="U104" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="V104" s="2" t="s">
         <v>15</v>
@@ -7069,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I106" s="2" t="str">
         <f xml:space="preserve"> "VGG19"</f>
@@ -7131,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I107" s="2" t="str">
         <f t="shared" ref="I107:I111" si="41" xml:space="preserve"> "VGG19"</f>
@@ -7195,7 +7186,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I108" s="2" t="str">
         <f t="shared" si="41"/>
@@ -7259,7 +7250,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I109" s="2" t="str">
         <f t="shared" si="41"/>
@@ -7323,7 +7314,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I110" s="2" t="str">
         <f t="shared" si="41"/>
@@ -7387,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I111" s="2" t="str">
         <f t="shared" si="41"/>
@@ -7471,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I113" s="2" t="str">
         <f xml:space="preserve"> "VGG19"</f>
@@ -7533,7 +7524,7 @@
         <v>1</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I114" s="2" t="str">
         <f t="shared" ref="I114:I118" si="43" xml:space="preserve"> "VGG19"</f>
@@ -7597,7 +7588,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I115" s="2" t="str">
         <f t="shared" si="43"/>
@@ -7661,7 +7652,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I116" s="2" t="str">
         <f t="shared" si="43"/>
@@ -7725,7 +7716,7 @@
         <v>1</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I117" s="2" t="str">
         <f t="shared" si="43"/>
@@ -7789,7 +7780,7 @@
         <v>1</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I118" s="2" t="str">
         <f t="shared" si="43"/>
@@ -7873,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I120" s="2" t="str">
         <f xml:space="preserve"> "VGG19"</f>
@@ -7935,7 +7926,7 @@
         <v>1</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I121" s="2" t="str">
         <f t="shared" ref="I121:I125" si="46" xml:space="preserve"> "VGG19"</f>
@@ -7999,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I122" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8063,7 +8054,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I123" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8127,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I124" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8191,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I125" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8273,42 +8264,42 @@
       <c r="F127" s="15"/>
       <c r="G127" s="16"/>
       <c r="H127" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="128" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F128" s="15"/>
       <c r="G128" s="16"/>
       <c r="H128" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F129" s="15"/>
       <c r="G129" s="16"/>
       <c r="H129" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="130" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F130" s="15"/>
       <c r="G130" s="16"/>
       <c r="H130" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F131" s="15"/>
       <c r="G131" s="16"/>
       <c r="H131" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="132" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F132" s="15"/>
       <c r="G132" s="16"/>
       <c r="H132" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="6:8" ht="21.75" thickTop="1" x14ac:dyDescent="0.35">

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="144">
   <si>
     <t>Dataset</t>
   </si>
@@ -345,24 +345,6 @@
     <t>080</t>
   </si>
   <si>
-    <t>085</t>
-  </si>
-  <si>
-    <t>086</t>
-  </si>
-  <si>
-    <t>087</t>
-  </si>
-  <si>
-    <t>088</t>
-  </si>
-  <si>
-    <t>089</t>
-  </si>
-  <si>
-    <t>090</t>
-  </si>
-  <si>
     <t>091</t>
   </si>
   <si>
@@ -441,9 +423,6 @@
     <t>0 Epoch</t>
   </si>
   <si>
-    <t>100 Epoch</t>
-  </si>
-  <si>
     <t>40 Epoch</t>
   </si>
   <si>
@@ -463,6 +442,18 @@
   </si>
   <si>
     <t>null</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>084</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1039,7 @@
         <v>26</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1067,7 +1058,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1076,7 +1067,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="2:23" s="1" customFormat="1" ht="43.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2754,7 +2745,7 @@
         <v>18</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>13</v>
@@ -2763,7 +2754,7 @@
         <v>15</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2818,7 +2809,7 @@
         <v>73.006632397021519</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>13</v>
@@ -2827,7 +2818,7 @@
         <v>15</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2882,7 +2873,7 @@
         <v>84.071152463752384</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>13</v>
@@ -2891,7 +2882,7 @@
         <v>15</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2946,7 +2937,7 @@
         <v>88.274383214203368</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>13</v>
@@ -2955,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3010,7 +3001,7 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>13</v>
@@ -3019,7 +3010,7 @@
         <v>15</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3074,7 +3065,7 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>13</v>
@@ -3083,7 +3074,7 @@
         <v>15</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3138,7 +3129,7 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>13</v>
@@ -3147,7 +3138,7 @@
         <v>15</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3202,7 +3193,7 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>13</v>
@@ -3211,7 +3202,7 @@
         <v>15</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3266,7 +3257,7 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>13</v>
@@ -3275,7 +3266,7 @@
         <v>15</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3330,7 +3321,7 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>13</v>
@@ -3339,7 +3330,7 @@
         <v>15</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3394,7 +3385,7 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>13</v>
@@ -3403,7 +3394,7 @@
         <v>15</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3458,7 +3449,7 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>13</v>
@@ -3467,7 +3458,7 @@
         <v>15</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5850,7 +5841,7 @@
     </row>
     <row r="85" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F85" s="15"/>
-      <c r="G85" s="19">
+      <c r="G85" s="23">
         <v>1</v>
       </c>
       <c r="H85" s="5" t="s">
@@ -5901,7 +5892,7 @@
         <v>12</v>
       </c>
       <c r="U85" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="V85" s="2" t="s">
         <v>15</v>
@@ -5912,7 +5903,7 @@
     </row>
     <row r="86" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F86" s="15"/>
-      <c r="G86" s="19">
+      <c r="G86" s="23">
         <v>1</v>
       </c>
       <c r="H86" s="5" t="s">
@@ -5962,7 +5953,7 @@
         <v>98.327817320828956</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="U86" s="2" t="s">
         <v>13</v>
@@ -5976,7 +5967,7 @@
     </row>
     <row r="87" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F87" s="15"/>
-      <c r="G87" s="19">
+      <c r="G87" s="23">
         <v>1</v>
       </c>
       <c r="H87" s="5" t="s">
@@ -6026,7 +6017,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="U87" s="2" t="s">
         <v>13</v>
@@ -6040,7 +6031,7 @@
     </row>
     <row r="88" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F88" s="15"/>
-      <c r="G88" s="19">
+      <c r="G88" s="23">
         <v>1</v>
       </c>
       <c r="H88" s="5" t="s">
@@ -6090,7 +6081,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="U88" s="2" t="s">
         <v>13</v>
@@ -6108,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I89" s="25" t="str">
         <f t="shared" si="32"/>
@@ -6157,7 +6148,7 @@
         <v>13</v>
       </c>
       <c r="U89" s="25" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="V89" s="25" t="s">
         <v>15</v>
@@ -6172,7 +6163,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I90" s="25" t="str">
         <f t="shared" si="32"/>
@@ -6221,7 +6212,7 @@
         <v>13</v>
       </c>
       <c r="U90" s="25" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="V90" s="25" t="s">
         <v>15</v>
@@ -6252,7 +6243,7 @@
     </row>
     <row r="92" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F92" s="15"/>
-      <c r="G92" s="19">
+      <c r="G92" s="23">
         <v>1</v>
       </c>
       <c r="H92" s="5" t="s">
@@ -6300,10 +6291,10 @@
         <v>18</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="U92" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>15</v>
@@ -6314,7 +6305,7 @@
     </row>
     <row r="93" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F93" s="15"/>
-      <c r="G93" s="19">
+      <c r="G93" s="23">
         <v>1</v>
       </c>
       <c r="H93" s="5" t="s">
@@ -6364,7 +6355,7 @@
         <v>98.327817320828956</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="U93" s="2" t="s">
         <v>13</v>
@@ -6378,7 +6369,7 @@
     </row>
     <row r="94" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F94" s="15"/>
-      <c r="G94" s="19">
+      <c r="G94" s="23">
         <v>1</v>
       </c>
       <c r="H94" s="5" t="s">
@@ -6428,7 +6419,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="U94" s="2" t="s">
         <v>13</v>
@@ -6442,7 +6433,7 @@
     </row>
     <row r="95" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F95" s="15"/>
-      <c r="G95" s="19">
+      <c r="G95" s="23">
         <v>1</v>
       </c>
       <c r="H95" s="5" t="s">
@@ -6492,7 +6483,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="U95" s="2" t="s">
         <v>13</v>
@@ -6510,7 +6501,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I96" s="25" t="str">
         <f t="shared" si="35"/>
@@ -6559,7 +6550,7 @@
         <v>13</v>
       </c>
       <c r="U96" s="25" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="V96" s="25" t="s">
         <v>15</v>
@@ -6574,7 +6565,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I97" s="25" t="str">
         <f t="shared" si="35"/>
@@ -6623,7 +6614,7 @@
         <v>13</v>
       </c>
       <c r="U97" s="25" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="V97" s="25" t="s">
         <v>15</v>
@@ -6654,11 +6645,11 @@
     </row>
     <row r="99" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F99" s="15"/>
-      <c r="G99" s="20">
+      <c r="G99" s="23">
         <v>1</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="I99" s="2" t="str">
         <f xml:space="preserve"> "CNN"</f>
@@ -6702,10 +6693,10 @@
         <v>18</v>
       </c>
       <c r="T99" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="U99" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>15</v>
@@ -6716,11 +6707,11 @@
     </row>
     <row r="100" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F100" s="15"/>
-      <c r="G100" s="20">
+      <c r="G100" s="23">
         <v>1</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="I100" s="2" t="str">
         <f t="shared" ref="I100:I104" si="37" xml:space="preserve"> "CNN"</f>
@@ -6742,34 +6733,34 @@
         <v>TCL + TRL</v>
       </c>
       <c r="N100" s="2" t="str">
-        <f>"tcl:: (100,4,4), trl:: (70,2,2,200)"</f>
-        <v>tcl:: (100,4,4), trl:: (70,2,2,200)</v>
+        <f>"tcl:: (128,6,6), trl:: (128,6,6,200)"</f>
+        <v>tcl:: (128,6,6), trl:: (128,6,6,200)</v>
       </c>
       <c r="O100" s="2" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
       <c r="P100" s="2" t="str">
-        <f>"(128,6,6) --&gt; (100,4,4) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (100,4,4) --&gt; (200)</v>
+        <f>"(128,6,6) --&gt; (128,6,6) --&gt; (200)"</f>
+        <v>(128,6,6) --&gt; (128,6,6) --&gt; (200)</v>
       </c>
       <c r="Q100" s="10">
-        <f>12848 + 103016</f>
-        <v>115864</v>
+        <f>994512</f>
+        <v>994512</v>
       </c>
       <c r="R100" s="10">
         <f xml:space="preserve"> R99 - Q99 + Q100</f>
-        <v>209560</v>
+        <v>1088208</v>
       </c>
       <c r="S100" s="2">
         <f xml:space="preserve"> (1-(Q100/Q99))*100</f>
-        <v>97.647248029084906</v>
+        <v>79.805288371722796</v>
       </c>
       <c r="T100" s="2" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="U100" s="2" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="V100" s="2" t="s">
         <v>15</v>
@@ -6780,11 +6771,11 @@
     </row>
     <row r="101" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F101" s="15"/>
-      <c r="G101" s="20">
+      <c r="G101" s="23">
         <v>1</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="I101" s="2" t="str">
         <f t="shared" si="37"/>
@@ -6802,38 +6793,38 @@
         <v>200</v>
       </c>
       <c r="M101" s="2" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N101" s="2" t="str">
-        <f>"tcl::(1,1,1,50,2,2), trl:: (1,1,1,30,1,1,100)"</f>
-        <v>tcl::(1,1,1,50,2,2), trl:: (1,1,1,30,1,1,100)</v>
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)</v>
       </c>
       <c r="O101" s="2" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type1"</f>
-        <v>(2,2,2)-type1</v>
+        <f xml:space="preserve"> "(2,1,1)-type1"</f>
+        <v>(2,1,1)-type1</v>
       </c>
       <c r="P101" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (200)</v>
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)</v>
       </c>
       <c r="Q101" s="10">
-        <f>3218 + 24507</f>
-        <v>27725</v>
+        <f>227416</f>
+        <v>227416</v>
       </c>
       <c r="R101" s="10">
         <f>R100 -Q100 + Q101</f>
-        <v>121421</v>
+        <v>321112</v>
       </c>
       <c r="S101" s="2">
         <f xml:space="preserve"> (1-(Q101/Q99))*100</f>
-        <v>99.437011941641742</v>
+        <v>95.382056184685254</v>
       </c>
       <c r="T101" s="2" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="U101" s="2" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>15</v>
@@ -6844,11 +6835,11 @@
     </row>
     <row r="102" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F102" s="15"/>
-      <c r="G102" s="20">
+      <c r="G102" s="23">
         <v>1</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="I102" s="2" t="str">
         <f t="shared" si="37"/>
@@ -6866,38 +6857,38 @@
         <v>200</v>
       </c>
       <c r="M102" s="2" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N102" s="2" t="str">
-        <f>"tcl::(1,1,1,50,2,2), trl:: (1,1,1,30,1,1,100)"</f>
-        <v>tcl::(1,1,1,50,2,2), trl:: (1,1,1,30,1,1,100)</v>
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)</v>
       </c>
       <c r="O102" s="2" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type2"</f>
-        <v>(2,2,2)-type2</v>
+        <f xml:space="preserve"> "(2,1,1)-type2"</f>
+        <v>(2,1,1)-type2</v>
       </c>
       <c r="P102" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (2,2,2,64,3,3) --&gt; (1,1,1,50,2,2) --&gt; (200)</v>
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)</v>
       </c>
       <c r="Q102" s="10">
-        <f>3218 + 24507</f>
-        <v>27725</v>
+        <f>227416</f>
+        <v>227416</v>
       </c>
       <c r="R102" s="10">
         <f xml:space="preserve"> R101 - Q101 + Q102</f>
-        <v>121421</v>
+        <v>321112</v>
       </c>
       <c r="S102" s="2">
         <f xml:space="preserve"> (1-(Q102/Q99))*100</f>
-        <v>99.437011941641742</v>
+        <v>95.382056184685254</v>
       </c>
       <c r="T102" s="2" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="U102" s="2" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="V102" s="2" t="s">
         <v>15</v>
@@ -6911,62 +6902,62 @@
       <c r="G103" s="20">
         <v>1</v>
       </c>
-      <c r="H103" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I103" s="2" t="str">
+      <c r="H103" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="I103" s="25" t="str">
         <f t="shared" si="37"/>
         <v>CNN</v>
       </c>
-      <c r="J103" s="2" t="str">
+      <c r="J103" s="25" t="str">
         <f t="shared" si="38"/>
         <v>TINY</v>
       </c>
-      <c r="K103" s="2" t="str">
+      <c r="K103" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L103" s="2">
+      <c r="L103" s="25">
         <v>200</v>
       </c>
-      <c r="M103" s="2" t="str">
+      <c r="M103" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N103" s="2" t="str">
+      <c r="N103" s="25" t="str">
         <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,50)"</f>
         <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,50)</v>
       </c>
-      <c r="O103" s="2" t="str">
+      <c r="O103" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type1"</f>
         <v>(8,2,2)-type1</v>
       </c>
-      <c r="P103" s="2" t="str">
+      <c r="P103" s="25" t="str">
         <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (200)"</f>
         <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (200)</v>
       </c>
-      <c r="Q103" s="10">
+      <c r="Q103" s="26">
         <f>192 + 10308</f>
         <v>10500</v>
       </c>
-      <c r="R103" s="10">
+      <c r="R103" s="26">
         <f>R102 -Q102+ Q103</f>
         <v>104196</v>
       </c>
-      <c r="S103" s="2">
+      <c r="S103" s="25">
         <f xml:space="preserve"> (1-(Q103/Q99))*100</f>
         <v>99.786785406212388</v>
       </c>
-      <c r="T103" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U103" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="V103" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W103" s="2" t="s">
+      <c r="T103" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U103" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="V103" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W103" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6975,62 +6966,62 @@
       <c r="G104" s="20">
         <v>1</v>
       </c>
-      <c r="H104" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="I104" s="2" t="str">
+      <c r="H104" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="I104" s="25" t="str">
         <f t="shared" si="37"/>
         <v>CNN</v>
       </c>
-      <c r="J104" s="2" t="str">
+      <c r="J104" s="25" t="str">
         <f t="shared" si="38"/>
         <v>TINY</v>
       </c>
-      <c r="K104" s="2" t="str">
+      <c r="K104" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L104" s="2">
+      <c r="L104" s="25">
         <v>200</v>
       </c>
-      <c r="M104" s="2" t="str">
+      <c r="M104" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N104" s="2" t="str">
+      <c r="N104" s="25" t="str">
         <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,50)"</f>
         <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,50)</v>
       </c>
-      <c r="O104" s="2" t="str">
+      <c r="O104" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type2"</f>
         <v>(8,2,2)-type2</v>
       </c>
-      <c r="P104" s="2" t="str">
+      <c r="P104" s="25" t="str">
         <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (200)"</f>
         <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (200)</v>
       </c>
-      <c r="Q104" s="10">
+      <c r="Q104" s="26">
         <f>192 + 10308</f>
         <v>10500</v>
       </c>
-      <c r="R104" s="10">
+      <c r="R104" s="26">
         <f t="shared" ref="R104" si="39" xml:space="preserve"> R103 - Q103 + Q104</f>
         <v>104196</v>
       </c>
-      <c r="S104" s="2">
+      <c r="S104" s="25">
         <f xml:space="preserve"> (1-(Q104/Q99))*100</f>
         <v>99.786785406212388</v>
       </c>
-      <c r="T104" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U104" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="V104" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W104" s="2" t="s">
+      <c r="T104" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U104" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="V104" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W104" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7060,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I106" s="2" t="str">
         <f xml:space="preserve"> "VGG19"</f>
@@ -7122,7 +7113,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I107" s="2" t="str">
         <f t="shared" ref="I107:I111" si="41" xml:space="preserve"> "VGG19"</f>
@@ -7186,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I108" s="2" t="str">
         <f t="shared" si="41"/>
@@ -7250,7 +7241,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I109" s="2" t="str">
         <f t="shared" si="41"/>
@@ -7314,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I110" s="2" t="str">
         <f t="shared" si="41"/>
@@ -7378,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I111" s="2" t="str">
         <f t="shared" si="41"/>
@@ -7462,7 +7453,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I113" s="2" t="str">
         <f xml:space="preserve"> "VGG19"</f>
@@ -7524,7 +7515,7 @@
         <v>1</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="I114" s="2" t="str">
         <f t="shared" ref="I114:I118" si="43" xml:space="preserve"> "VGG19"</f>
@@ -7588,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="I115" s="2" t="str">
         <f t="shared" si="43"/>
@@ -7652,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I116" s="2" t="str">
         <f t="shared" si="43"/>
@@ -7716,7 +7707,7 @@
         <v>1</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="I117" s="2" t="str">
         <f t="shared" si="43"/>
@@ -7780,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I118" s="2" t="str">
         <f t="shared" si="43"/>
@@ -7864,7 +7855,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I120" s="2" t="str">
         <f xml:space="preserve"> "VGG19"</f>
@@ -7926,7 +7917,7 @@
         <v>1</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I121" s="2" t="str">
         <f t="shared" ref="I121:I125" si="46" xml:space="preserve"> "VGG19"</f>
@@ -7990,7 +7981,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I122" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8054,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I123" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8118,7 +8109,7 @@
         <v>1</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="I124" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8182,7 +8173,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I125" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8264,42 +8255,42 @@
       <c r="F127" s="15"/>
       <c r="G127" s="16"/>
       <c r="H127" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F128" s="15"/>
       <c r="G128" s="16"/>
       <c r="H128" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="129" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F129" s="15"/>
       <c r="G129" s="16"/>
       <c r="H129" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F130" s="15"/>
       <c r="G130" s="16"/>
       <c r="H130" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F131" s="15"/>
       <c r="G131" s="16"/>
       <c r="H131" s="5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F132" s="15"/>
       <c r="G132" s="16"/>
       <c r="H132" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="6:8" ht="21.75" thickTop="1" x14ac:dyDescent="0.35">

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="125">
   <si>
     <t>Dataset</t>
   </si>
@@ -345,81 +345,9 @@
     <t>080</t>
   </si>
   <si>
-    <t>091</t>
-  </si>
-  <si>
-    <t>092</t>
-  </si>
-  <si>
-    <t>093</t>
-  </si>
-  <si>
-    <t>094</t>
-  </si>
-  <si>
-    <t>095</t>
-  </si>
-  <si>
-    <t>096</t>
-  </si>
-  <si>
-    <t>097</t>
-  </si>
-  <si>
-    <t>098</t>
-  </si>
-  <si>
-    <t>099</t>
-  </si>
-  <si>
     <t>Count</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>0 Epoch</t>
   </si>
   <si>
@@ -454,6 +382,21 @@
   </si>
   <si>
     <t>084</t>
+  </si>
+  <si>
+    <t>20 Epoch</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>088</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +982,7 @@
         <v>26</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1048,8 +991,8 @@
         <v>23</v>
       </c>
       <c r="D3" s="14">
-        <f>72</f>
-        <v>72</v>
+        <f>84</f>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1058,7 +1001,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1067,7 +1010,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="2:23" s="1" customFormat="1" ht="43.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2745,7 +2688,7 @@
         <v>18</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>13</v>
@@ -2754,7 +2697,7 @@
         <v>15</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2809,7 +2752,7 @@
         <v>73.006632397021519</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>13</v>
@@ -2818,7 +2761,7 @@
         <v>15</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2873,7 +2816,7 @@
         <v>84.071152463752384</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>13</v>
@@ -2882,7 +2825,7 @@
         <v>15</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2937,7 +2880,7 @@
         <v>88.274383214203368</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>13</v>
@@ -2946,7 +2889,7 @@
         <v>15</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3001,7 +2944,7 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>13</v>
@@ -3010,7 +2953,7 @@
         <v>15</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3065,7 +3008,7 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>13</v>
@@ -3074,7 +3017,7 @@
         <v>15</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3129,7 +3072,7 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>13</v>
@@ -3138,7 +3081,7 @@
         <v>15</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3193,7 +3136,7 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>13</v>
@@ -3202,7 +3145,7 @@
         <v>15</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3257,7 +3200,7 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>13</v>
@@ -3266,7 +3209,7 @@
         <v>15</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3321,7 +3264,7 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>13</v>
@@ -3330,7 +3273,7 @@
         <v>15</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3385,7 +3328,7 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>13</v>
@@ -3394,7 +3337,7 @@
         <v>15</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3449,7 +3392,7 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>13</v>
@@ -3458,7 +3401,7 @@
         <v>15</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5892,7 +5835,7 @@
         <v>12</v>
       </c>
       <c r="U85" s="2" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="V85" s="2" t="s">
         <v>15</v>
@@ -5953,7 +5896,7 @@
         <v>98.327817320828956</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="U86" s="2" t="s">
         <v>13</v>
@@ -6017,7 +5960,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="U87" s="2" t="s">
         <v>13</v>
@@ -6081,7 +6024,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="U88" s="2" t="s">
         <v>13</v>
@@ -6099,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I89" s="25" t="str">
         <f t="shared" si="32"/>
@@ -6148,7 +6091,7 @@
         <v>13</v>
       </c>
       <c r="U89" s="25" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="V89" s="25" t="s">
         <v>15</v>
@@ -6163,7 +6106,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I90" s="25" t="str">
         <f t="shared" si="32"/>
@@ -6212,7 +6155,7 @@
         <v>13</v>
       </c>
       <c r="U90" s="25" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="V90" s="25" t="s">
         <v>15</v>
@@ -6291,10 +6234,10 @@
         <v>18</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="U92" s="2" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>15</v>
@@ -6355,7 +6298,7 @@
         <v>98.327817320828956</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="U93" s="2" t="s">
         <v>13</v>
@@ -6419,7 +6362,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="U94" s="2" t="s">
         <v>13</v>
@@ -6483,7 +6426,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="U95" s="2" t="s">
         <v>13</v>
@@ -6501,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I96" s="25" t="str">
         <f t="shared" si="35"/>
@@ -6550,7 +6493,7 @@
         <v>13</v>
       </c>
       <c r="U96" s="25" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="V96" s="25" t="s">
         <v>15</v>
@@ -6565,7 +6508,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I97" s="25" t="str">
         <f t="shared" si="35"/>
@@ -6614,7 +6557,7 @@
         <v>13</v>
       </c>
       <c r="U97" s="25" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="V97" s="25" t="s">
         <v>15</v>
@@ -6649,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="I99" s="2" t="str">
         <f xml:space="preserve"> "CNN"</f>
@@ -6693,10 +6636,10 @@
         <v>18</v>
       </c>
       <c r="T99" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="U99" s="2" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6654,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="I100" s="2" t="str">
         <f t="shared" ref="I100:I104" si="37" xml:space="preserve"> "CNN"</f>
@@ -6757,10 +6700,10 @@
         <v>79.805288371722796</v>
       </c>
       <c r="T100" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="U100" s="2" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="V100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6718,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="I101" s="2" t="str">
         <f t="shared" si="37"/>
@@ -6821,10 +6764,10 @@
         <v>95.382056184685254</v>
       </c>
       <c r="T101" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="U101" s="2" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="I102" s="2" t="str">
         <f t="shared" si="37"/>
@@ -6885,10 +6828,10 @@
         <v>95.382056184685254</v>
       </c>
       <c r="T102" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="U102" s="2" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="V102" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="24" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I103" s="25" t="str">
         <f t="shared" si="37"/>
@@ -6952,7 +6895,7 @@
         <v>13</v>
       </c>
       <c r="U103" s="25" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="V103" s="25" t="s">
         <v>15</v>
@@ -6967,7 +6910,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="24" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I104" s="25" t="str">
         <f t="shared" si="37"/>
@@ -7016,7 +6959,7 @@
         <v>13</v>
       </c>
       <c r="U104" s="25" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="V104" s="25" t="s">
         <v>15</v>
@@ -7050,60 +6993,60 @@
       <c r="G106" s="20">
         <v>1</v>
       </c>
-      <c r="H106" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I106" s="2" t="str">
+      <c r="H106" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I106" s="25" t="str">
         <f xml:space="preserve"> "VGG19"</f>
         <v>VGG19</v>
       </c>
-      <c r="J106" s="2" t="str">
+      <c r="J106" s="25" t="str">
         <f t="shared" ref="J106:J111" si="40" xml:space="preserve"> "MNIST"</f>
         <v>MNIST</v>
       </c>
-      <c r="K106" s="2" t="str">
+      <c r="K106" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L106" s="2">
+      <c r="L106" s="25">
         <v>10</v>
       </c>
-      <c r="M106" s="2" t="str">
+      <c r="M106" s="25" t="str">
         <f xml:space="preserve"> "Linear"</f>
         <v>Linear</v>
       </c>
-      <c r="N106" s="2" t="s">
+      <c r="N106" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O106" s="2" t="b">
+      <c r="O106" s="25" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
-      <c r="P106" s="2" t="str">
+      <c r="P106" s="25" t="str">
         <f>"(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (10)</v>
       </c>
-      <c r="Q106" s="10">
+      <c r="Q106" s="26">
         <f>92323850</f>
         <v>92323850</v>
       </c>
-      <c r="R106" s="10">
+      <c r="R106" s="26">
         <f>112348234</f>
         <v>112348234</v>
       </c>
-      <c r="S106" s="2" t="s">
+      <c r="S106" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="T106" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U106" s="2" t="s">
+      <c r="T106" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U106" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V106" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W106" s="2" t="s">
+      <c r="V106" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W106" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7112,62 +7055,62 @@
       <c r="G107" s="20">
         <v>1</v>
       </c>
-      <c r="H107" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="I107" s="2" t="str">
+      <c r="H107" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I107" s="25" t="str">
         <f t="shared" ref="I107:I111" si="41" xml:space="preserve"> "VGG19"</f>
         <v>VGG19</v>
       </c>
-      <c r="J107" s="2" t="str">
+      <c r="J107" s="25" t="str">
         <f t="shared" si="40"/>
         <v>MNIST</v>
       </c>
-      <c r="K107" s="2" t="str">
+      <c r="K107" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L107" s="2">
+      <c r="L107" s="25">
         <v>10</v>
       </c>
-      <c r="M107" s="2" t="str">
+      <c r="M107" s="25" t="str">
         <f xml:space="preserve"> "TCL + TRL"</f>
         <v>TCL + TRL</v>
       </c>
-      <c r="N107" s="2" t="str">
+      <c r="N107" s="25" t="str">
         <f>"tcl:: (350,4,4), trl:: (150,1,1,10)"</f>
         <v>tcl:: (350,4,4), trl:: (150,1,1,10)</v>
       </c>
-      <c r="O107" s="2" t="b">
+      <c r="O107" s="25" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
-      <c r="P107" s="2" t="str">
+      <c r="P107" s="25" t="str">
         <f>"(512,6,6) --&gt; (350,4,4) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (350,4,4) --&gt; (10)</v>
       </c>
-      <c r="Q107" s="10">
+      <c r="Q107" s="26">
         <f>179248 + 54108</f>
         <v>233356</v>
       </c>
-      <c r="R107" s="10">
+      <c r="R107" s="26">
         <f xml:space="preserve"> R106 - Q106 + Q107</f>
         <v>20257740</v>
       </c>
-      <c r="S107" s="2">
+      <c r="S107" s="25">
         <f xml:space="preserve"> (1-(Q107/Q106))*100</f>
         <v>99.74724190986403</v>
       </c>
-      <c r="T107" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U107" s="2" t="s">
+      <c r="T107" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U107" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V107" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W107" s="2" t="s">
+      <c r="V107" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W107" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7176,62 +7119,62 @@
       <c r="G108" s="20">
         <v>1</v>
       </c>
-      <c r="H108" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I108" s="2" t="str">
+      <c r="H108" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I108" s="25" t="str">
         <f t="shared" si="41"/>
         <v>VGG19</v>
       </c>
-      <c r="J108" s="2" t="str">
+      <c r="J108" s="25" t="str">
         <f t="shared" si="40"/>
         <v>MNIST</v>
       </c>
-      <c r="K108" s="2" t="str">
+      <c r="K108" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L108" s="2">
+      <c r="L108" s="25">
         <v>10</v>
       </c>
-      <c r="M108" s="2" t="str">
+      <c r="M108" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N108" s="2" t="str">
+      <c r="N108" s="25" t="str">
         <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)"</f>
         <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)</v>
       </c>
-      <c r="O108" s="2" t="str">
+      <c r="O108" s="25" t="str">
         <f xml:space="preserve"> "(2,2,2)-type1"</f>
         <v>(2,2,2)-type1</v>
       </c>
-      <c r="P108" s="2" t="str">
+      <c r="P108" s="25" t="str">
         <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q108" s="10">
+      <c r="Q108" s="26">
         <f>25618 + 5607</f>
         <v>31225</v>
       </c>
-      <c r="R108" s="10">
+      <c r="R108" s="26">
         <f>R107 -Q107 + Q108</f>
         <v>20055609</v>
       </c>
-      <c r="S108" s="2">
+      <c r="S108" s="25">
         <f xml:space="preserve"> (1-(Q108/Q106))*100</f>
         <v>99.966178836779434</v>
       </c>
-      <c r="T108" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U108" s="2" t="s">
+      <c r="T108" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U108" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V108" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W108" s="2" t="s">
+      <c r="V108" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W108" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7240,62 +7183,62 @@
       <c r="G109" s="20">
         <v>1</v>
       </c>
-      <c r="H109" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I109" s="2" t="str">
+      <c r="H109" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I109" s="25" t="str">
         <f t="shared" si="41"/>
         <v>VGG19</v>
       </c>
-      <c r="J109" s="2" t="str">
+      <c r="J109" s="25" t="str">
         <f t="shared" si="40"/>
         <v>MNIST</v>
       </c>
-      <c r="K109" s="2" t="str">
+      <c r="K109" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L109" s="2">
+      <c r="L109" s="25">
         <v>10</v>
       </c>
-      <c r="M109" s="2" t="str">
+      <c r="M109" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N109" s="2" t="str">
+      <c r="N109" s="25" t="str">
         <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)"</f>
         <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)</v>
       </c>
-      <c r="O109" s="2" t="str">
+      <c r="O109" s="25" t="str">
         <f xml:space="preserve"> "(2,2,2)-type2"</f>
         <v>(2,2,2)-type2</v>
       </c>
-      <c r="P109" s="2" t="str">
+      <c r="P109" s="25" t="str">
         <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q109" s="10">
+      <c r="Q109" s="26">
         <f>25618 + 5607</f>
         <v>31225</v>
       </c>
-      <c r="R109" s="10">
+      <c r="R109" s="26">
         <f xml:space="preserve"> R108 - Q108 + Q109</f>
         <v>20055609</v>
       </c>
-      <c r="S109" s="2">
+      <c r="S109" s="25">
         <f xml:space="preserve"> (1-(Q109/Q106))*100</f>
         <v>99.966178836779434</v>
       </c>
-      <c r="T109" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U109" s="2" t="s">
+      <c r="T109" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U109" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V109" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W109" s="2" t="s">
+      <c r="V109" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W109" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7304,62 +7247,62 @@
       <c r="G110" s="20">
         <v>1</v>
       </c>
-      <c r="H110" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I110" s="2" t="str">
+      <c r="H110" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I110" s="25" t="str">
         <f t="shared" si="41"/>
         <v>VGG19</v>
       </c>
-      <c r="J110" s="2" t="str">
+      <c r="J110" s="25" t="str">
         <f t="shared" si="40"/>
         <v>MNIST</v>
       </c>
-      <c r="K110" s="2" t="str">
+      <c r="K110" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L110" s="2">
+      <c r="L110" s="25">
         <v>10</v>
       </c>
-      <c r="M110" s="2" t="str">
+      <c r="M110" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N110" s="2" t="str">
+      <c r="N110" s="25" t="str">
         <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)"</f>
         <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)</v>
       </c>
-      <c r="O110" s="2" t="str">
+      <c r="O110" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type1"</f>
         <v>(8,2,2)-type1</v>
       </c>
-      <c r="P110" s="2" t="str">
+      <c r="P110" s="25" t="str">
         <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q110" s="10">
+      <c r="Q110" s="26">
         <f>2592 + 608</f>
         <v>3200</v>
       </c>
-      <c r="R110" s="10">
+      <c r="R110" s="26">
         <f>R109 -Q109+ Q110</f>
         <v>20027584</v>
       </c>
-      <c r="S110" s="2">
+      <c r="S110" s="25">
         <f xml:space="preserve"> (1-(Q110/Q106))*100</f>
         <v>99.996533940038248</v>
       </c>
-      <c r="T110" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U110" s="2" t="s">
+      <c r="T110" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U110" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V110" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W110" s="2" t="s">
+      <c r="V110" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W110" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7368,62 +7311,62 @@
       <c r="G111" s="20">
         <v>1</v>
       </c>
-      <c r="H111" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="I111" s="2" t="str">
+      <c r="H111" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I111" s="25" t="str">
         <f t="shared" si="41"/>
         <v>VGG19</v>
       </c>
-      <c r="J111" s="2" t="str">
+      <c r="J111" s="25" t="str">
         <f t="shared" si="40"/>
         <v>MNIST</v>
       </c>
-      <c r="K111" s="2" t="str">
+      <c r="K111" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L111" s="2">
+      <c r="L111" s="25">
         <v>10</v>
       </c>
-      <c r="M111" s="2" t="str">
+      <c r="M111" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N111" s="2" t="str">
+      <c r="N111" s="25" t="str">
         <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)"</f>
         <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)</v>
       </c>
-      <c r="O111" s="2" t="str">
+      <c r="O111" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type2"</f>
         <v>(8,2,2)-type2</v>
       </c>
-      <c r="P111" s="2" t="str">
+      <c r="P111" s="25" t="str">
         <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q111" s="10">
+      <c r="Q111" s="26">
         <f>2592 + 608</f>
         <v>3200</v>
       </c>
-      <c r="R111" s="10">
+      <c r="R111" s="26">
         <f t="shared" ref="R111" si="42" xml:space="preserve"> R110 - Q110 + Q111</f>
         <v>20027584</v>
       </c>
-      <c r="S111" s="2">
+      <c r="S111" s="25">
         <f xml:space="preserve"> (1-(Q111/Q106))*100</f>
         <v>99.996533940038248</v>
       </c>
-      <c r="T111" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U111" s="2" t="s">
+      <c r="T111" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U111" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V111" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W111" s="2" t="s">
+      <c r="V111" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W111" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7452,60 +7395,60 @@
       <c r="G113" s="20">
         <v>1</v>
       </c>
-      <c r="H113" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I113" s="2" t="str">
+      <c r="H113" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I113" s="25" t="str">
         <f xml:space="preserve"> "VGG19"</f>
         <v>VGG19</v>
       </c>
-      <c r="J113" s="2" t="str">
+      <c r="J113" s="25" t="str">
         <f xml:space="preserve"> "CIFAR10"</f>
         <v>CIFAR10</v>
       </c>
-      <c r="K113" s="2" t="str">
+      <c r="K113" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L113" s="2">
+      <c r="L113" s="25">
         <v>10</v>
       </c>
-      <c r="M113" s="2" t="str">
+      <c r="M113" s="25" t="str">
         <f xml:space="preserve"> "Linear"</f>
         <v>Linear</v>
       </c>
-      <c r="N113" s="2" t="s">
+      <c r="N113" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O113" s="2" t="b">
+      <c r="O113" s="25" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
-      <c r="P113" s="2" t="str">
+      <c r="P113" s="25" t="str">
         <f>"(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (10)</v>
       </c>
-      <c r="Q113" s="10">
+      <c r="Q113" s="26">
         <f>92323850</f>
         <v>92323850</v>
       </c>
-      <c r="R113" s="10">
+      <c r="R113" s="26">
         <f>112348234</f>
         <v>112348234</v>
       </c>
-      <c r="S113" s="2" t="s">
+      <c r="S113" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="T113" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U113" s="2" t="s">
+      <c r="T113" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U113" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V113" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W113" s="2" t="s">
+      <c r="V113" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W113" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7514,62 +7457,62 @@
       <c r="G114" s="20">
         <v>1</v>
       </c>
-      <c r="H114" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I114" s="2" t="str">
+      <c r="H114" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I114" s="25" t="str">
         <f t="shared" ref="I114:I118" si="43" xml:space="preserve"> "VGG19"</f>
         <v>VGG19</v>
       </c>
-      <c r="J114" s="2" t="str">
+      <c r="J114" s="25" t="str">
         <f t="shared" ref="J114:J118" si="44" xml:space="preserve"> "CIFAR10"</f>
         <v>CIFAR10</v>
       </c>
-      <c r="K114" s="2" t="str">
+      <c r="K114" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L114" s="2">
+      <c r="L114" s="25">
         <v>10</v>
       </c>
-      <c r="M114" s="2" t="str">
+      <c r="M114" s="25" t="str">
         <f xml:space="preserve"> "TCL + TRL"</f>
         <v>TCL + TRL</v>
       </c>
-      <c r="N114" s="2" t="str">
+      <c r="N114" s="25" t="str">
         <f>"tcl:: (350,4,4), trl:: (150,1,1,10)"</f>
         <v>tcl:: (350,4,4), trl:: (150,1,1,10)</v>
       </c>
-      <c r="O114" s="2" t="b">
+      <c r="O114" s="25" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
-      <c r="P114" s="2" t="str">
+      <c r="P114" s="25" t="str">
         <f>"(512,6,6) --&gt; (350,4,4) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (350,4,4) --&gt; (10)</v>
       </c>
-      <c r="Q114" s="10">
+      <c r="Q114" s="26">
         <f>179248 + 54108</f>
         <v>233356</v>
       </c>
-      <c r="R114" s="10">
+      <c r="R114" s="26">
         <f xml:space="preserve"> R113 - Q113 + Q114</f>
         <v>20257740</v>
       </c>
-      <c r="S114" s="2">
+      <c r="S114" s="25">
         <f xml:space="preserve"> (1-(Q114/Q113))*100</f>
         <v>99.74724190986403</v>
       </c>
-      <c r="T114" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U114" s="2" t="s">
+      <c r="T114" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U114" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V114" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W114" s="2" t="s">
+      <c r="V114" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W114" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7578,62 +7521,62 @@
       <c r="G115" s="20">
         <v>1</v>
       </c>
-      <c r="H115" s="5" t="s">
+      <c r="H115" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="I115" s="2" t="str">
+      <c r="I115" s="25" t="str">
         <f t="shared" si="43"/>
         <v>VGG19</v>
       </c>
-      <c r="J115" s="2" t="str">
+      <c r="J115" s="25" t="str">
         <f t="shared" si="44"/>
         <v>CIFAR10</v>
       </c>
-      <c r="K115" s="2" t="str">
+      <c r="K115" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L115" s="2">
+      <c r="L115" s="25">
         <v>10</v>
       </c>
-      <c r="M115" s="2" t="str">
+      <c r="M115" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N115" s="2" t="str">
+      <c r="N115" s="25" t="str">
         <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)"</f>
         <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)</v>
       </c>
-      <c r="O115" s="2" t="str">
+      <c r="O115" s="25" t="str">
         <f xml:space="preserve"> "(2,2,2)-type1"</f>
         <v>(2,2,2)-type1</v>
       </c>
-      <c r="P115" s="2" t="str">
+      <c r="P115" s="25" t="str">
         <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q115" s="10">
+      <c r="Q115" s="26">
         <f>25618 + 5607</f>
         <v>31225</v>
       </c>
-      <c r="R115" s="10">
+      <c r="R115" s="26">
         <f>R114 -Q114 + Q115</f>
         <v>20055609</v>
       </c>
-      <c r="S115" s="2">
+      <c r="S115" s="25">
         <f xml:space="preserve"> (1-(Q115/Q113))*100</f>
         <v>99.966178836779434</v>
       </c>
-      <c r="T115" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U115" s="2" t="s">
+      <c r="T115" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U115" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V115" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W115" s="2" t="s">
+      <c r="V115" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W115" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7642,62 +7585,62 @@
       <c r="G116" s="20">
         <v>1</v>
       </c>
-      <c r="H116" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I116" s="2" t="str">
+      <c r="H116" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I116" s="25" t="str">
         <f t="shared" si="43"/>
         <v>VGG19</v>
       </c>
-      <c r="J116" s="2" t="str">
+      <c r="J116" s="25" t="str">
         <f t="shared" si="44"/>
         <v>CIFAR10</v>
       </c>
-      <c r="K116" s="2" t="str">
+      <c r="K116" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L116" s="2">
+      <c r="L116" s="25">
         <v>10</v>
       </c>
-      <c r="M116" s="2" t="str">
+      <c r="M116" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N116" s="2" t="str">
+      <c r="N116" s="25" t="str">
         <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)"</f>
         <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)</v>
       </c>
-      <c r="O116" s="2" t="str">
+      <c r="O116" s="25" t="str">
         <f xml:space="preserve"> "(2,2,2)-type2"</f>
         <v>(2,2,2)-type2</v>
       </c>
-      <c r="P116" s="2" t="str">
+      <c r="P116" s="25" t="str">
         <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q116" s="10">
+      <c r="Q116" s="26">
         <f>25618 + 5607</f>
         <v>31225</v>
       </c>
-      <c r="R116" s="10">
+      <c r="R116" s="26">
         <f xml:space="preserve"> R115 - Q115 + Q116</f>
         <v>20055609</v>
       </c>
-      <c r="S116" s="2">
+      <c r="S116" s="25">
         <f xml:space="preserve"> (1-(Q116/Q113))*100</f>
         <v>99.966178836779434</v>
       </c>
-      <c r="T116" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U116" s="2" t="s">
+      <c r="T116" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U116" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V116" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W116" s="2" t="s">
+      <c r="V116" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W116" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7706,62 +7649,62 @@
       <c r="G117" s="20">
         <v>1</v>
       </c>
-      <c r="H117" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="I117" s="2" t="str">
+      <c r="H117" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I117" s="25" t="str">
         <f t="shared" si="43"/>
         <v>VGG19</v>
       </c>
-      <c r="J117" s="2" t="str">
+      <c r="J117" s="25" t="str">
         <f t="shared" si="44"/>
         <v>CIFAR10</v>
       </c>
-      <c r="K117" s="2" t="str">
+      <c r="K117" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L117" s="2">
+      <c r="L117" s="25">
         <v>10</v>
       </c>
-      <c r="M117" s="2" t="str">
+      <c r="M117" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N117" s="2" t="str">
+      <c r="N117" s="25" t="str">
         <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)"</f>
         <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)</v>
       </c>
-      <c r="O117" s="2" t="str">
+      <c r="O117" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type1"</f>
         <v>(8,2,2)-type1</v>
       </c>
-      <c r="P117" s="2" t="str">
+      <c r="P117" s="25" t="str">
         <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q117" s="10">
+      <c r="Q117" s="26">
         <f>2592 + 608</f>
         <v>3200</v>
       </c>
-      <c r="R117" s="10">
+      <c r="R117" s="26">
         <f>R116 -Q116+ Q117</f>
         <v>20027584</v>
       </c>
-      <c r="S117" s="2">
+      <c r="S117" s="25">
         <f xml:space="preserve"> (1-(Q117/Q113))*100</f>
         <v>99.996533940038248</v>
       </c>
-      <c r="T117" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U117" s="2" t="s">
+      <c r="T117" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U117" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V117" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W117" s="2" t="s">
+      <c r="V117" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W117" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7770,62 +7713,62 @@
       <c r="G118" s="20">
         <v>1</v>
       </c>
-      <c r="H118" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I118" s="2" t="str">
+      <c r="H118" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I118" s="25" t="str">
         <f t="shared" si="43"/>
         <v>VGG19</v>
       </c>
-      <c r="J118" s="2" t="str">
+      <c r="J118" s="25" t="str">
         <f t="shared" si="44"/>
         <v>CIFAR10</v>
       </c>
-      <c r="K118" s="2" t="str">
+      <c r="K118" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L118" s="2">
+      <c r="L118" s="25">
         <v>10</v>
       </c>
-      <c r="M118" s="2" t="str">
+      <c r="M118" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N118" s="2" t="str">
+      <c r="N118" s="25" t="str">
         <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)"</f>
         <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)</v>
       </c>
-      <c r="O118" s="2" t="str">
+      <c r="O118" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type2"</f>
         <v>(8,2,2)-type2</v>
       </c>
-      <c r="P118" s="2" t="str">
+      <c r="P118" s="25" t="str">
         <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)"</f>
         <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)</v>
       </c>
-      <c r="Q118" s="10">
+      <c r="Q118" s="26">
         <f>2592 + 608</f>
         <v>3200</v>
       </c>
-      <c r="R118" s="10">
+      <c r="R118" s="26">
         <f t="shared" ref="R118" si="45" xml:space="preserve"> R117 - Q117 + Q118</f>
         <v>20027584</v>
       </c>
-      <c r="S118" s="2">
+      <c r="S118" s="25">
         <f xml:space="preserve"> (1-(Q118/Q113))*100</f>
         <v>99.996533940038248</v>
       </c>
-      <c r="T118" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U118" s="2" t="s">
+      <c r="T118" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U118" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V118" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W118" s="2" t="s">
+      <c r="V118" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W118" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7855,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I120" s="2" t="str">
         <f xml:space="preserve"> "VGG19"</f>
@@ -7917,7 +7860,7 @@
         <v>1</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I121" s="2" t="str">
         <f t="shared" ref="I121:I125" si="46" xml:space="preserve"> "VGG19"</f>
@@ -7981,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I122" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8045,7 +7988,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I123" s="2" t="str">
         <f t="shared" si="46"/>
@@ -8108,62 +8051,62 @@
       <c r="G124" s="20">
         <v>1</v>
       </c>
-      <c r="H124" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I124" s="2" t="str">
+      <c r="H124" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I124" s="25" t="str">
         <f t="shared" si="46"/>
         <v>VGG19</v>
       </c>
-      <c r="J124" s="2" t="str">
+      <c r="J124" s="25" t="str">
         <f t="shared" si="47"/>
         <v>TINY</v>
       </c>
-      <c r="K124" s="2" t="str">
+      <c r="K124" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L124" s="2">
+      <c r="L124" s="25">
         <v>200</v>
       </c>
-      <c r="M124" s="2" t="str">
+      <c r="M124" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N124" s="2" t="str">
+      <c r="N124" s="25" t="str">
         <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,200)"</f>
         <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,200)</v>
       </c>
-      <c r="O124" s="2" t="str">
+      <c r="O124" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type1"</f>
         <v>(8,2,2)-type1</v>
       </c>
-      <c r="P124" s="2" t="str">
+      <c r="P124" s="25" t="str">
         <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (200)"</f>
         <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (200)</v>
       </c>
-      <c r="Q124" s="10">
+      <c r="Q124" s="26">
         <f>2592 + 42408</f>
         <v>45000</v>
       </c>
-      <c r="R124" s="10">
+      <c r="R124" s="26">
         <f>R123 -Q123+ Q124</f>
         <v>20069384</v>
       </c>
-      <c r="S124" s="2">
+      <c r="S124" s="25">
         <f xml:space="preserve"> (1-(Q124/Q120))*100</f>
         <v>99.951666060165238</v>
       </c>
-      <c r="T124" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U124" s="2" t="s">
+      <c r="T124" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U124" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V124" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W124" s="2" t="s">
+      <c r="V124" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W124" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8172,62 +8115,62 @@
       <c r="G125" s="20">
         <v>1</v>
       </c>
-      <c r="H125" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I125" s="2" t="str">
+      <c r="H125" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I125" s="25" t="str">
         <f t="shared" si="46"/>
         <v>VGG19</v>
       </c>
-      <c r="J125" s="2" t="str">
+      <c r="J125" s="25" t="str">
         <f t="shared" si="47"/>
         <v>TINY</v>
       </c>
-      <c r="K125" s="2" t="str">
+      <c r="K125" s="25" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L125" s="2">
+      <c r="L125" s="25">
         <v>200</v>
       </c>
-      <c r="M125" s="2" t="str">
+      <c r="M125" s="25" t="str">
         <f>"Reshape+TCL+TRL"</f>
         <v>Reshape+TCL+TRL</v>
       </c>
-      <c r="N125" s="2" t="str">
+      <c r="N125" s="25" t="str">
         <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,200)"</f>
         <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,200)</v>
       </c>
-      <c r="O125" s="2" t="str">
+      <c r="O125" s="25" t="str">
         <f xml:space="preserve"> "(8,2,2)-type2"</f>
         <v>(8,2,2)-type2</v>
       </c>
-      <c r="P125" s="2" t="str">
+      <c r="P125" s="25" t="str">
         <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (200)"</f>
         <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (200)</v>
       </c>
-      <c r="Q125" s="10">
+      <c r="Q125" s="26">
         <f>2592 + 42408</f>
         <v>45000</v>
       </c>
-      <c r="R125" s="10">
+      <c r="R125" s="26">
         <f t="shared" ref="R125" si="48" xml:space="preserve"> R124 - Q124 + Q125</f>
         <v>20069384</v>
       </c>
-      <c r="S125" s="2">
+      <c r="S125" s="25">
         <f xml:space="preserve"> (1-(Q125/Q120))*100</f>
         <v>99.951666060165238</v>
       </c>
-      <c r="T125" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U125" s="2" t="s">
+      <c r="T125" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="U125" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V125" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W125" s="2" t="s">
+      <c r="V125" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="W125" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8255,42 +8198,42 @@
       <c r="F127" s="15"/>
       <c r="G127" s="16"/>
       <c r="H127" s="5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="128" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F128" s="15"/>
       <c r="G128" s="16"/>
       <c r="H128" s="5" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="129" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F129" s="15"/>
       <c r="G129" s="16"/>
       <c r="H129" s="5" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="130" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F130" s="15"/>
       <c r="G130" s="16"/>
       <c r="H130" s="5" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="131" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F131" s="15"/>
       <c r="G131" s="16"/>
       <c r="H131" s="5" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="132" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F132" s="15"/>
       <c r="G132" s="16"/>
       <c r="H132" s="5" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133" spans="6:8" ht="21.75" thickTop="1" x14ac:dyDescent="0.35">

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="126">
   <si>
     <t>Dataset</t>
   </si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t>088</t>
+  </si>
+  <si>
+    <t>25 Epoch</t>
   </si>
 </sst>
 </file>
@@ -7792,7 +7795,7 @@
       <c r="V119" s="17"/>
       <c r="W119" s="17"/>
     </row>
-    <row r="120" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F120" s="15"/>
       <c r="G120" s="19">
         <v>1</v>
@@ -7816,8 +7819,8 @@
         <v>200</v>
       </c>
       <c r="M120" s="2" t="str">
-        <f xml:space="preserve"> "Linear"</f>
-        <v>Linear</v>
+        <f xml:space="preserve"> "avgpool+Linear"</f>
+        <v>avgpool+Linear</v>
       </c>
       <c r="N120" s="2" t="s">
         <v>9</v>
@@ -7842,19 +7845,19 @@
         <v>18</v>
       </c>
       <c r="T120" s="2" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="U120" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W120" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="121" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="121" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F121" s="15"/>
       <c r="G121" s="19">
         <v>1</v>
@@ -7906,19 +7909,19 @@
         <v>99.675887636693744</v>
       </c>
       <c r="T121" s="2" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="U121" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W121" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="122" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="122" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F122" s="15"/>
       <c r="G122" s="19">
         <v>1</v>
@@ -7970,19 +7973,19 @@
         <v>99.913401691129366</v>
       </c>
       <c r="T122" s="2" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="U122" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W122" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="123" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F123" s="15"/>
       <c r="G123" s="19">
         <v>1</v>
@@ -8034,16 +8037,16 @@
         <v>99.913401691129366</v>
       </c>
       <c r="T123" s="2" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="U123" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W123" s="2" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -399,7 +399,7 @@
     <t>088</t>
   </si>
   <si>
-    <t>25 Epoch</t>
+    <t>35 Epoch</t>
   </si>
 </sst>
 </file>
@@ -7797,7 +7797,7 @@
     </row>
     <row r="120" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F120" s="15"/>
-      <c r="G120" s="19">
+      <c r="G120" s="23">
         <v>1</v>
       </c>
       <c r="H120" s="5" t="s">
@@ -7819,8 +7819,8 @@
         <v>200</v>
       </c>
       <c r="M120" s="2" t="str">
-        <f xml:space="preserve"> "avgpool+Linear"</f>
-        <v>avgpool+Linear</v>
+        <f xml:space="preserve"> "Linear"</f>
+        <v>Linear</v>
       </c>
       <c r="N120" s="2" t="s">
         <v>9</v>
@@ -7885,28 +7885,28 @@
         <v>TCL + TRL</v>
       </c>
       <c r="N121" s="2" t="str">
-        <f>"tcl:: (350,4,4), trl:: (150,1,1,200)"</f>
-        <v>tcl:: (350,4,4), trl:: (150,1,1,200)</v>
+        <f>"tcl:: (512,6,6), trl:: (512,6,6,200)"</f>
+        <v>tcl:: (512,6,6), trl:: (512,6,6,200)</v>
       </c>
       <c r="O121" s="2" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
       <c r="P121" s="2" t="str">
-        <f>"(512,6,6) --&gt; (350,4,4) --&gt; (200)"</f>
-        <v>(512,6,6) --&gt; (350,4,4) --&gt; (200)</v>
+        <f>"(512,6,6) --&gt; (512,6,6) --&gt; (200)"</f>
+        <v>(512,6,6) --&gt; (512,6,6) --&gt; (200)</v>
       </c>
       <c r="Q121" s="10">
-        <f>179248 + 122508</f>
-        <v>301756</v>
+        <f>4250832</f>
+        <v>4250832</v>
       </c>
       <c r="R121" s="10">
         <f xml:space="preserve"> R120 - Q120 + Q121</f>
-        <v>20326140</v>
+        <v>24275216</v>
       </c>
       <c r="S121" s="2">
         <f xml:space="preserve"> (1-(Q121/Q120))*100</f>
-        <v>99.675887636693744</v>
+        <v>95.43423426365068</v>
       </c>
       <c r="T121" s="2" t="s">
         <v>125</v>
@@ -7945,12 +7945,12 @@
         <v>200</v>
       </c>
       <c r="M122" s="2" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N122" s="2" t="str">
-        <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,200)"</f>
-        <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,200)</v>
+        <f>"tcl::(2,2,2,512,1,1), trl:: (1,1,1,512,1,1,200)"</f>
+        <v>tcl::(2,2,2,512,1,1), trl:: (1,1,1,512,1,1,200)</v>
       </c>
       <c r="O122" s="2" t="str">
         <f xml:space="preserve"> "(2,2,2)-type1"</f>
@@ -7961,16 +7961,16 @@
         <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (200)</v>
       </c>
       <c r="Q122" s="10">
-        <f>25618 + 55007</f>
-        <v>80625</v>
+        <f>666714</f>
+        <v>666714</v>
       </c>
       <c r="R122" s="10">
         <f>R121 -Q121 + Q122</f>
-        <v>20105009</v>
+        <v>20691098</v>
       </c>
       <c r="S122" s="2">
         <f xml:space="preserve"> (1-(Q122/Q120))*100</f>
-        <v>99.913401691129366</v>
+        <v>99.283890791933345</v>
       </c>
       <c r="T122" s="2" t="s">
         <v>125</v>
@@ -8009,12 +8009,12 @@
         <v>200</v>
       </c>
       <c r="M123" s="2" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N123" s="2" t="str">
-        <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,200)"</f>
-        <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,200)</v>
+        <f>"tcl::(2,2,2,512,1,1), trl:: (1,1,1,512,1,1,200)"</f>
+        <v>tcl::(2,2,2,512,1,1), trl:: (1,1,1,512,1,1,200)</v>
       </c>
       <c r="O123" s="2" t="str">
         <f xml:space="preserve"> "(2,2,2)-type2"</f>
@@ -8025,16 +8025,16 @@
         <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (200)</v>
       </c>
       <c r="Q123" s="10">
-        <f>25618 + 55007</f>
-        <v>80625</v>
+        <f>666714</f>
+        <v>666714</v>
       </c>
       <c r="R123" s="10">
         <f xml:space="preserve"> R122 - Q122 + Q123</f>
-        <v>20105009</v>
+        <v>20691098</v>
       </c>
       <c r="S123" s="2">
         <f xml:space="preserve"> (1-(Q123/Q120))*100</f>
-        <v>99.913401691129366</v>
+        <v>99.283890791933345</v>
       </c>
       <c r="T123" s="2" t="s">
         <v>125</v>

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -1,28 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AAE1C29-907E-475F-BB12-420AFAC48D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Plans" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Plans'!$G$1:$G$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Plans'!$G$1:$G$108</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="132">
   <si>
     <t>Dataset</t>
   </si>
@@ -351,9 +362,6 @@
     <t>0 Epoch</t>
   </si>
   <si>
-    <t>40 Epoch</t>
-  </si>
-  <si>
     <t>10 Epoch</t>
   </si>
   <si>
@@ -369,9 +377,6 @@
     <t>15 Epoch</t>
   </si>
   <si>
-    <t>null</t>
-  </si>
-  <si>
     <t>081</t>
   </si>
   <si>
@@ -399,13 +404,37 @@
     <t>088</t>
   </si>
   <si>
-    <t>35 Epoch</t>
+    <t>Test top_1</t>
+  </si>
+  <si>
+    <t>Train top_1</t>
+  </si>
+  <si>
+    <t>Train top5</t>
+  </si>
+  <si>
+    <t>Test top_5</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>TINY</t>
+  </si>
+  <si>
+    <t>Reshape+Dropout+TCL+TRL</t>
+  </si>
+  <si>
+    <t>VGG19</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -438,14 +467,13 @@
     </font>
     <font>
       <sz val="16"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FF92D050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF92D050"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -595,7 +623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -642,37 +670,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -954,33 +964,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:W134"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:AA108"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="9.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" style="2" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" style="2"/>
-    <col min="7" max="7" width="16.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="31.28515625" style="6" customWidth="1"/>
-    <col min="9" max="12" width="18.42578125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.5703125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="65.140625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="26.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="2"/>
+    <col min="2" max="2" width="9.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="2" customWidth="1"/>
+    <col min="5" max="6" width="9.109375" style="2"/>
+    <col min="7" max="7" width="16.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="31.33203125" style="6" customWidth="1"/>
+    <col min="9" max="12" width="18.44140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.5546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="65.109375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="26.44140625" style="2" customWidth="1"/>
     <col min="16" max="16" width="129" style="2" customWidth="1"/>
-    <col min="17" max="17" width="27.42578125" style="10" customWidth="1"/>
-    <col min="18" max="18" width="28.140625" style="10" customWidth="1"/>
-    <col min="19" max="19" width="36.42578125" style="2" customWidth="1"/>
-    <col min="20" max="21" width="18.28515625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="18.140625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="2"/>
+    <col min="17" max="17" width="27.44140625" style="10" customWidth="1"/>
+    <col min="18" max="18" width="28.109375" style="10" customWidth="1"/>
+    <col min="19" max="19" width="36.44140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="18.33203125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="18.109375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="25.109375" style="2" customWidth="1"/>
+    <col min="24" max="24" width="28.21875" style="2" customWidth="1"/>
+    <col min="25" max="25" width="22.77734375" style="2" customWidth="1"/>
+    <col min="26" max="26" width="20.33203125" style="2" customWidth="1"/>
+    <col min="27" max="27" width="15.44140625" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="21.75" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:27" ht="21.6" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C2" s="14" t="s">
         <v>26</v>
       </c>
@@ -988,7 +1002,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="s">
         <v>23</v>
@@ -998,25 +1012,25 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="12"/>
       <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="11"/>
       <c r="C5" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="2:23" s="1" customFormat="1" ht="43.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="1" customFormat="1" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="G6" s="4" t="s">
         <v>22</v>
       </c>
@@ -1068,10 +1082,22 @@
       <c r="W6" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F7" s="15"/>
-      <c r="G7" s="22">
+      <c r="G7" s="19">
         <v>1</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -1130,10 +1156,22 @@
       <c r="W7" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X7" s="2">
+        <v>0.98198336399999997</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0.99975001799999996</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.97259998299999995</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0.99930000299999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F8" s="15"/>
-      <c r="G8" s="23">
+      <c r="G8" s="20">
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -1194,10 +1232,22 @@
       <c r="W8" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X8" s="2">
+        <v>0.98870003200000001</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0.99983334499999998</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0.98759996900000002</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0.99989998300000005</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F9" s="15"/>
-      <c r="G9" s="23">
+      <c r="G9" s="20">
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
@@ -1258,10 +1308,22 @@
       <c r="W9" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X9" s="2">
+        <v>0.989050031</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0.99993336200000005</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.97999995900000003</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0.99969995</v>
+      </c>
+    </row>
+    <row r="10" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F10" s="15"/>
-      <c r="G10" s="23">
+      <c r="G10" s="20">
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -1322,10 +1384,22 @@
       <c r="W10" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X10" s="2">
+        <v>0.98465001600000002</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.99860000599999998</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0.96499997400000004</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>0.99789994999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F11" s="15"/>
-      <c r="G11" s="23">
+      <c r="G11" s="20">
         <v>1</v>
       </c>
       <c r="H11" s="5" t="s">
@@ -1386,10 +1460,22 @@
       <c r="W11" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X11" s="2">
+        <v>0.98884999799999995</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0.99993336200000005</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0.97810000200000002</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0.99959999300000002</v>
+      </c>
+    </row>
+    <row r="12" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F12" s="15"/>
-      <c r="G12" s="23">
+      <c r="G12" s="20">
         <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
@@ -1450,10 +1536,22 @@
       <c r="W12" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X12" s="2">
+        <v>0.98808336299999999</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0.99989998300000005</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0.98189997699999998</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0.99989998300000005</v>
+      </c>
+    </row>
+    <row r="13" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F13" s="15"/>
-      <c r="G13" s="23">
+      <c r="G13" s="20">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
@@ -1514,10 +1612,22 @@
       <c r="W13" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="2:23" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X13" s="2">
+        <v>0.98623335400000001</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0.99954998500000003</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0.98569995200000005</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0.99949997700000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:27" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F14" s="15"/>
-      <c r="G14" s="23">
+      <c r="G14" s="20">
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
@@ -1578,10 +1688,22 @@
       <c r="W14" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X14" s="2">
+        <v>0.98669999799999997</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0.99943333899999998</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0.97799998499999996</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0.99959999300000002</v>
+      </c>
+    </row>
+    <row r="15" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F15" s="15"/>
-      <c r="G15" s="23">
+      <c r="G15" s="20">
         <v>1</v>
       </c>
       <c r="H15" s="5" t="s">
@@ -1642,10 +1764,22 @@
       <c r="W15" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="2:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X15" s="2">
+        <v>0.98813337099999998</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0.99993336200000005</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.97859996599999999</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0.99969995</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F16" s="15"/>
-      <c r="G16" s="23">
+      <c r="G16" s="20">
         <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
@@ -1706,10 +1840,22 @@
       <c r="W16" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X16" s="2">
+        <v>0.98890000600000005</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0.99996668099999997</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.98129999599999995</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F17" s="15"/>
-      <c r="G17" s="23">
+      <c r="G17" s="20">
         <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
@@ -1770,10 +1916,22 @@
       <c r="W17" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X17" s="2">
+        <v>0.98605001000000003</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0.99956667399999999</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0.977499962</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0.99939995999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F18" s="15"/>
-      <c r="G18" s="23">
+      <c r="G18" s="20">
         <v>1</v>
       </c>
       <c r="H18" s="5" t="s">
@@ -1834,30 +1992,46 @@
       <c r="W18" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X18" s="2">
+        <v>0.98591667400000005</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0.99918335700000005</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0.98439997400000001</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0.998999953</v>
+      </c>
+    </row>
+    <row r="19" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F19" s="7"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-    </row>
-    <row r="20" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G19" s="17"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+    </row>
+    <row r="20" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F20" s="15"/>
-      <c r="G20" s="23">
+      <c r="G20" s="20">
         <v>1</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -1916,10 +2090,22 @@
       <c r="W20" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X20" s="2">
+        <v>0.91493999999999998</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0.99689996199999997</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0.90719997900000005</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0.99719995299999997</v>
+      </c>
+    </row>
+    <row r="21" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F21" s="15"/>
-      <c r="G21" s="23">
+      <c r="G21" s="20">
         <v>1</v>
       </c>
       <c r="H21" s="5" t="s">
@@ -1980,10 +2166,22 @@
       <c r="W21" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X21" s="2">
+        <v>0.93430000499999999</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0.99859994600000002</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0.91029995699999999</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>0.997799993</v>
+      </c>
+    </row>
+    <row r="22" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F22" s="15"/>
-      <c r="G22" s="23">
+      <c r="G22" s="20">
         <v>1</v>
       </c>
       <c r="H22" s="5" t="s">
@@ -2044,10 +2242,22 @@
       <c r="W22" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X22" s="2">
+        <v>0.93495994800000004</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0.99883997400000002</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0.92319995200000005</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0.99709999599999999</v>
+      </c>
+    </row>
+    <row r="23" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F23" s="15"/>
-      <c r="G23" s="23">
+      <c r="G23" s="20">
         <v>1</v>
       </c>
       <c r="H23" s="5" t="s">
@@ -2108,10 +2318,22 @@
       <c r="W23" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="24" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X23" s="2">
+        <v>0.90928000200000003</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>0.99437999700000002</v>
+      </c>
+      <c r="Z23" s="2">
+        <v>0.90410000099999999</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>0.99289995399999997</v>
+      </c>
+    </row>
+    <row r="24" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F24" s="15"/>
-      <c r="G24" s="23">
+      <c r="G24" s="20">
         <v>1</v>
       </c>
       <c r="H24" s="5" t="s">
@@ -2172,10 +2394,22 @@
       <c r="W24" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X24" s="2">
+        <v>0.938019991</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>0.99903994799999996</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>0.91789996600000001</v>
+      </c>
+      <c r="AA24" s="2">
+        <v>0.99799996599999996</v>
+      </c>
+    </row>
+    <row r="25" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F25" s="15"/>
-      <c r="G25" s="23">
+      <c r="G25" s="20">
         <v>1</v>
       </c>
       <c r="H25" s="5" t="s">
@@ -2236,10 +2470,22 @@
       <c r="W25" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X25" s="2">
+        <v>0.93711996099999995</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>0.99901998000000003</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>0.92589998200000001</v>
+      </c>
+      <c r="AA25" s="2">
+        <v>0.99839997300000005</v>
+      </c>
+    </row>
+    <row r="26" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F26" s="15"/>
-      <c r="G26" s="23">
+      <c r="G26" s="20">
         <v>1</v>
       </c>
       <c r="H26" s="5" t="s">
@@ -2276,11 +2522,11 @@
         <f>"(2048,6,6) --&gt; (2,2,2,1024,3,3) --&gt; (10)"</f>
         <v>(2048,6,6) --&gt; (2,2,2,1024,3,3) --&gt; (10)</v>
       </c>
-      <c r="Q26" s="21">
+      <c r="Q26" s="18">
         <f>20612</f>
         <v>20612</v>
       </c>
-      <c r="R26" s="21">
+      <c r="R26" s="18">
         <f t="shared" si="8"/>
         <v>23528644</v>
       </c>
@@ -2300,10 +2546,22 @@
       <c r="W26" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X26" s="2">
+        <v>0.92403995999999999</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>0.99661999899999998</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>0.90999996699999997</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>0.99469995499999997</v>
+      </c>
+    </row>
+    <row r="27" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F27" s="15"/>
-      <c r="G27" s="23">
+      <c r="G27" s="20">
         <v>1</v>
       </c>
       <c r="H27" s="5" t="s">
@@ -2364,10 +2622,22 @@
       <c r="W27" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X27" s="2">
+        <v>0.92245995999999997</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>0.99581998599999999</v>
+      </c>
+      <c r="Z27" s="2">
+        <v>0.91529995200000003</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>0.99509996199999995</v>
+      </c>
+    </row>
+    <row r="28" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F28" s="15"/>
-      <c r="G28" s="23">
+      <c r="G28" s="20">
         <v>1</v>
       </c>
       <c r="H28" s="5" t="s">
@@ -2428,10 +2698,22 @@
       <c r="W28" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X28" s="2">
+        <v>0.93926000600000004</v>
+      </c>
+      <c r="Y28" s="2">
+        <v>0.99908000200000002</v>
+      </c>
+      <c r="Z28" s="2">
+        <v>0.92269998799999997</v>
+      </c>
+      <c r="AA28" s="2">
+        <v>0.99829995599999999</v>
+      </c>
+    </row>
+    <row r="29" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F29" s="15"/>
-      <c r="G29" s="23">
+      <c r="G29" s="20">
         <v>1</v>
       </c>
       <c r="H29" s="5" t="s">
@@ -2492,10 +2774,22 @@
       <c r="W29" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="30" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X29" s="2">
+        <v>0.93831998100000003</v>
+      </c>
+      <c r="Y29" s="2">
+        <v>0.99908000200000002</v>
+      </c>
+      <c r="Z29" s="2">
+        <v>0.91949999299999996</v>
+      </c>
+      <c r="AA29" s="2">
+        <v>0.99839997300000005</v>
+      </c>
+    </row>
+    <row r="30" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F30" s="15"/>
-      <c r="G30" s="23">
+      <c r="G30" s="20">
         <v>1</v>
       </c>
       <c r="H30" s="5" t="s">
@@ -2532,11 +2826,11 @@
         <f>"(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (10)"</f>
         <v>(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (10)</v>
       </c>
-      <c r="Q30" s="21">
+      <c r="Q30" s="18">
         <f>1386</f>
         <v>1386</v>
       </c>
-      <c r="R30" s="21">
+      <c r="R30" s="18">
         <f t="shared" si="8"/>
         <v>23509418</v>
       </c>
@@ -2556,10 +2850,22 @@
       <c r="W30" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="31" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X30" s="2">
+        <v>0.92133998900000003</v>
+      </c>
+      <c r="Y30" s="2">
+        <v>0.99636000400000002</v>
+      </c>
+      <c r="Z30" s="2">
+        <v>0.904499948</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>0.99320000399999997</v>
+      </c>
+    </row>
+    <row r="31" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F31" s="15"/>
-      <c r="G31" s="23">
+      <c r="G31" s="20">
         <v>1</v>
       </c>
       <c r="H31" s="5" t="s">
@@ -2620,30 +2926,46 @@
       <c r="W31" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="32" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X31" s="2">
+        <v>0.92347997400000004</v>
+      </c>
+      <c r="Y31" s="2">
+        <v>0.99636000400000002</v>
+      </c>
+      <c r="Z31" s="2">
+        <v>0.89039999199999997</v>
+      </c>
+      <c r="AA31" s="2">
+        <v>0.99439996500000005</v>
+      </c>
+    </row>
+    <row r="32" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F32" s="7"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-    </row>
-    <row r="33" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G32" s="17"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="16"/>
+      <c r="Z32" s="16"/>
+      <c r="AA32" s="16"/>
+    </row>
+    <row r="33" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F33" s="15"/>
-      <c r="G33" s="23">
+      <c r="G33" s="20">
         <v>1</v>
       </c>
       <c r="H33" s="5" t="s">
@@ -2691,21 +3013,33 @@
         <v>18</v>
       </c>
       <c r="T33" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X33" s="2">
+        <v>0.87820994900000005</v>
+      </c>
+      <c r="Y33" s="2">
+        <v>0.98069000200000001</v>
+      </c>
+      <c r="Z33" s="2">
+        <v>0.75779998299999995</v>
+      </c>
+      <c r="AA33" s="2">
+        <v>0.90829998300000003</v>
+      </c>
+    </row>
+    <row r="34" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F34" s="15"/>
-      <c r="G34" s="23">
+      <c r="G34" s="20">
         <v>1</v>
       </c>
       <c r="H34" s="5" t="s">
@@ -2755,21 +3089,33 @@
         <v>73.006632397021519</v>
       </c>
       <c r="T34" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W34" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X34" s="2">
+        <v>0.96313995100000005</v>
+      </c>
+      <c r="Y34" s="2">
+        <v>0.99846994899999997</v>
+      </c>
+      <c r="Z34" s="2">
+        <v>0.80680000799999996</v>
+      </c>
+      <c r="AA34" s="2">
+        <v>0.93729996699999996</v>
+      </c>
+    </row>
+    <row r="35" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F35" s="15"/>
-      <c r="G35" s="23">
+      <c r="G35" s="20">
         <v>1</v>
       </c>
       <c r="H35" s="5" t="s">
@@ -2819,21 +3165,33 @@
         <v>84.071152463752384</v>
       </c>
       <c r="T35" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W35" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X35" s="2">
+        <v>0.96099996600000004</v>
+      </c>
+      <c r="Y35" s="2">
+        <v>0.99844998100000004</v>
+      </c>
+      <c r="Z35" s="2">
+        <v>0.81089997300000005</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>0.93809998000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F36" s="15"/>
-      <c r="G36" s="23">
+      <c r="G36" s="20">
         <v>1</v>
       </c>
       <c r="H36" s="5" t="s">
@@ -2883,21 +3241,33 @@
         <v>88.274383214203368</v>
       </c>
       <c r="T36" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W36" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U36" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X36" s="2">
+        <v>0.95857995699999998</v>
+      </c>
+      <c r="Y36" s="2">
+        <v>0.998249948</v>
+      </c>
+      <c r="Z36" s="2">
+        <v>0.81339997100000005</v>
+      </c>
+      <c r="AA36" s="2">
+        <v>0.94009995499999999</v>
+      </c>
+    </row>
+    <row r="37" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F37" s="15"/>
-      <c r="G37" s="23">
+      <c r="G37" s="20">
         <v>1</v>
       </c>
       <c r="H37" s="5" t="s">
@@ -2947,21 +3317,33 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W37" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U37" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X37" s="2">
+        <v>0.94349998199999996</v>
+      </c>
+      <c r="Y37" s="2">
+        <v>0.995469987</v>
+      </c>
+      <c r="Z37" s="2">
+        <v>0.81869995600000001</v>
+      </c>
+      <c r="AA37" s="2">
+        <v>0.94579994700000003</v>
+      </c>
+    </row>
+    <row r="38" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F38" s="15"/>
-      <c r="G38" s="23">
+      <c r="G38" s="20">
         <v>1</v>
       </c>
       <c r="H38" s="5" t="s">
@@ -3011,21 +3393,33 @@
         <v>95.578320606545603</v>
       </c>
       <c r="T38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W38" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X38" s="2">
+        <v>0.94514995800000001</v>
+      </c>
+      <c r="Y38" s="2">
+        <v>0.99605995400000003</v>
+      </c>
+      <c r="Z38" s="2">
+        <v>0.81949996899999999</v>
+      </c>
+      <c r="AA38" s="2">
+        <v>0.94329994900000003</v>
+      </c>
+    </row>
+    <row r="39" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F39" s="15"/>
-      <c r="G39" s="23">
+      <c r="G39" s="20">
         <v>1</v>
       </c>
       <c r="H39" s="5" t="s">
@@ -3075,21 +3469,33 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T39" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W39" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W39" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X39" s="2">
+        <v>0.92127996700000003</v>
+      </c>
+      <c r="Y39" s="2">
+        <v>0.98805999799999999</v>
+      </c>
+      <c r="Z39" s="2">
+        <v>0.82029998299999995</v>
+      </c>
+      <c r="AA39" s="2">
+        <v>0.945499957</v>
+      </c>
+    </row>
+    <row r="40" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F40" s="15"/>
-      <c r="G40" s="23">
+      <c r="G40" s="20">
         <v>1</v>
       </c>
       <c r="H40" s="5" t="s">
@@ -3139,21 +3545,33 @@
         <v>99.102035833932376</v>
       </c>
       <c r="T40" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W40" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X40" s="2">
+        <v>0.92683994800000002</v>
+      </c>
+      <c r="Y40" s="2">
+        <v>0.99030995399999999</v>
+      </c>
+      <c r="Z40" s="2">
+        <v>0.82739996900000001</v>
+      </c>
+      <c r="AA40" s="2">
+        <v>0.94499999300000004</v>
+      </c>
+    </row>
+    <row r="41" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F41" s="15"/>
-      <c r="G41" s="23">
+      <c r="G41" s="20">
         <v>1</v>
       </c>
       <c r="H41" s="5" t="s">
@@ -3203,21 +3621,33 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T41" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W41" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W41" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X41" s="2">
+        <v>0.91512000599999999</v>
+      </c>
+      <c r="Y41" s="2">
+        <v>0.986029983</v>
+      </c>
+      <c r="Z41" s="2">
+        <v>0.82649999900000004</v>
+      </c>
+      <c r="AA41" s="2">
+        <v>0.94879996799999999</v>
+      </c>
+    </row>
+    <row r="42" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F42" s="15"/>
-      <c r="G42" s="23">
+      <c r="G42" s="20">
         <v>1</v>
       </c>
       <c r="H42" s="5" t="s">
@@ -3267,21 +3697,33 @@
         <v>98.491272091036095</v>
       </c>
       <c r="T42" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W42" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X42" s="2">
+        <v>0.93201994899999996</v>
+      </c>
+      <c r="Y42" s="2">
+        <v>0.99160999100000002</v>
+      </c>
+      <c r="Z42" s="2">
+        <v>0.81929999600000003</v>
+      </c>
+      <c r="AA42" s="2">
+        <v>0.94629996999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F43" s="15"/>
-      <c r="G43" s="23">
+      <c r="G43" s="20">
         <v>1</v>
       </c>
       <c r="H43" s="5" t="s">
@@ -3318,11 +3760,11 @@
         <f>"(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (200)"</f>
         <v>(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (200)</v>
       </c>
-      <c r="Q43" s="21">
+      <c r="Q43" s="18">
         <f>91274</f>
         <v>91274</v>
       </c>
-      <c r="R43" s="21">
+      <c r="R43" s="18">
         <f t="shared" si="13"/>
         <v>23599306</v>
       </c>
@@ -3331,21 +3773,33 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T43" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V43" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="W43" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V43" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X43" s="2">
+        <v>0.91926997899999996</v>
+      </c>
+      <c r="Y43" s="2">
+        <v>0.98724997000000003</v>
+      </c>
+      <c r="Z43" s="2">
+        <v>0.82389998399999997</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>0.94359999900000002</v>
+      </c>
+    </row>
+    <row r="44" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F44" s="15"/>
-      <c r="G44" s="23">
+      <c r="G44" s="20">
         <v>1</v>
       </c>
       <c r="H44" s="5" t="s">
@@ -3395,41 +3849,57 @@
         <v>99.381016967543303</v>
       </c>
       <c r="T44" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W44" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X44" s="2">
+        <v>0.91260999399999998</v>
+      </c>
+      <c r="Y44" s="2">
+        <v>0.98383998900000003</v>
+      </c>
+      <c r="Z44" s="2">
+        <v>0.82309997099999999</v>
+      </c>
+      <c r="AA44" s="2">
+        <v>0.94479995999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F45" s="7"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-    </row>
-    <row r="46" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G45" s="17"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="16"/>
+    </row>
+    <row r="46" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F46" s="15"/>
-      <c r="G46" s="23">
+      <c r="G46" s="20">
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
@@ -3488,10 +3958,22 @@
       <c r="W46" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X46" s="2">
+        <v>0.98328334100000003</v>
+      </c>
+      <c r="Y46" s="2">
+        <v>0.99975001799999996</v>
+      </c>
+      <c r="Z46" s="2">
+        <v>0.98589998499999998</v>
+      </c>
+      <c r="AA46" s="2">
+        <v>0.99979996699999996</v>
+      </c>
+    </row>
+    <row r="47" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F47" s="15"/>
-      <c r="G47" s="23">
+      <c r="G47" s="20">
         <v>1</v>
       </c>
       <c r="H47" s="5" t="s">
@@ -3552,10 +4034,22 @@
       <c r="W47" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X47" s="2">
+        <v>0.98820000900000005</v>
+      </c>
+      <c r="Y47" s="2">
+        <v>0.99989998300000005</v>
+      </c>
+      <c r="Z47" s="2">
+        <v>0.98359996100000002</v>
+      </c>
+      <c r="AA47" s="2">
+        <v>0.99989998300000005</v>
+      </c>
+    </row>
+    <row r="48" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F48" s="15"/>
-      <c r="G48" s="23">
+      <c r="G48" s="20">
         <v>1</v>
       </c>
       <c r="H48" s="5" t="s">
@@ -3616,10 +4110,22 @@
       <c r="W48" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X48" s="2">
+        <v>0.98846668000000004</v>
+      </c>
+      <c r="Y48" s="2">
+        <v>0.99998337000000004</v>
+      </c>
+      <c r="Z48" s="2">
+        <v>0.97990000200000005</v>
+      </c>
+      <c r="AA48" s="2">
+        <v>0.99989998300000005</v>
+      </c>
+    </row>
+    <row r="49" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F49" s="15"/>
-      <c r="G49" s="23">
+      <c r="G49" s="20">
         <v>1</v>
       </c>
       <c r="H49" s="5" t="s">
@@ -3680,10 +4186,22 @@
       <c r="W49" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="50" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X49" s="2">
+        <v>0.98453336999999996</v>
+      </c>
+      <c r="Y49" s="2">
+        <v>0.998766661</v>
+      </c>
+      <c r="Z49" s="2">
+        <v>0.97429996699999999</v>
+      </c>
+      <c r="AA49" s="2">
+        <v>0.99869996299999997</v>
+      </c>
+    </row>
+    <row r="50" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F50" s="15"/>
-      <c r="G50" s="23">
+      <c r="G50" s="20">
         <v>1</v>
       </c>
       <c r="H50" s="5" t="s">
@@ -3744,10 +4262,22 @@
       <c r="W50" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="51" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X50" s="2">
+        <v>0.98768335600000001</v>
+      </c>
+      <c r="Y50" s="2">
+        <v>0.99989998300000005</v>
+      </c>
+      <c r="Z50" s="2">
+        <v>0.98039996600000001</v>
+      </c>
+      <c r="AA50" s="2">
+        <v>0.99989998300000005</v>
+      </c>
+    </row>
+    <row r="51" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F51" s="15"/>
-      <c r="G51" s="23">
+      <c r="G51" s="20">
         <v>1</v>
       </c>
       <c r="H51" s="5" t="s">
@@ -3808,10 +4338,22 @@
       <c r="W51" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X51" s="2">
+        <v>0.98811668200000002</v>
+      </c>
+      <c r="Y51" s="2">
+        <v>0.99988335399999995</v>
+      </c>
+      <c r="Z51" s="2">
+        <v>0.97779995200000003</v>
+      </c>
+      <c r="AA51" s="2">
+        <v>0.99969995</v>
+      </c>
+    </row>
+    <row r="52" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F52" s="15"/>
-      <c r="G52" s="23">
+      <c r="G52" s="20">
         <v>1</v>
       </c>
       <c r="H52" s="5" t="s">
@@ -3872,10 +4414,22 @@
       <c r="W52" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X52" s="2">
+        <v>0.98559999499999995</v>
+      </c>
+      <c r="Y52" s="2">
+        <v>0.99919998600000004</v>
+      </c>
+      <c r="Z52" s="2">
+        <v>0.98249995700000003</v>
+      </c>
+      <c r="AA52" s="2">
+        <v>0.99849999</v>
+      </c>
+    </row>
+    <row r="53" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F53" s="15"/>
-      <c r="G53" s="23">
+      <c r="G53" s="20">
         <v>1</v>
       </c>
       <c r="H53" s="5" t="s">
@@ -3936,10 +4490,22 @@
       <c r="W53" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="54" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X53" s="2">
+        <v>0.98594999299999997</v>
+      </c>
+      <c r="Y53" s="2">
+        <v>0.99926668399999996</v>
+      </c>
+      <c r="Z53" s="2">
+        <v>0.98249995700000003</v>
+      </c>
+      <c r="AA53" s="2">
+        <v>0.99909996999999995</v>
+      </c>
+    </row>
+    <row r="54" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F54" s="15"/>
-      <c r="G54" s="23">
+      <c r="G54" s="20">
         <v>1</v>
       </c>
       <c r="H54" s="5" t="s">
@@ -4000,10 +4566,22 @@
       <c r="W54" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="55" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X54" s="2">
+        <v>0.987216651</v>
+      </c>
+      <c r="Y54" s="2">
+        <v>0.99994999200000001</v>
+      </c>
+      <c r="Z54" s="2">
+        <v>0.98409998399999998</v>
+      </c>
+      <c r="AA54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F55" s="15"/>
-      <c r="G55" s="23">
+      <c r="G55" s="20">
         <v>1</v>
       </c>
       <c r="H55" s="5" t="s">
@@ -4064,10 +4642,22 @@
       <c r="W55" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="56" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X55" s="2">
+        <v>0.98761665799999998</v>
+      </c>
+      <c r="Y55" s="2">
+        <v>0.99988335399999995</v>
+      </c>
+      <c r="Z55" s="2">
+        <v>0.98259997399999999</v>
+      </c>
+      <c r="AA55" s="2">
+        <v>0.99959999300000002</v>
+      </c>
+    </row>
+    <row r="56" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F56" s="15"/>
-      <c r="G56" s="23">
+      <c r="G56" s="20">
         <v>1</v>
       </c>
       <c r="H56" s="5" t="s">
@@ -4128,10 +4718,22 @@
       <c r="W56" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="57" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X56" s="2">
+        <v>0.98536670199999998</v>
+      </c>
+      <c r="Y56" s="2">
+        <v>0.99940001999999994</v>
+      </c>
+      <c r="Z56" s="2">
+        <v>0.98039996600000001</v>
+      </c>
+      <c r="AA56" s="2">
+        <v>0.99969995</v>
+      </c>
+    </row>
+    <row r="57" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F57" s="15"/>
-      <c r="G57" s="23">
+      <c r="G57" s="20">
         <v>1</v>
       </c>
       <c r="H57" s="5" t="s">
@@ -4192,30 +4794,46 @@
       <c r="W57" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="58" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X57" s="2">
+        <v>0.98568332199999997</v>
+      </c>
+      <c r="Y57" s="2">
+        <v>0.99919998600000004</v>
+      </c>
+      <c r="Z57" s="2">
+        <v>0.98059999900000006</v>
+      </c>
+      <c r="AA57" s="2">
+        <v>0.998999953</v>
+      </c>
+    </row>
+    <row r="58" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F58" s="7"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
-      <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="17"/>
-      <c r="S58" s="17"/>
-      <c r="T58" s="17"/>
-      <c r="U58" s="17"/>
-      <c r="V58" s="17"/>
-      <c r="W58" s="17"/>
-    </row>
-    <row r="59" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G58" s="17"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="16"/>
+      <c r="Q58" s="16"/>
+      <c r="R58" s="16"/>
+      <c r="S58" s="16"/>
+      <c r="T58" s="16"/>
+      <c r="U58" s="16"/>
+      <c r="V58" s="16"/>
+      <c r="W58" s="16"/>
+      <c r="X58" s="16"/>
+      <c r="Y58" s="16"/>
+      <c r="Z58" s="16"/>
+      <c r="AA58" s="16"/>
+    </row>
+    <row r="59" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F59" s="15"/>
-      <c r="G59" s="23">
+      <c r="G59" s="20">
         <v>1</v>
       </c>
       <c r="H59" s="5" t="s">
@@ -4274,10 +4892,22 @@
       <c r="W59" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="60" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X59" s="2">
+        <v>0.93485999099999995</v>
+      </c>
+      <c r="Y59" s="2">
+        <v>0.99807995599999999</v>
+      </c>
+      <c r="Z59" s="2">
+        <v>0.92679995299999995</v>
+      </c>
+      <c r="AA59" s="2">
+        <v>0.99719995299999997</v>
+      </c>
+    </row>
+    <row r="60" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F60" s="15"/>
-      <c r="G60" s="23">
+      <c r="G60" s="20">
         <v>1</v>
       </c>
       <c r="H60" s="5" t="s">
@@ -4338,10 +4968,22 @@
       <c r="W60" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="61" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X60" s="2">
+        <v>0.93895995600000004</v>
+      </c>
+      <c r="Y60" s="2">
+        <v>0.99901998000000003</v>
+      </c>
+      <c r="Z60" s="2">
+        <v>0.91969996700000001</v>
+      </c>
+      <c r="AA60" s="2">
+        <v>0.99789994999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F61" s="15"/>
-      <c r="G61" s="23">
+      <c r="G61" s="20">
         <v>1</v>
       </c>
       <c r="H61" s="5" t="s">
@@ -4402,10 +5044,22 @@
       <c r="W61" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="62" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X61" s="2">
+        <v>0.93955999599999995</v>
+      </c>
+      <c r="Y61" s="2">
+        <v>0.99913996500000002</v>
+      </c>
+      <c r="Z61" s="2">
+        <v>0.906699955</v>
+      </c>
+      <c r="AA61" s="2">
+        <v>0.99839997300000005</v>
+      </c>
+    </row>
+    <row r="62" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F62" s="15"/>
-      <c r="G62" s="23">
+      <c r="G62" s="20">
         <v>1</v>
       </c>
       <c r="H62" s="5" t="s">
@@ -4466,10 +5120,22 @@
       <c r="W62" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X62" s="2">
+        <v>0.91203999499999999</v>
+      </c>
+      <c r="Y62" s="2">
+        <v>0.99259996399999995</v>
+      </c>
+      <c r="Z62" s="2">
+        <v>0.90309995399999998</v>
+      </c>
+      <c r="AA62" s="2">
+        <v>0.991999984</v>
+      </c>
+    </row>
+    <row r="63" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F63" s="15"/>
-      <c r="G63" s="23">
+      <c r="G63" s="20">
         <v>1</v>
       </c>
       <c r="H63" s="5" t="s">
@@ -4530,10 +5196,22 @@
       <c r="W63" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="64" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X63" s="2">
+        <v>0.94035994999999994</v>
+      </c>
+      <c r="Y63" s="2">
+        <v>0.99941998700000001</v>
+      </c>
+      <c r="Z63" s="2">
+        <v>0.92189997400000001</v>
+      </c>
+      <c r="AA63" s="2">
+        <v>0.99799996599999996</v>
+      </c>
+    </row>
+    <row r="64" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F64" s="15"/>
-      <c r="G64" s="23">
+      <c r="G64" s="20">
         <v>1</v>
       </c>
       <c r="H64" s="5" t="s">
@@ -4570,11 +5248,11 @@
         <f>"(2048,6,6) --&gt; (2,2,2,1024,3,3) --&gt; (10)"</f>
         <v>(2048,6,6) --&gt; (2,2,2,1024,3,3) --&gt; (10)</v>
       </c>
-      <c r="Q64" s="21">
+      <c r="Q64" s="18">
         <f>103512</f>
         <v>103512</v>
       </c>
-      <c r="R64" s="21">
+      <c r="R64" s="18">
         <f t="shared" si="23"/>
         <v>42603672</v>
       </c>
@@ -4594,10 +5272,22 @@
       <c r="W64" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="65" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X64" s="2">
+        <v>0.94117999100000005</v>
+      </c>
+      <c r="Y64" s="2">
+        <v>0.99909996999999995</v>
+      </c>
+      <c r="Z64" s="2">
+        <v>0.91859996300000002</v>
+      </c>
+      <c r="AA64" s="2">
+        <v>0.99889999600000001</v>
+      </c>
+    </row>
+    <row r="65" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F65" s="15"/>
-      <c r="G65" s="23">
+      <c r="G65" s="20">
         <v>1</v>
       </c>
       <c r="H65" s="5" t="s">
@@ -4658,10 +5348,22 @@
       <c r="W65" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="66" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X65" s="2">
+        <v>0.92931997799999999</v>
+      </c>
+      <c r="Y65" s="2">
+        <v>0.99706000100000003</v>
+      </c>
+      <c r="Z65" s="2">
+        <v>0.92079997099999999</v>
+      </c>
+      <c r="AA65" s="2">
+        <v>0.99619996499999997</v>
+      </c>
+    </row>
+    <row r="66" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F66" s="15"/>
-      <c r="G66" s="23">
+      <c r="G66" s="20">
         <v>1</v>
       </c>
       <c r="H66" s="5" t="s">
@@ -4722,10 +5424,22 @@
       <c r="W66" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="67" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X66" s="2">
+        <v>0.927519977</v>
+      </c>
+      <c r="Y66" s="2">
+        <v>0.99609994899999998</v>
+      </c>
+      <c r="Z66" s="2">
+        <v>0.90289998100000002</v>
+      </c>
+      <c r="AA66" s="2">
+        <v>0.99299997100000004</v>
+      </c>
+    </row>
+    <row r="67" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F67" s="15"/>
-      <c r="G67" s="23">
+      <c r="G67" s="20">
         <v>1</v>
       </c>
       <c r="H67" s="5" t="s">
@@ -4786,10 +5500,22 @@
       <c r="W67" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="68" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X67" s="2">
+        <v>0.94079995199999999</v>
+      </c>
+      <c r="Y67" s="2">
+        <v>0.99935996500000002</v>
+      </c>
+      <c r="Z67" s="2">
+        <v>0.90340000399999998</v>
+      </c>
+      <c r="AA67" s="2">
+        <v>0.99789994999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F68" s="15"/>
-      <c r="G68" s="23">
+      <c r="G68" s="20">
         <v>1</v>
       </c>
       <c r="H68" s="5" t="s">
@@ -4850,10 +5576,22 @@
       <c r="W68" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="69" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X68" s="2">
+        <v>0.94233995699999995</v>
+      </c>
+      <c r="Y68" s="2">
+        <v>0.99945998199999997</v>
+      </c>
+      <c r="Z68" s="2">
+        <v>0.921499968</v>
+      </c>
+      <c r="AA68" s="2">
+        <v>0.99879998000000003</v>
+      </c>
+    </row>
+    <row r="69" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F69" s="15"/>
-      <c r="G69" s="23">
+      <c r="G69" s="20">
         <v>1</v>
       </c>
       <c r="H69" s="5" t="s">
@@ -4914,10 +5652,22 @@
       <c r="W69" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="70" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X69" s="2">
+        <v>0.92725998200000004</v>
+      </c>
+      <c r="Y69" s="2">
+        <v>0.99673998399999997</v>
+      </c>
+      <c r="Z69" s="2">
+        <v>0.92439997200000001</v>
+      </c>
+      <c r="AA69" s="2">
+        <v>0.99649995599999996</v>
+      </c>
+    </row>
+    <row r="70" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F70" s="15"/>
-      <c r="G70" s="23">
+      <c r="G70" s="20">
         <v>1</v>
       </c>
       <c r="H70" s="5" t="s">
@@ -4954,11 +5704,11 @@
         <f>"(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (10)"</f>
         <v>(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (10)</v>
       </c>
-      <c r="Q70" s="21">
+      <c r="Q70" s="18">
         <f>1386</f>
         <v>1386</v>
       </c>
-      <c r="R70" s="21">
+      <c r="R70" s="18">
         <f t="shared" si="23"/>
         <v>42501546</v>
       </c>
@@ -4978,30 +5728,46 @@
       <c r="W70" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="71" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X70" s="2">
+        <v>0.92917996599999997</v>
+      </c>
+      <c r="Y70" s="2">
+        <v>0.99647998800000004</v>
+      </c>
+      <c r="Z70" s="2">
+        <v>0.89969998600000001</v>
+      </c>
+      <c r="AA70" s="2">
+        <v>0.99269998100000001</v>
+      </c>
+    </row>
+    <row r="71" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F71" s="7"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
-      <c r="N71" s="17"/>
-      <c r="O71" s="17"/>
-      <c r="P71" s="17"/>
-      <c r="Q71" s="17"/>
-      <c r="R71" s="17"/>
-      <c r="S71" s="17"/>
-      <c r="T71" s="17"/>
-      <c r="U71" s="17"/>
-      <c r="V71" s="17"/>
-      <c r="W71" s="17"/>
-    </row>
-    <row r="72" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G71" s="17"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
+      <c r="N71" s="16"/>
+      <c r="O71" s="16"/>
+      <c r="P71" s="16"/>
+      <c r="Q71" s="16"/>
+      <c r="R71" s="16"/>
+      <c r="S71" s="16"/>
+      <c r="T71" s="16"/>
+      <c r="U71" s="16"/>
+      <c r="V71" s="16"/>
+      <c r="W71" s="16"/>
+      <c r="X71" s="16"/>
+      <c r="Y71" s="16"/>
+      <c r="Z71" s="16"/>
+      <c r="AA71" s="16"/>
+    </row>
+    <row r="72" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F72" s="15"/>
-      <c r="G72" s="23">
+      <c r="G72" s="20">
         <v>1</v>
       </c>
       <c r="H72" s="5" t="s">
@@ -5060,10 +5826,22 @@
       <c r="W72" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="73" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X72" s="2">
+        <v>0.913029969</v>
+      </c>
+      <c r="Y72" s="2">
+        <v>0.98892998700000001</v>
+      </c>
+      <c r="Z72" s="2">
+        <v>0.79819995200000005</v>
+      </c>
+      <c r="AA72" s="2">
+        <v>0.92280000399999995</v>
+      </c>
+    </row>
+    <row r="73" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F73" s="15"/>
-      <c r="G73" s="23">
+      <c r="G73" s="20">
         <v>1</v>
       </c>
       <c r="H73" s="5" t="s">
@@ -5124,10 +5902,22 @@
       <c r="W73" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="74" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X73" s="2">
+        <v>0.97539997099999998</v>
+      </c>
+      <c r="Y73" s="2">
+        <v>0.99919998600000004</v>
+      </c>
+      <c r="Z73" s="2">
+        <v>0.84109997700000005</v>
+      </c>
+      <c r="AA73" s="2">
+        <v>0.94559997299999998</v>
+      </c>
+    </row>
+    <row r="74" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F74" s="15"/>
-      <c r="G74" s="23">
+      <c r="G74" s="20">
         <v>1</v>
       </c>
       <c r="H74" s="5" t="s">
@@ -5188,10 +5978,22 @@
       <c r="W74" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="75" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X74" s="2">
+        <v>0.97393995499999997</v>
+      </c>
+      <c r="Y74" s="2">
+        <v>0.99919998600000004</v>
+      </c>
+      <c r="Z74" s="2">
+        <v>0.84200000799999997</v>
+      </c>
+      <c r="AA74" s="2">
+        <v>0.94989997100000001</v>
+      </c>
+    </row>
+    <row r="75" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F75" s="15"/>
-      <c r="G75" s="23">
+      <c r="G75" s="20">
         <v>1</v>
       </c>
       <c r="H75" s="5" t="s">
@@ -5252,10 +6054,22 @@
       <c r="W75" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="76" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X75" s="2">
+        <v>0.97247999900000004</v>
+      </c>
+      <c r="Y75" s="2">
+        <v>0.99901998000000003</v>
+      </c>
+      <c r="Z75" s="2">
+        <v>0.84559994900000002</v>
+      </c>
+      <c r="AA75" s="2">
+        <v>0.94999998799999996</v>
+      </c>
+    </row>
+    <row r="76" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F76" s="15"/>
-      <c r="G76" s="23">
+      <c r="G76" s="20">
         <v>1</v>
       </c>
       <c r="H76" s="5" t="s">
@@ -5316,10 +6130,22 @@
       <c r="W76" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="77" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X76" s="2">
+        <v>0.97148996600000004</v>
+      </c>
+      <c r="Y76" s="2">
+        <v>0.99886000200000002</v>
+      </c>
+      <c r="Z76" s="2">
+        <v>0.849999964</v>
+      </c>
+      <c r="AA76" s="2">
+        <v>0.954999983</v>
+      </c>
+    </row>
+    <row r="77" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F77" s="15"/>
-      <c r="G77" s="23">
+      <c r="G77" s="20">
         <v>1</v>
       </c>
       <c r="H77" s="5" t="s">
@@ -5380,10 +6206,22 @@
       <c r="W77" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="78" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X77" s="2">
+        <v>0.97331994799999999</v>
+      </c>
+      <c r="Y77" s="2">
+        <v>0.99906998899999999</v>
+      </c>
+      <c r="Z77" s="2">
+        <v>0.85529995000000003</v>
+      </c>
+      <c r="AA77" s="2">
+        <v>0.95829999399999999</v>
+      </c>
+    </row>
+    <row r="78" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F78" s="15"/>
-      <c r="G78" s="23">
+      <c r="G78" s="20">
         <v>1</v>
       </c>
       <c r="H78" s="5" t="s">
@@ -5444,10 +6282,22 @@
       <c r="W78" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="79" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X78" s="2">
+        <v>0.95879000400000003</v>
+      </c>
+      <c r="Y78" s="2">
+        <v>0.99580997199999999</v>
+      </c>
+      <c r="Z78" s="2">
+        <v>0.84869998700000004</v>
+      </c>
+      <c r="AA78" s="2">
+        <v>0.95299994899999996</v>
+      </c>
+    </row>
+    <row r="79" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F79" s="15"/>
-      <c r="G79" s="23">
+      <c r="G79" s="20">
         <v>1</v>
       </c>
       <c r="H79" s="5" t="s">
@@ -5508,10 +6358,22 @@
       <c r="W79" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="80" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X79" s="2">
+        <v>0.94853997199999995</v>
+      </c>
+      <c r="Y79" s="2">
+        <v>0.99313998199999998</v>
+      </c>
+      <c r="Z79" s="2">
+        <v>0.85139995800000001</v>
+      </c>
+      <c r="AA79" s="2">
+        <v>0.95260000199999995</v>
+      </c>
+    </row>
+    <row r="80" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F80" s="15"/>
-      <c r="G80" s="23">
+      <c r="G80" s="20">
         <v>1</v>
       </c>
       <c r="H80" s="5" t="s">
@@ -5572,10 +6434,22 @@
       <c r="W80" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="81" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X80" s="2">
+        <v>0.96441996100000005</v>
+      </c>
+      <c r="Y80" s="2">
+        <v>0.99751997000000003</v>
+      </c>
+      <c r="Z80" s="2">
+        <v>0.85229998799999995</v>
+      </c>
+      <c r="AA80" s="2">
+        <v>0.95529997300000002</v>
+      </c>
+    </row>
+    <row r="81" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F81" s="15"/>
-      <c r="G81" s="23">
+      <c r="G81" s="20">
         <v>1</v>
       </c>
       <c r="H81" s="5" t="s">
@@ -5636,10 +6510,22 @@
       <c r="W81" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="82" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X81" s="2">
+        <v>0.96591997100000004</v>
+      </c>
+      <c r="Y81" s="2">
+        <v>0.99764996800000005</v>
+      </c>
+      <c r="Z81" s="2">
+        <v>0.85359996599999999</v>
+      </c>
+      <c r="AA81" s="2">
+        <v>0.95459997699999999</v>
+      </c>
+    </row>
+    <row r="82" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F82" s="15"/>
-      <c r="G82" s="23">
+      <c r="G82" s="20">
         <v>1</v>
       </c>
       <c r="H82" s="5" t="s">
@@ -5700,10 +6586,22 @@
       <c r="W82" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="83" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X82" s="2">
+        <v>0.95944994699999997</v>
+      </c>
+      <c r="Y82" s="2">
+        <v>0.99612999000000002</v>
+      </c>
+      <c r="Z82" s="2">
+        <v>0.85209995500000002</v>
+      </c>
+      <c r="AA82" s="2">
+        <v>0.95219999600000005</v>
+      </c>
+    </row>
+    <row r="83" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F83" s="15"/>
-      <c r="G83" s="23">
+      <c r="G83" s="20">
         <v>1</v>
       </c>
       <c r="H83" s="5" t="s">
@@ -5740,11 +6638,11 @@
         <f>"(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (200)"</f>
         <v>(2048,6,6) --&gt; (16,2,2,128,3,3) --&gt; (200)</v>
       </c>
-      <c r="Q83" s="21">
+      <c r="Q83" s="18">
         <f>91274</f>
         <v>91274</v>
       </c>
-      <c r="R83" s="21">
+      <c r="R83" s="18">
         <f t="shared" si="28"/>
         <v>42591434</v>
       </c>
@@ -5764,30 +6662,46 @@
       <c r="W83" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="84" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X83" s="2">
+        <v>0.96065998100000005</v>
+      </c>
+      <c r="Y83" s="2">
+        <v>0.99593997000000001</v>
+      </c>
+      <c r="Z83" s="2">
+        <v>0.852499962</v>
+      </c>
+      <c r="AA83" s="2">
+        <v>0.95369994599999997</v>
+      </c>
+    </row>
+    <row r="84" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F84" s="7"/>
-      <c r="G84" s="18"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="17"/>
-      <c r="K84" s="17"/>
-      <c r="L84" s="17"/>
-      <c r="M84" s="17"/>
-      <c r="N84" s="17"/>
-      <c r="O84" s="17"/>
-      <c r="P84" s="17"/>
-      <c r="Q84" s="17"/>
-      <c r="R84" s="17"/>
-      <c r="S84" s="17"/>
-      <c r="T84" s="17"/>
-      <c r="U84" s="17"/>
-      <c r="V84" s="17"/>
-      <c r="W84" s="17"/>
-    </row>
-    <row r="85" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G84" s="17"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
+      <c r="J84" s="16"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="16"/>
+      <c r="M84" s="16"/>
+      <c r="N84" s="16"/>
+      <c r="O84" s="16"/>
+      <c r="P84" s="16"/>
+      <c r="Q84" s="16"/>
+      <c r="R84" s="16"/>
+      <c r="S84" s="16"/>
+      <c r="T84" s="16"/>
+      <c r="U84" s="16"/>
+      <c r="V84" s="16"/>
+      <c r="W84" s="16"/>
+      <c r="X84" s="16"/>
+      <c r="Y84" s="16"/>
+      <c r="Z84" s="16"/>
+      <c r="AA84" s="16"/>
+    </row>
+    <row r="85" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F85" s="15"/>
-      <c r="G85" s="23">
+      <c r="G85" s="20">
         <v>1</v>
       </c>
       <c r="H85" s="5" t="s">
@@ -5798,11 +6712,11 @@
         <v>CNN</v>
       </c>
       <c r="J85" s="2" t="str">
-        <f t="shared" ref="J85:J90" si="30" xml:space="preserve"> "MNIST"</f>
+        <f t="shared" ref="J85:J88" si="30" xml:space="preserve"> "MNIST"</f>
         <v>MNIST</v>
       </c>
       <c r="K85" s="2" t="str">
-        <f t="shared" ref="K85:K125" si="31" xml:space="preserve"> "(3,192,192)"</f>
+        <f t="shared" ref="K85:K105" si="31" xml:space="preserve"> "(3,192,192)"</f>
         <v>(3,192,192)</v>
       </c>
       <c r="L85" s="2">
@@ -5846,17 +6760,29 @@
       <c r="W85" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="86" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X85" s="2">
+        <v>0.998283327</v>
+      </c>
+      <c r="Y85" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="2">
+        <v>0.98149997</v>
+      </c>
+      <c r="AA85" s="2">
+        <v>0.99959999300000002</v>
+      </c>
+    </row>
+    <row r="86" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F86" s="15"/>
-      <c r="G86" s="23">
+      <c r="G86" s="20">
         <v>1</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>100</v>
       </c>
       <c r="I86" s="2" t="str">
-        <f t="shared" ref="I86:I90" si="32" xml:space="preserve"> "CNN"</f>
+        <f t="shared" ref="I86:I88" si="32" xml:space="preserve"> "CNN"</f>
         <v>CNN</v>
       </c>
       <c r="J86" s="2" t="str">
@@ -5899,7 +6825,7 @@
         <v>98.327817320828956</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U86" s="2" t="s">
         <v>13</v>
@@ -5910,10 +6836,22 @@
       <c r="W86" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="87" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X86" s="2">
+        <v>0.98510003099999999</v>
+      </c>
+      <c r="Y86" s="2">
+        <v>0.99991667299999998</v>
+      </c>
+      <c r="Z86" s="2">
+        <v>0.95629996100000003</v>
+      </c>
+      <c r="AA86" s="2">
+        <v>0.99969995</v>
+      </c>
+    </row>
+    <row r="87" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F87" s="15"/>
-      <c r="G87" s="23">
+      <c r="G87" s="20">
         <v>1</v>
       </c>
       <c r="H87" s="5" t="s">
@@ -5963,7 +6901,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U87" s="2" t="s">
         <v>13</v>
@@ -5974,10 +6912,22 @@
       <c r="W87" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="88" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X87" s="2">
+        <v>0.96313333499999998</v>
+      </c>
+      <c r="Y87" s="2">
+        <v>0.99953335499999996</v>
+      </c>
+      <c r="Z87" s="2">
+        <v>0.97119998900000004</v>
+      </c>
+      <c r="AA87" s="2">
+        <v>0.99979996699999996</v>
+      </c>
+    </row>
+    <row r="88" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F88" s="15"/>
-      <c r="G88" s="23">
+      <c r="G88" s="20">
         <v>1</v>
       </c>
       <c r="H88" s="5" t="s">
@@ -6027,7 +6977,7 @@
         <v>98.847155500811226</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U88" s="2" t="s">
         <v>13</v>
@@ -6038,169 +6988,207 @@
       <c r="W88" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="89" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F89" s="15"/>
-      <c r="G89" s="20">
-        <v>1</v>
-      </c>
-      <c r="H89" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I89" s="25" t="str">
-        <f t="shared" si="32"/>
-        <v>CNN</v>
-      </c>
-      <c r="J89" s="25" t="str">
-        <f t="shared" si="30"/>
-        <v>MNIST</v>
-      </c>
-      <c r="K89" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L89" s="25">
-        <v>10</v>
-      </c>
-      <c r="M89" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N89" s="25" t="str">
-        <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)"</f>
-        <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)</v>
-      </c>
-      <c r="O89" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type1"</f>
-        <v>(8,2,2)-type1</v>
-      </c>
-      <c r="P89" s="25" t="str">
-        <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q89" s="26">
-        <f>192 + 208</f>
-        <v>400</v>
-      </c>
-      <c r="R89" s="26">
-        <f>R88 -Q88+ Q89</f>
-        <v>94096</v>
-      </c>
-      <c r="S89" s="25">
-        <f xml:space="preserve"> (1-(Q89/Q85))*100</f>
-        <v>99.991543100798211</v>
-      </c>
-      <c r="T89" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U89" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="V89" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W89" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="X88" s="2">
+        <v>0.96453332899999999</v>
+      </c>
+      <c r="Y88" s="2">
+        <v>0.99950003600000004</v>
+      </c>
+      <c r="Z88" s="2">
+        <v>0.97129994600000003</v>
+      </c>
+      <c r="AA88" s="2">
+        <v>0.99969995</v>
+      </c>
+    </row>
+    <row r="89" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F89" s="7"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="16"/>
+      <c r="I89" s="16"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
+      <c r="L89" s="16"/>
+      <c r="M89" s="16"/>
+      <c r="N89" s="16"/>
+      <c r="O89" s="16"/>
+      <c r="P89" s="16"/>
+      <c r="Q89" s="16"/>
+      <c r="R89" s="16"/>
+      <c r="S89" s="16"/>
+      <c r="T89" s="16"/>
+      <c r="U89" s="16"/>
+      <c r="V89" s="16"/>
+      <c r="W89" s="16"/>
+      <c r="X89" s="16"/>
+      <c r="Y89" s="16"/>
+      <c r="Z89" s="16"/>
+      <c r="AA89" s="16"/>
+    </row>
+    <row r="90" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F90" s="15"/>
       <c r="G90" s="20">
         <v>1</v>
       </c>
-      <c r="H90" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I90" s="25" t="str">
-        <f t="shared" si="32"/>
-        <v>CNN</v>
-      </c>
-      <c r="J90" s="25" t="str">
-        <f t="shared" si="30"/>
-        <v>MNIST</v>
-      </c>
-      <c r="K90" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L90" s="25">
-        <v>10</v>
-      </c>
-      <c r="M90" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N90" s="25" t="str">
-        <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)"</f>
-        <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)</v>
-      </c>
-      <c r="O90" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type2"</f>
-        <v>(8,2,2)-type2</v>
-      </c>
-      <c r="P90" s="25" t="str">
-        <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q90" s="26">
-        <f>192 + 208</f>
-        <v>400</v>
-      </c>
-      <c r="R90" s="26">
-        <f t="shared" ref="R90" si="33" xml:space="preserve"> R89 - Q89 + Q90</f>
-        <v>94096</v>
-      </c>
-      <c r="S90" s="25">
-        <f xml:space="preserve"> (1-(Q90/Q85))*100</f>
-        <v>99.991543100798211</v>
-      </c>
-      <c r="T90" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U90" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="V90" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W90" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F91" s="7"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
-      <c r="L91" s="17"/>
-      <c r="M91" s="17"/>
-      <c r="N91" s="17"/>
-      <c r="O91" s="17"/>
-      <c r="P91" s="17"/>
-      <c r="Q91" s="17"/>
-      <c r="R91" s="17"/>
-      <c r="S91" s="17"/>
-      <c r="T91" s="17"/>
-      <c r="U91" s="17"/>
-      <c r="V91" s="17"/>
-      <c r="W91" s="17"/>
-    </row>
-    <row r="92" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F92" s="15"/>
-      <c r="G92" s="23">
-        <v>1</v>
-      </c>
-      <c r="H92" s="5" t="s">
+      <c r="H90" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="I92" s="2" t="str">
+      <c r="I90" s="2" t="str">
         <f xml:space="preserve"> "CNN"</f>
         <v>CNN</v>
       </c>
+      <c r="J90" s="2" t="str">
+        <f t="shared" ref="J90:J93" si="33" xml:space="preserve"> "CIFAR10"</f>
+        <v>CIFAR10</v>
+      </c>
+      <c r="K90" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>(3,192,192)</v>
+      </c>
+      <c r="L90" s="2">
+        <v>10</v>
+      </c>
+      <c r="M90" s="2" t="str">
+        <f xml:space="preserve"> "Linear"</f>
+        <v>Linear</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O90" s="2" t="b">
+        <f xml:space="preserve"> FALSE</f>
+        <v>0</v>
+      </c>
+      <c r="P90" s="2" t="str">
+        <f>"(128,6,6) --&gt; (1024) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (1024) --&gt; (10)</v>
+      </c>
+      <c r="Q90" s="10">
+        <f>4729866</f>
+        <v>4729866</v>
+      </c>
+      <c r="R90" s="10">
+        <f>4823562</f>
+        <v>4823562</v>
+      </c>
+      <c r="S90" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T90" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="U90" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X90" s="2">
+        <v>0.94639998700000005</v>
+      </c>
+      <c r="Y90" s="2">
+        <v>0.99974000500000004</v>
+      </c>
+      <c r="Z90" s="2">
+        <v>0.76099997799999997</v>
+      </c>
+      <c r="AA90" s="2">
+        <v>0.98049998299999996</v>
+      </c>
+    </row>
+    <row r="91" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F91" s="15"/>
+      <c r="G91" s="20">
+        <v>1</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I91" s="2" t="str">
+        <f t="shared" ref="I91:I93" si="34" xml:space="preserve"> "CNN"</f>
+        <v>CNN</v>
+      </c>
+      <c r="J91" s="2" t="str">
+        <f t="shared" si="33"/>
+        <v>CIFAR10</v>
+      </c>
+      <c r="K91" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>(3,192,192)</v>
+      </c>
+      <c r="L91" s="2">
+        <v>10</v>
+      </c>
+      <c r="M91" s="2" t="str">
+        <f xml:space="preserve"> "TCL + TRL"</f>
+        <v>TCL + TRL</v>
+      </c>
+      <c r="N91" s="2" t="str">
+        <f>"tcl:: (128,6,6), trl:: (128,6,6,10)"</f>
+        <v>tcl:: (128,6,6), trl:: (128,6,6,10)</v>
+      </c>
+      <c r="O91" s="2" t="b">
+        <f xml:space="preserve"> FALSE</f>
+        <v>0</v>
+      </c>
+      <c r="P91" s="2" t="str">
+        <f>"(128,6,6) --&gt; (128,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (128,6,6) --&gt; (10)</v>
+      </c>
+      <c r="Q91" s="10">
+        <f>79092</f>
+        <v>79092</v>
+      </c>
+      <c r="R91" s="10">
+        <f xml:space="preserve"> R90 - Q90 + Q91</f>
+        <v>172788</v>
+      </c>
+      <c r="S91" s="2">
+        <f xml:space="preserve"> (1-(Q91/Q90))*100</f>
+        <v>98.327817320828956</v>
+      </c>
+      <c r="T91" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="U91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W91" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X91" s="2">
+        <v>0.75427997099999999</v>
+      </c>
+      <c r="Y91" s="2">
+        <v>0.98355996599999995</v>
+      </c>
+      <c r="Z91" s="2">
+        <v>0.75069999700000001</v>
+      </c>
+      <c r="AA91" s="2">
+        <v>0.98329997099999999</v>
+      </c>
+    </row>
+    <row r="92" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F92" s="15"/>
+      <c r="G92" s="20">
+        <v>1</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I92" s="2" t="str">
+        <f t="shared" si="34"/>
+        <v>CNN</v>
+      </c>
       <c r="J92" s="2" t="str">
-        <f t="shared" ref="J92:J97" si="34" xml:space="preserve"> "CIFAR10"</f>
+        <f t="shared" si="33"/>
         <v>CIFAR10</v>
       </c>
       <c r="K92" s="2" t="str">
@@ -6211,524 +7199,572 @@
         <v>10</v>
       </c>
       <c r="M92" s="2" t="str">
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
+      </c>
+      <c r="N92" s="2" t="str">
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)</v>
+      </c>
+      <c r="O92" s="2" t="str">
+        <f xml:space="preserve"> "(2,1,1)-type1"</f>
+        <v>(2,1,1)-type1</v>
+      </c>
+      <c r="P92" s="2" t="str">
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)</v>
+      </c>
+      <c r="Q92" s="10">
+        <f>54528</f>
+        <v>54528</v>
+      </c>
+      <c r="R92" s="10">
+        <f>R91 -Q91 + Q92</f>
+        <v>148224</v>
+      </c>
+      <c r="S92" s="2">
+        <f xml:space="preserve"> (1-(Q92/Q90))*100</f>
+        <v>98.847155500811226</v>
+      </c>
+      <c r="T92" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="U92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X92" s="2">
+        <v>0.69481998700000003</v>
+      </c>
+      <c r="Y92" s="2">
+        <v>0.97643995299999997</v>
+      </c>
+      <c r="Z92" s="2">
+        <v>0.73579996800000003</v>
+      </c>
+      <c r="AA92" s="2">
+        <v>0.98099994700000004</v>
+      </c>
+    </row>
+    <row r="93" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F93" s="15"/>
+      <c r="G93" s="20">
+        <v>1</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I93" s="2" t="str">
+        <f t="shared" si="34"/>
+        <v>CNN</v>
+      </c>
+      <c r="J93" s="2" t="str">
+        <f t="shared" si="33"/>
+        <v>CIFAR10</v>
+      </c>
+      <c r="K93" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>(3,192,192)</v>
+      </c>
+      <c r="L93" s="2">
+        <v>10</v>
+      </c>
+      <c r="M93" s="2" t="str">
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
+      </c>
+      <c r="N93" s="2" t="str">
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)</v>
+      </c>
+      <c r="O93" s="2" t="str">
+        <f xml:space="preserve"> "(2,1,1)-type2"</f>
+        <v>(2,1,1)-type2</v>
+      </c>
+      <c r="P93" s="2" t="str">
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)</v>
+      </c>
+      <c r="Q93" s="10">
+        <f>54528</f>
+        <v>54528</v>
+      </c>
+      <c r="R93" s="10">
+        <f xml:space="preserve"> R92 - Q92 + Q93</f>
+        <v>148224</v>
+      </c>
+      <c r="S93" s="2">
+        <f xml:space="preserve"> (1-(Q93/Q90))*100</f>
+        <v>98.847155500811226</v>
+      </c>
+      <c r="T93" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="U93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X93" s="2">
+        <v>0.69066000000000005</v>
+      </c>
+      <c r="Y93" s="2">
+        <v>0.97525996000000004</v>
+      </c>
+      <c r="Z93" s="2">
+        <v>0.73039996600000001</v>
+      </c>
+      <c r="AA93" s="2">
+        <v>0.98069995600000004</v>
+      </c>
+    </row>
+    <row r="94" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F94" s="7"/>
+      <c r="G94" s="17"/>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+      <c r="J94" s="16"/>
+      <c r="K94" s="16"/>
+      <c r="L94" s="16"/>
+      <c r="M94" s="16"/>
+      <c r="N94" s="16"/>
+      <c r="O94" s="16"/>
+      <c r="P94" s="16"/>
+      <c r="Q94" s="16"/>
+      <c r="R94" s="16"/>
+      <c r="S94" s="16"/>
+      <c r="T94" s="16"/>
+      <c r="U94" s="16"/>
+      <c r="V94" s="16"/>
+      <c r="W94" s="16"/>
+      <c r="X94" s="16"/>
+      <c r="Y94" s="16"/>
+      <c r="Z94" s="16"/>
+      <c r="AA94" s="16"/>
+    </row>
+    <row r="95" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F95" s="15"/>
+      <c r="G95" s="20">
+        <v>1</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I95" s="2" t="str">
+        <f xml:space="preserve"> "CNN"</f>
+        <v>CNN</v>
+      </c>
+      <c r="J95" s="2" t="str">
+        <f xml:space="preserve"> "TINY"</f>
+        <v>TINY</v>
+      </c>
+      <c r="K95" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>(3,192,192)</v>
+      </c>
+      <c r="L95" s="2">
+        <v>200</v>
+      </c>
+      <c r="M95" s="2" t="str">
         <f xml:space="preserve"> "Linear"</f>
         <v>Linear</v>
       </c>
-      <c r="N92" s="2" t="s">
+      <c r="N95" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O92" s="2" t="b">
+      <c r="O95" s="2" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
-      <c r="P92" s="2" t="str">
-        <f>"(128,6,6) --&gt; (1024) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (1024) --&gt; (10)</v>
-      </c>
-      <c r="Q92" s="10">
-        <f>4729866</f>
-        <v>4729866</v>
-      </c>
-      <c r="R92" s="10">
-        <f>4823562</f>
-        <v>4823562</v>
-      </c>
-      <c r="S92" s="2" t="s">
+      <c r="P95" s="2" t="str">
+        <f>"(128,6,6) --&gt; (1024) --&gt; (200)"</f>
+        <v>(128,6,6) --&gt; (1024) --&gt; (200)</v>
+      </c>
+      <c r="Q95" s="10">
+        <f>4924616</f>
+        <v>4924616</v>
+      </c>
+      <c r="R95" s="10">
+        <f>5018312</f>
+        <v>5018312</v>
+      </c>
+      <c r="S95" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T92" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="U92" s="2" t="s">
+      <c r="T95" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U95" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="V92" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W92" s="2" t="s">
+      <c r="V95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W95" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="93" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F93" s="15"/>
-      <c r="G93" s="23">
-        <v>1</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I93" s="2" t="str">
-        <f t="shared" ref="I93:I97" si="35" xml:space="preserve"> "CNN"</f>
+      <c r="X95" s="2">
+        <v>0.36274999400000002</v>
+      </c>
+      <c r="Y95" s="2">
+        <v>0.64269000300000001</v>
+      </c>
+      <c r="Z95" s="2">
+        <v>0.28329998299999998</v>
+      </c>
+      <c r="AA95" s="2">
+        <v>0.54019999500000004</v>
+      </c>
+    </row>
+    <row r="96" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F96" s="15"/>
+      <c r="G96" s="20">
+        <v>1</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I96" s="2" t="str">
+        <f t="shared" ref="I96:I98" si="35" xml:space="preserve"> "CNN"</f>
         <v>CNN</v>
       </c>
-      <c r="J93" s="2" t="str">
-        <f t="shared" si="34"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K93" s="2" t="str">
+      <c r="J96" s="2" t="str">
+        <f t="shared" ref="J96:J98" si="36" xml:space="preserve"> "TINY"</f>
+        <v>TINY</v>
+      </c>
+      <c r="K96" s="2" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L93" s="2">
-        <v>10</v>
-      </c>
-      <c r="M93" s="2" t="str">
+      <c r="L96" s="2">
+        <v>200</v>
+      </c>
+      <c r="M96" s="2" t="str">
         <f xml:space="preserve"> "TCL + TRL"</f>
         <v>TCL + TRL</v>
       </c>
-      <c r="N93" s="2" t="str">
-        <f>"tcl:: (128,6,6), trl:: (128,6,6,10)"</f>
-        <v>tcl:: (128,6,6), trl:: (128,6,6,10)</v>
-      </c>
-      <c r="O93" s="2" t="b">
+      <c r="N96" s="2" t="str">
+        <f>"tcl:: (128,6,6), trl:: (128,6,6,200)"</f>
+        <v>tcl:: (128,6,6), trl:: (128,6,6,200)</v>
+      </c>
+      <c r="O96" s="2" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
-      <c r="P93" s="2" t="str">
-        <f>"(128,6,6) --&gt; (128,6,6) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (128,6,6) --&gt; (10)</v>
-      </c>
-      <c r="Q93" s="10">
-        <f>79092</f>
-        <v>79092</v>
-      </c>
-      <c r="R93" s="10">
-        <f xml:space="preserve"> R92 - Q92 + Q93</f>
-        <v>172788</v>
-      </c>
-      <c r="S93" s="2">
-        <f xml:space="preserve"> (1-(Q93/Q92))*100</f>
-        <v>98.327817320828956</v>
-      </c>
-      <c r="T93" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="U93" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W93" s="2" t="s">
+      <c r="P96" s="2" t="str">
+        <f>"(128,6,6) --&gt; (128,6,6) --&gt; (200)"</f>
+        <v>(128,6,6) --&gt; (128,6,6) --&gt; (200)</v>
+      </c>
+      <c r="Q96" s="10">
+        <f>994512</f>
+        <v>994512</v>
+      </c>
+      <c r="R96" s="10">
+        <f xml:space="preserve"> R95 - Q95 + Q96</f>
+        <v>1088208</v>
+      </c>
+      <c r="S96" s="2">
+        <f xml:space="preserve"> (1-(Q96/Q95))*100</f>
+        <v>79.805288371722796</v>
+      </c>
+      <c r="T96" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U96" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W96" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="94" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F94" s="15"/>
-      <c r="G94" s="23">
-        <v>1</v>
-      </c>
-      <c r="H94" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I94" s="2" t="str">
+      <c r="X96" s="2">
+        <v>0.36796999000000002</v>
+      </c>
+      <c r="Y96" s="2">
+        <v>0.63266998500000005</v>
+      </c>
+      <c r="Z96" s="2">
+        <v>0.319599986</v>
+      </c>
+      <c r="AA96" s="2">
+        <v>0.57949996000000004</v>
+      </c>
+    </row>
+    <row r="97" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F97" s="15"/>
+      <c r="G97" s="20">
+        <v>1</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="I97" s="2" t="str">
         <f t="shared" si="35"/>
         <v>CNN</v>
       </c>
-      <c r="J94" s="2" t="str">
-        <f t="shared" si="34"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K94" s="2" t="str">
+      <c r="J97" s="2" t="str">
+        <f t="shared" si="36"/>
+        <v>TINY</v>
+      </c>
+      <c r="K97" s="2" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L94" s="2">
-        <v>10</v>
-      </c>
-      <c r="M94" s="2" t="str">
+      <c r="L97" s="2">
+        <v>200</v>
+      </c>
+      <c r="M97" s="2" t="str">
         <f>"Reshape+Dropout+TCL+TRL"</f>
         <v>Reshape+Dropout+TCL+TRL</v>
       </c>
-      <c r="N94" s="2" t="str">
-        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)"</f>
-        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)</v>
-      </c>
-      <c r="O94" s="2" t="str">
+      <c r="N97" s="2" t="str">
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)</v>
+      </c>
+      <c r="O97" s="2" t="str">
         <f xml:space="preserve"> "(2,1,1)-type1"</f>
         <v>(2,1,1)-type1</v>
       </c>
-      <c r="P94" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)</v>
-      </c>
-      <c r="Q94" s="10">
-        <f>54528</f>
-        <v>54528</v>
-      </c>
-      <c r="R94" s="10">
-        <f>R93 -Q93 + Q94</f>
-        <v>148224</v>
-      </c>
-      <c r="S94" s="2">
-        <f xml:space="preserve"> (1-(Q94/Q92))*100</f>
-        <v>98.847155500811226</v>
-      </c>
-      <c r="T94" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="U94" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W94" s="2" t="s">
+      <c r="P97" s="2" t="str">
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)</v>
+      </c>
+      <c r="Q97" s="10">
+        <f>227416</f>
+        <v>227416</v>
+      </c>
+      <c r="R97" s="10">
+        <f>R96 -Q96 + Q97</f>
+        <v>321112</v>
+      </c>
+      <c r="S97" s="2">
+        <f xml:space="preserve"> (1-(Q97/Q95))*100</f>
+        <v>95.382056184685254</v>
+      </c>
+      <c r="T97" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U97" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W97" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="95" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F95" s="15"/>
-      <c r="G95" s="23">
-        <v>1</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I95" s="2" t="str">
+      <c r="X97" s="2">
+        <v>0.27983999300000001</v>
+      </c>
+      <c r="Y97" s="2">
+        <v>0.538259983</v>
+      </c>
+      <c r="Z97" s="2">
+        <v>0.30269998300000001</v>
+      </c>
+      <c r="AA97" s="2">
+        <v>0.55879998200000003</v>
+      </c>
+    </row>
+    <row r="98" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F98" s="15"/>
+      <c r="G98" s="20">
+        <v>1</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I98" s="2" t="str">
         <f t="shared" si="35"/>
         <v>CNN</v>
       </c>
-      <c r="J95" s="2" t="str">
-        <f t="shared" si="34"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K95" s="2" t="str">
+      <c r="J98" s="2" t="str">
+        <f t="shared" si="36"/>
+        <v>TINY</v>
+      </c>
+      <c r="K98" s="2" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L95" s="2">
-        <v>10</v>
-      </c>
-      <c r="M95" s="2" t="str">
+      <c r="L98" s="2">
+        <v>200</v>
+      </c>
+      <c r="M98" s="2" t="str">
         <f>"Reshape+Dropout+TCL+TRL"</f>
         <v>Reshape+Dropout+TCL+TRL</v>
       </c>
-      <c r="N95" s="2" t="str">
-        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)"</f>
-        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,64,6,6,10)</v>
-      </c>
-      <c r="O95" s="2" t="str">
+      <c r="N98" s="2" t="str">
+        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)"</f>
+        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)</v>
+      </c>
+      <c r="O98" s="2" t="str">
         <f xml:space="preserve"> "(2,1,1)-type2"</f>
         <v>(2,1,1)-type2</v>
       </c>
-      <c r="P95" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (10)</v>
-      </c>
-      <c r="Q95" s="10">
-        <f>54528</f>
-        <v>54528</v>
-      </c>
-      <c r="R95" s="10">
-        <f xml:space="preserve"> R94 - Q94 + Q95</f>
-        <v>148224</v>
-      </c>
-      <c r="S95" s="2">
-        <f xml:space="preserve"> (1-(Q95/Q92))*100</f>
-        <v>98.847155500811226</v>
-      </c>
-      <c r="T95" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="U95" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V95" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W95" s="2" t="s">
+      <c r="P98" s="2" t="str">
+        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)"</f>
+        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)</v>
+      </c>
+      <c r="Q98" s="10">
+        <f>227416</f>
+        <v>227416</v>
+      </c>
+      <c r="R98" s="10">
+        <f xml:space="preserve"> R97 - Q97 + Q98</f>
+        <v>321112</v>
+      </c>
+      <c r="S98" s="2">
+        <f xml:space="preserve"> (1-(Q98/Q95))*100</f>
+        <v>95.382056184685254</v>
+      </c>
+      <c r="T98" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U98" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W98" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="96" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F96" s="15"/>
-      <c r="G96" s="20">
-        <v>1</v>
-      </c>
-      <c r="H96" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I96" s="25" t="str">
-        <f t="shared" si="35"/>
-        <v>CNN</v>
-      </c>
-      <c r="J96" s="25" t="str">
-        <f t="shared" si="34"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K96" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L96" s="25">
-        <v>10</v>
-      </c>
-      <c r="M96" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N96" s="25" t="str">
-        <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)"</f>
-        <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)</v>
-      </c>
-      <c r="O96" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type1"</f>
-        <v>(8,2,2)-type1</v>
-      </c>
-      <c r="P96" s="25" t="str">
-        <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q96" s="26">
-        <f>192 + 208</f>
-        <v>400</v>
-      </c>
-      <c r="R96" s="26">
-        <f>R95 -Q95+ Q96</f>
-        <v>94096</v>
-      </c>
-      <c r="S96" s="25">
-        <f xml:space="preserve"> (1-(Q96/Q92))*100</f>
-        <v>99.991543100798211</v>
-      </c>
-      <c r="T96" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U96" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="V96" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W96" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F97" s="15"/>
-      <c r="G97" s="20">
-        <v>1</v>
-      </c>
-      <c r="H97" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I97" s="25" t="str">
-        <f t="shared" si="35"/>
-        <v>CNN</v>
-      </c>
-      <c r="J97" s="25" t="str">
-        <f t="shared" si="34"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K97" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L97" s="25">
-        <v>10</v>
-      </c>
-      <c r="M97" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N97" s="25" t="str">
-        <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)"</f>
-        <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,10)</v>
-      </c>
-      <c r="O97" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type2"</f>
-        <v>(8,2,2)-type2</v>
-      </c>
-      <c r="P97" s="25" t="str">
-        <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)"</f>
-        <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q97" s="26">
-        <f>192 + 208</f>
-        <v>400</v>
-      </c>
-      <c r="R97" s="26">
-        <f t="shared" ref="R97" si="36" xml:space="preserve"> R96 - Q96 + Q97</f>
-        <v>94096</v>
-      </c>
-      <c r="S97" s="25">
-        <f xml:space="preserve"> (1-(Q97/Q92))*100</f>
-        <v>99.991543100798211</v>
-      </c>
-      <c r="T97" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U97" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="V97" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W97" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F98" s="7"/>
-      <c r="G98" s="18"/>
-      <c r="H98" s="17"/>
-      <c r="I98" s="17"/>
-      <c r="J98" s="17"/>
-      <c r="K98" s="17"/>
-      <c r="L98" s="17"/>
-      <c r="M98" s="17"/>
-      <c r="N98" s="17"/>
-      <c r="O98" s="17"/>
-      <c r="P98" s="17"/>
-      <c r="Q98" s="17"/>
-      <c r="R98" s="17"/>
-      <c r="S98" s="17"/>
-      <c r="T98" s="17"/>
-      <c r="U98" s="17"/>
-      <c r="V98" s="17"/>
-      <c r="W98" s="17"/>
-    </row>
-    <row r="99" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F99" s="15"/>
-      <c r="G99" s="23">
-        <v>1</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="I99" s="2" t="str">
-        <f xml:space="preserve"> "CNN"</f>
-        <v>CNN</v>
-      </c>
-      <c r="J99" s="2" t="str">
+      <c r="X98" s="2">
+        <v>0.27495998100000002</v>
+      </c>
+      <c r="Y98" s="2">
+        <v>0.53253996400000003</v>
+      </c>
+      <c r="Z98" s="2">
+        <v>0.29670000099999999</v>
+      </c>
+      <c r="AA98" s="2">
+        <v>0.55689996500000005</v>
+      </c>
+    </row>
+    <row r="99" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F99" s="7"/>
+      <c r="G99" s="17"/>
+      <c r="H99" s="16"/>
+      <c r="I99" s="16"/>
+      <c r="J99" s="16"/>
+      <c r="K99" s="16"/>
+      <c r="L99" s="16"/>
+      <c r="M99" s="16"/>
+      <c r="N99" s="16"/>
+      <c r="O99" s="16"/>
+      <c r="P99" s="16"/>
+      <c r="Q99" s="16"/>
+      <c r="R99" s="16"/>
+      <c r="S99" s="16"/>
+      <c r="T99" s="16"/>
+      <c r="U99" s="16"/>
+      <c r="V99" s="16"/>
+      <c r="W99" s="16"/>
+      <c r="X99" s="16"/>
+      <c r="Y99" s="16"/>
+      <c r="Z99" s="16"/>
+      <c r="AA99" s="16"/>
+    </row>
+    <row r="100" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F100" s="15"/>
+      <c r="G100" s="20">
+        <v>1</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I100" s="2" t="str">
+        <f xml:space="preserve"> "VGG19"</f>
+        <v>VGG19</v>
+      </c>
+      <c r="J100" s="2" t="str">
         <f xml:space="preserve"> "TINY"</f>
         <v>TINY</v>
       </c>
-      <c r="K99" s="2" t="str">
+      <c r="K100" s="2" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L99" s="2">
+      <c r="L100" s="2">
         <v>200</v>
       </c>
-      <c r="M99" s="2" t="str">
+      <c r="M100" s="2" t="str">
         <f xml:space="preserve"> "Linear"</f>
         <v>Linear</v>
       </c>
-      <c r="N99" s="2" t="s">
+      <c r="N100" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="O99" s="2" t="b">
-        <f xml:space="preserve"> FALSE</f>
-        <v>0</v>
-      </c>
-      <c r="P99" s="2" t="str">
-        <f>"(128,6,6) --&gt; (1024) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (1024) --&gt; (200)</v>
-      </c>
-      <c r="Q99" s="10">
-        <f>4924616</f>
-        <v>4924616</v>
-      </c>
-      <c r="R99" s="10">
-        <f>5018312</f>
-        <v>5018312</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U99" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V99" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W99" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="100" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F100" s="15"/>
-      <c r="G100" s="23">
-        <v>1</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I100" s="2" t="str">
-        <f t="shared" ref="I100:I104" si="37" xml:space="preserve"> "CNN"</f>
-        <v>CNN</v>
-      </c>
-      <c r="J100" s="2" t="str">
-        <f t="shared" ref="J100:J104" si="38" xml:space="preserve"> "TINY"</f>
-        <v>TINY</v>
-      </c>
-      <c r="K100" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L100" s="2">
-        <v>200</v>
-      </c>
-      <c r="M100" s="2" t="str">
-        <f xml:space="preserve"> "TCL + TRL"</f>
-        <v>TCL + TRL</v>
-      </c>
-      <c r="N100" s="2" t="str">
-        <f>"tcl:: (128,6,6), trl:: (128,6,6,200)"</f>
-        <v>tcl:: (128,6,6), trl:: (128,6,6,200)</v>
       </c>
       <c r="O100" s="2" t="b">
         <f xml:space="preserve"> FALSE</f>
         <v>0</v>
       </c>
       <c r="P100" s="2" t="str">
-        <f>"(128,6,6) --&gt; (128,6,6) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (128,6,6) --&gt; (200)</v>
+        <f>"(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (200)"</f>
+        <v>(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (200)</v>
       </c>
       <c r="Q100" s="10">
-        <f>994512</f>
-        <v>994512</v>
+        <f>93102280</f>
+        <v>93102280</v>
       </c>
       <c r="R100" s="10">
-        <f xml:space="preserve"> R99 - Q99 + Q100</f>
-        <v>1088208</v>
-      </c>
-      <c r="S100" s="2">
-        <f xml:space="preserve"> (1-(Q100/Q99))*100</f>
-        <v>79.805288371722796</v>
+        <f>113126664</f>
+        <v>113126664</v>
+      </c>
+      <c r="S100" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="T100" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W100" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="X100" s="2">
+        <v>0.68415999400000005</v>
+      </c>
+      <c r="Y100" s="2">
+        <v>0.87247997499999996</v>
+      </c>
+      <c r="Z100" s="2">
+        <v>0.63669997499999997</v>
+      </c>
+      <c r="AA100" s="2">
+        <v>0.84169995799999997</v>
+      </c>
+    </row>
+    <row r="101" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F101" s="15"/>
+      <c r="G101" s="20">
+        <v>1</v>
+      </c>
+      <c r="H101" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="U100" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V100" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W100" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="101" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F101" s="15"/>
-      <c r="G101" s="23">
-        <v>1</v>
-      </c>
-      <c r="H101" s="5" t="s">
-        <v>118</v>
-      </c>
       <c r="I101" s="2" t="str">
-        <f t="shared" si="37"/>
-        <v>CNN</v>
+        <f t="shared" ref="I101:I103" si="37" xml:space="preserve"> "VGG19"</f>
+        <v>VGG19</v>
       </c>
       <c r="J101" s="2" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="J101:J103" si="38" xml:space="preserve"> "TINY"</f>
         <v>TINY</v>
       </c>
       <c r="K101" s="2" t="str">
@@ -6739,60 +7775,72 @@
         <v>200</v>
       </c>
       <c r="M101" s="2" t="str">
-        <f>"Reshape+Dropout+TCL+TRL"</f>
-        <v>Reshape+Dropout+TCL+TRL</v>
+        <f xml:space="preserve"> "TCL + TRL"</f>
+        <v>TCL + TRL</v>
       </c>
       <c r="N101" s="2" t="str">
-        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)"</f>
-        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)</v>
-      </c>
-      <c r="O101" s="2" t="str">
-        <f xml:space="preserve"> "(2,1,1)-type1"</f>
-        <v>(2,1,1)-type1</v>
+        <f>"tcl:: (512,6,6), trl:: (512,6,6,200)"</f>
+        <v>tcl:: (512,6,6), trl:: (512,6,6,200)</v>
+      </c>
+      <c r="O101" s="2" t="b">
+        <f xml:space="preserve"> FALSE</f>
+        <v>0</v>
       </c>
       <c r="P101" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)</v>
+        <f>"(512,6,6) --&gt; (512,6,6) --&gt; (200)"</f>
+        <v>(512,6,6) --&gt; (512,6,6) --&gt; (200)</v>
       </c>
       <c r="Q101" s="10">
-        <f>227416</f>
-        <v>227416</v>
+        <f>4250832</f>
+        <v>4250832</v>
       </c>
       <c r="R101" s="10">
-        <f>R100 -Q100 + Q101</f>
-        <v>321112</v>
+        <f xml:space="preserve"> R100 - Q100 + Q101</f>
+        <v>24275216</v>
       </c>
       <c r="S101" s="2">
-        <f xml:space="preserve"> (1-(Q101/Q99))*100</f>
-        <v>95.382056184685254</v>
+        <f xml:space="preserve"> (1-(Q101/Q100))*100</f>
+        <v>95.43423426365068</v>
       </c>
       <c r="T101" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="U101" s="2" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>110</v>
+      </c>
+      <c r="X101" s="2">
+        <v>0.81009995899999998</v>
+      </c>
+      <c r="Y101" s="2">
+        <v>0.95995998400000004</v>
+      </c>
+      <c r="Z101" s="2">
+        <v>0.67320001100000004</v>
+      </c>
+      <c r="AA101" s="2">
+        <v>0.87879997499999996</v>
+      </c>
+    </row>
+    <row r="102" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F102" s="15"/>
-      <c r="G102" s="23">
+      <c r="G102" s="20">
         <v>1</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I102" s="2" t="str">
         <f t="shared" si="37"/>
-        <v>CNN</v>
+        <v>VGG19</v>
       </c>
       <c r="J102" s="2" t="str">
-        <f t="shared" si="38"/>
+        <f xml:space="preserve"> "TINY"</f>
         <v>TINY</v>
       </c>
       <c r="K102" s="2" t="str">
@@ -6807,1451 +7855,306 @@
         <v>Reshape+Dropout+TCL+TRL</v>
       </c>
       <c r="N102" s="2" t="str">
-        <f>"tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)"</f>
-        <v>tcl::(2,1,1,64,6,6), trl:: (2,1,1,50,3,3,200)</v>
+        <f>"tcl::(2,2,2,256,1,1), trl:: (1,1,1,256,1,1,200)"</f>
+        <v>tcl::(2,2,2,256,1,1), trl:: (1,1,1,256,1,1,200)</v>
       </c>
       <c r="O102" s="2" t="str">
-        <f xml:space="preserve"> "(2,1,1)-type2"</f>
-        <v>(2,1,1)-type2</v>
+        <f xml:space="preserve"> "(2,2,2)-type1"</f>
+        <v>(2,2,2)-type1</v>
       </c>
       <c r="P102" s="2" t="str">
-        <f>"(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (2,1,1,64,6,6) --&gt; (2,1,1,64,6,6) --&gt; (200)</v>
+        <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (2,P1232,2,256,1,1) --&gt; (200)"</f>
+        <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (2,P1232,2,256,1,1) --&gt; (200)</v>
       </c>
       <c r="Q102" s="10">
-        <f>227416</f>
-        <v>227416</v>
+        <f>666714</f>
+        <v>666714</v>
       </c>
       <c r="R102" s="10">
-        <f xml:space="preserve"> R101 - Q101 + Q102</f>
-        <v>321112</v>
+        <f>R101 -Q101 + Q102</f>
+        <v>20691098</v>
       </c>
       <c r="S102" s="2">
-        <f xml:space="preserve"> (1-(Q102/Q99))*100</f>
-        <v>95.382056184685254</v>
+        <f xml:space="preserve"> (1-(Q102/Q100))*100</f>
+        <v>99.283890791933345</v>
       </c>
       <c r="T102" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="U102" s="2" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="V102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="103" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>110</v>
+      </c>
+      <c r="X102" s="2">
+        <v>0.77741998400000001</v>
+      </c>
+      <c r="Y102" s="2">
+        <v>0.93988996700000005</v>
+      </c>
+      <c r="Z102" s="2">
+        <v>0.68919998400000004</v>
+      </c>
+      <c r="AA102" s="2">
+        <v>0.88169997899999997</v>
+      </c>
+    </row>
+    <row r="103" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F103" s="15"/>
       <c r="G103" s="20">
         <v>1</v>
       </c>
-      <c r="H103" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I103" s="25" t="str">
+      <c r="H103" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I103" s="2" t="str">
         <f t="shared" si="37"/>
-        <v>CNN</v>
-      </c>
-      <c r="J103" s="25" t="str">
+        <v>VGG19</v>
+      </c>
+      <c r="J103" s="2" t="str">
         <f t="shared" si="38"/>
         <v>TINY</v>
       </c>
-      <c r="K103" s="25" t="str">
+      <c r="K103" s="2" t="str">
+        <f xml:space="preserve"> "(3,192,192)"</f>
+        <v>(3,192,192)</v>
+      </c>
+      <c r="L103" s="2">
+        <v>200</v>
+      </c>
+      <c r="M103" s="2" t="str">
+        <f>"Reshape+Dropout+TCL+TRL"</f>
+        <v>Reshape+Dropout+TCL+TRL</v>
+      </c>
+      <c r="N103" s="2" t="str">
+        <f>"tcl::(2,2,2,256,1,1), trl:: (1,1,1,256,1,1,200)"</f>
+        <v>tcl::(2,2,2,256,1,1), trl:: (1,1,1,256,1,1,200)</v>
+      </c>
+      <c r="O103" s="2" t="str">
+        <f xml:space="preserve"> "(2,2,2)-type2"</f>
+        <v>(2,2,2)-type2</v>
+      </c>
+      <c r="P103" s="2" t="str">
+        <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (2,2,2,256,1,1) --&gt; (200)"</f>
+        <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (2,2,2,256,1,1) --&gt; (200)</v>
+      </c>
+      <c r="Q103" s="10">
+        <f>666714</f>
+        <v>666714</v>
+      </c>
+      <c r="R103" s="10">
+        <f xml:space="preserve"> R102 - Q102 + Q103</f>
+        <v>20691098</v>
+      </c>
+      <c r="S103" s="2">
+        <f xml:space="preserve"> (1-(Q103/Q100))*100</f>
+        <v>99.283890791933345</v>
+      </c>
+      <c r="T103" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="X103" s="2">
+        <v>0.77881997800000002</v>
+      </c>
+      <c r="Y103" s="2">
+        <v>0.939239979</v>
+      </c>
+      <c r="Z103" s="2">
+        <v>0.67680001300000003</v>
+      </c>
+      <c r="AA103" s="2">
+        <v>0.88159996299999999</v>
+      </c>
+    </row>
+    <row r="104" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F104" s="15"/>
+      <c r="G104" s="20"/>
+      <c r="H104" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K104" s="2" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L103" s="25">
+      <c r="L104" s="2">
         <v>200</v>
       </c>
-      <c r="M103" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N103" s="25" t="str">
-        <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,50)"</f>
-        <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,50)</v>
-      </c>
-      <c r="O103" s="25" t="str">
+      <c r="M104" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="N104" s="2" t="str">
+        <f>"tcl::(6,2,2,64,3,3), trl:: (4,2,2,64,1,1,200)"</f>
+        <v>tcl::(6,2,2,64,3,3), trl:: (4,2,2,64,1,1,200)</v>
+      </c>
+      <c r="O104" s="2" t="str">
         <f xml:space="preserve"> "(8,2,2)-type1"</f>
         <v>(8,2,2)-type1</v>
       </c>
-      <c r="P103" s="25" t="str">
-        <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (200)</v>
-      </c>
-      <c r="Q103" s="26">
-        <f>192 + 10308</f>
-        <v>10500</v>
-      </c>
-      <c r="R103" s="26">
-        <f>R102 -Q102+ Q103</f>
-        <v>104196</v>
-      </c>
-      <c r="S103" s="25">
-        <f xml:space="preserve"> (1-(Q103/Q99))*100</f>
-        <v>99.786785406212388</v>
-      </c>
-      <c r="T103" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U103" s="25" t="s">
+      <c r="P104" s="2" t="str">
+        <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (8,2,2,64,3,3) --&gt; (200)"</f>
+        <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (8,2,2,64,3,3) --&gt; (200)</v>
+      </c>
+      <c r="Q104" s="10">
+        <v>253104</v>
+      </c>
+      <c r="R104" s="10">
+        <v>20277488</v>
+      </c>
+      <c r="S104" s="2">
+        <f xml:space="preserve"> (1-(Q104/Q100))*100</f>
+        <v>99.728144144268001</v>
+      </c>
+      <c r="T104" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="V103" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W103" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="104" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F104" s="15"/>
-      <c r="G104" s="20">
-        <v>1</v>
-      </c>
-      <c r="H104" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I104" s="25" t="str">
-        <f t="shared" si="37"/>
-        <v>CNN</v>
-      </c>
-      <c r="J104" s="25" t="str">
-        <f t="shared" si="38"/>
-        <v>TINY</v>
-      </c>
-      <c r="K104" s="25" t="str">
+      <c r="U104" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="X104" s="2">
+        <v>0.78709995700000002</v>
+      </c>
+      <c r="Y104" s="2">
+        <v>0.94349998199999996</v>
+      </c>
+      <c r="Z104" s="2">
+        <v>0.68669998600000004</v>
+      </c>
+      <c r="AA104" s="2">
+        <v>0.88330000600000003</v>
+      </c>
+    </row>
+    <row r="105" spans="6:27" ht="43.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F105" s="15"/>
+      <c r="G105" s="20"/>
+      <c r="H105" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K105" s="2" t="str">
         <f t="shared" si="31"/>
         <v>(3,192,192)</v>
       </c>
-      <c r="L104" s="25">
+      <c r="L105" s="2">
         <v>200</v>
       </c>
-      <c r="M104" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N104" s="25" t="str">
-        <f>"tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,50)"</f>
-        <v>tcl::(2,1,1,10,2,2), trl:: (1,1,1,5,1,1,50)</v>
-      </c>
-      <c r="O104" s="25" t="str">
+      <c r="M105" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="N105" s="2" t="str">
+        <f>"tcl::(6,2,2,64,3,3), trl:: (4,2,2,64,1,1,200)"</f>
+        <v>tcl::(6,2,2,64,3,3), trl:: (4,2,2,64,1,1,200)</v>
+      </c>
+      <c r="O105" s="2" t="str">
         <f xml:space="preserve"> "(8,2,2)-type2"</f>
         <v>(8,2,2)-type2</v>
       </c>
-      <c r="P104" s="25" t="str">
-        <f>"(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (200)"</f>
-        <v>(128,6,6) --&gt; (8,2,2,16,3,3) --&gt; (2,1,1,10,2,2) --&gt; (200)</v>
-      </c>
-      <c r="Q104" s="26">
-        <f>192 + 10308</f>
-        <v>10500</v>
-      </c>
-      <c r="R104" s="26">
-        <f t="shared" ref="R104" si="39" xml:space="preserve"> R103 - Q103 + Q104</f>
-        <v>104196</v>
-      </c>
-      <c r="S104" s="25">
-        <f xml:space="preserve"> (1-(Q104/Q99))*100</f>
-        <v>99.786785406212388</v>
-      </c>
-      <c r="T104" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U104" s="25" t="s">
+      <c r="P105" s="2" t="str">
+        <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (8,2,2,64,3,3) --&gt; (200)"</f>
+        <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (8,2,2,64,3,3) --&gt; (200)</v>
+      </c>
+      <c r="Q105" s="10">
+        <v>253104</v>
+      </c>
+      <c r="R105" s="10">
+        <v>20277488</v>
+      </c>
+      <c r="S105" s="2">
+        <f xml:space="preserve"> (1-(Q105/Q100))*100</f>
+        <v>99.728144144268001</v>
+      </c>
+      <c r="T105" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="V104" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W104" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="105" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F105" s="7"/>
-      <c r="G105" s="18"/>
-      <c r="H105" s="17"/>
-      <c r="I105" s="17"/>
-      <c r="J105" s="17"/>
-      <c r="K105" s="17"/>
-      <c r="L105" s="17"/>
-      <c r="M105" s="17"/>
-      <c r="N105" s="17"/>
-      <c r="O105" s="17"/>
-      <c r="P105" s="17"/>
-      <c r="Q105" s="17"/>
-      <c r="R105" s="17"/>
-      <c r="S105" s="17"/>
-      <c r="T105" s="17"/>
-      <c r="U105" s="17"/>
-      <c r="V105" s="17"/>
-      <c r="W105" s="17"/>
-    </row>
-    <row r="106" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F106" s="15"/>
-      <c r="G106" s="20">
-        <v>1</v>
-      </c>
-      <c r="H106" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I106" s="25" t="str">
-        <f xml:space="preserve"> "VGG19"</f>
-        <v>VGG19</v>
-      </c>
-      <c r="J106" s="25" t="str">
-        <f t="shared" ref="J106:J111" si="40" xml:space="preserve"> "MNIST"</f>
-        <v>MNIST</v>
-      </c>
-      <c r="K106" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L106" s="25">
-        <v>10</v>
-      </c>
-      <c r="M106" s="25" t="str">
-        <f xml:space="preserve"> "Linear"</f>
-        <v>Linear</v>
-      </c>
-      <c r="N106" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="O106" s="25" t="b">
-        <f xml:space="preserve"> FALSE</f>
-        <v>0</v>
-      </c>
-      <c r="P106" s="25" t="str">
-        <f>"(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (10)</v>
-      </c>
-      <c r="Q106" s="26">
-        <f>92323850</f>
-        <v>92323850</v>
-      </c>
-      <c r="R106" s="26">
-        <f>112348234</f>
-        <v>112348234</v>
-      </c>
-      <c r="S106" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="T106" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U106" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V106" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W106" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="107" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F107" s="15"/>
-      <c r="G107" s="20">
-        <v>1</v>
-      </c>
-      <c r="H107" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I107" s="25" t="str">
-        <f t="shared" ref="I107:I111" si="41" xml:space="preserve"> "VGG19"</f>
-        <v>VGG19</v>
-      </c>
-      <c r="J107" s="25" t="str">
-        <f t="shared" si="40"/>
-        <v>MNIST</v>
-      </c>
-      <c r="K107" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L107" s="25">
-        <v>10</v>
-      </c>
-      <c r="M107" s="25" t="str">
-        <f xml:space="preserve"> "TCL + TRL"</f>
-        <v>TCL + TRL</v>
-      </c>
-      <c r="N107" s="25" t="str">
-        <f>"tcl:: (350,4,4), trl:: (150,1,1,10)"</f>
-        <v>tcl:: (350,4,4), trl:: (150,1,1,10)</v>
-      </c>
-      <c r="O107" s="25" t="b">
-        <f xml:space="preserve"> FALSE</f>
-        <v>0</v>
-      </c>
-      <c r="P107" s="25" t="str">
-        <f>"(512,6,6) --&gt; (350,4,4) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (350,4,4) --&gt; (10)</v>
-      </c>
-      <c r="Q107" s="26">
-        <f>179248 + 54108</f>
-        <v>233356</v>
-      </c>
-      <c r="R107" s="26">
-        <f xml:space="preserve"> R106 - Q106 + Q107</f>
-        <v>20257740</v>
-      </c>
-      <c r="S107" s="25">
-        <f xml:space="preserve"> (1-(Q107/Q106))*100</f>
-        <v>99.74724190986403</v>
-      </c>
-      <c r="T107" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U107" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V107" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W107" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="108" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F108" s="15"/>
-      <c r="G108" s="20">
-        <v>1</v>
-      </c>
-      <c r="H108" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I108" s="25" t="str">
-        <f t="shared" si="41"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J108" s="25" t="str">
-        <f t="shared" si="40"/>
-        <v>MNIST</v>
-      </c>
-      <c r="K108" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L108" s="25">
-        <v>10</v>
-      </c>
-      <c r="M108" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N108" s="25" t="str">
-        <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)"</f>
-        <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)</v>
-      </c>
-      <c r="O108" s="25" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type1"</f>
-        <v>(2,2,2)-type1</v>
-      </c>
-      <c r="P108" s="25" t="str">
-        <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q108" s="26">
-        <f>25618 + 5607</f>
-        <v>31225</v>
-      </c>
-      <c r="R108" s="26">
-        <f>R107 -Q107 + Q108</f>
-        <v>20055609</v>
-      </c>
-      <c r="S108" s="25">
-        <f xml:space="preserve"> (1-(Q108/Q106))*100</f>
-        <v>99.966178836779434</v>
-      </c>
-      <c r="T108" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U108" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V108" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W108" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="109" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F109" s="15"/>
-      <c r="G109" s="20">
-        <v>1</v>
-      </c>
-      <c r="H109" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I109" s="25" t="str">
-        <f t="shared" si="41"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J109" s="25" t="str">
-        <f t="shared" si="40"/>
-        <v>MNIST</v>
-      </c>
-      <c r="K109" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L109" s="25">
-        <v>10</v>
-      </c>
-      <c r="M109" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N109" s="25" t="str">
-        <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)"</f>
-        <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)</v>
-      </c>
-      <c r="O109" s="25" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type2"</f>
-        <v>(2,2,2)-type2</v>
-      </c>
-      <c r="P109" s="25" t="str">
-        <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q109" s="26">
-        <f>25618 + 5607</f>
-        <v>31225</v>
-      </c>
-      <c r="R109" s="26">
-        <f xml:space="preserve"> R108 - Q108 + Q109</f>
-        <v>20055609</v>
-      </c>
-      <c r="S109" s="25">
-        <f xml:space="preserve"> (1-(Q109/Q106))*100</f>
-        <v>99.966178836779434</v>
-      </c>
-      <c r="T109" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U109" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V109" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W109" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="110" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F110" s="15"/>
-      <c r="G110" s="20">
-        <v>1</v>
-      </c>
-      <c r="H110" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I110" s="25" t="str">
-        <f t="shared" si="41"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J110" s="25" t="str">
-        <f t="shared" si="40"/>
-        <v>MNIST</v>
-      </c>
-      <c r="K110" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L110" s="25">
-        <v>10</v>
-      </c>
-      <c r="M110" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N110" s="25" t="str">
-        <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)"</f>
-        <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)</v>
-      </c>
-      <c r="O110" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type1"</f>
-        <v>(8,2,2)-type1</v>
-      </c>
-      <c r="P110" s="25" t="str">
-        <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q110" s="26">
-        <f>2592 + 608</f>
-        <v>3200</v>
-      </c>
-      <c r="R110" s="26">
-        <f>R109 -Q109+ Q110</f>
-        <v>20027584</v>
-      </c>
-      <c r="S110" s="25">
-        <f xml:space="preserve"> (1-(Q110/Q106))*100</f>
-        <v>99.996533940038248</v>
-      </c>
-      <c r="T110" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U110" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V110" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W110" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="111" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F111" s="15"/>
-      <c r="G111" s="20">
-        <v>1</v>
-      </c>
-      <c r="H111" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I111" s="25" t="str">
-        <f t="shared" si="41"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J111" s="25" t="str">
-        <f t="shared" si="40"/>
-        <v>MNIST</v>
-      </c>
-      <c r="K111" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L111" s="25">
-        <v>10</v>
-      </c>
-      <c r="M111" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N111" s="25" t="str">
-        <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)"</f>
-        <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)</v>
-      </c>
-      <c r="O111" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type2"</f>
-        <v>(8,2,2)-type2</v>
-      </c>
-      <c r="P111" s="25" t="str">
-        <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q111" s="26">
-        <f>2592 + 608</f>
-        <v>3200</v>
-      </c>
-      <c r="R111" s="26">
-        <f t="shared" ref="R111" si="42" xml:space="preserve"> R110 - Q110 + Q111</f>
-        <v>20027584</v>
-      </c>
-      <c r="S111" s="25">
-        <f xml:space="preserve"> (1-(Q111/Q106))*100</f>
-        <v>99.996533940038248</v>
-      </c>
-      <c r="T111" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U111" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V111" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W111" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F112" s="7"/>
-      <c r="G112" s="18"/>
-      <c r="H112" s="17"/>
-      <c r="I112" s="17"/>
-      <c r="J112" s="17"/>
-      <c r="K112" s="17"/>
-      <c r="L112" s="17"/>
-      <c r="M112" s="17"/>
-      <c r="N112" s="17"/>
-      <c r="O112" s="17"/>
-      <c r="P112" s="17"/>
-      <c r="Q112" s="17"/>
-      <c r="R112" s="17"/>
-      <c r="S112" s="17"/>
-      <c r="T112" s="17"/>
-      <c r="U112" s="17"/>
-      <c r="V112" s="17"/>
-      <c r="W112" s="17"/>
-    </row>
-    <row r="113" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F113" s="15"/>
-      <c r="G113" s="20">
-        <v>1</v>
-      </c>
-      <c r="H113" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I113" s="25" t="str">
-        <f xml:space="preserve"> "VGG19"</f>
-        <v>VGG19</v>
-      </c>
-      <c r="J113" s="25" t="str">
-        <f xml:space="preserve"> "CIFAR10"</f>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K113" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L113" s="25">
-        <v>10</v>
-      </c>
-      <c r="M113" s="25" t="str">
-        <f xml:space="preserve"> "Linear"</f>
-        <v>Linear</v>
-      </c>
-      <c r="N113" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="O113" s="25" t="b">
-        <f xml:space="preserve"> FALSE</f>
-        <v>0</v>
-      </c>
-      <c r="P113" s="25" t="str">
-        <f>"(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (10)</v>
-      </c>
-      <c r="Q113" s="26">
-        <f>92323850</f>
-        <v>92323850</v>
-      </c>
-      <c r="R113" s="26">
-        <f>112348234</f>
-        <v>112348234</v>
-      </c>
-      <c r="S113" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="T113" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U113" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V113" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W113" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="114" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F114" s="15"/>
-      <c r="G114" s="20">
-        <v>1</v>
-      </c>
-      <c r="H114" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I114" s="25" t="str">
-        <f t="shared" ref="I114:I118" si="43" xml:space="preserve"> "VGG19"</f>
-        <v>VGG19</v>
-      </c>
-      <c r="J114" s="25" t="str">
-        <f t="shared" ref="J114:J118" si="44" xml:space="preserve"> "CIFAR10"</f>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K114" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L114" s="25">
-        <v>10</v>
-      </c>
-      <c r="M114" s="25" t="str">
-        <f xml:space="preserve"> "TCL + TRL"</f>
-        <v>TCL + TRL</v>
-      </c>
-      <c r="N114" s="25" t="str">
-        <f>"tcl:: (350,4,4), trl:: (150,1,1,10)"</f>
-        <v>tcl:: (350,4,4), trl:: (150,1,1,10)</v>
-      </c>
-      <c r="O114" s="25" t="b">
-        <f xml:space="preserve"> FALSE</f>
-        <v>0</v>
-      </c>
-      <c r="P114" s="25" t="str">
-        <f>"(512,6,6) --&gt; (350,4,4) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (350,4,4) --&gt; (10)</v>
-      </c>
-      <c r="Q114" s="26">
-        <f>179248 + 54108</f>
-        <v>233356</v>
-      </c>
-      <c r="R114" s="26">
-        <f xml:space="preserve"> R113 - Q113 + Q114</f>
-        <v>20257740</v>
-      </c>
-      <c r="S114" s="25">
-        <f xml:space="preserve"> (1-(Q114/Q113))*100</f>
-        <v>99.74724190986403</v>
-      </c>
-      <c r="T114" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U114" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V114" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W114" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="115" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F115" s="15"/>
-      <c r="G115" s="20">
-        <v>1</v>
-      </c>
-      <c r="H115" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I115" s="25" t="str">
-        <f t="shared" si="43"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J115" s="25" t="str">
-        <f t="shared" si="44"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K115" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L115" s="25">
-        <v>10</v>
-      </c>
-      <c r="M115" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N115" s="25" t="str">
-        <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)"</f>
-        <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)</v>
-      </c>
-      <c r="O115" s="25" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type1"</f>
-        <v>(2,2,2)-type1</v>
-      </c>
-      <c r="P115" s="25" t="str">
-        <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q115" s="26">
-        <f>25618 + 5607</f>
-        <v>31225</v>
-      </c>
-      <c r="R115" s="26">
-        <f>R114 -Q114 + Q115</f>
-        <v>20055609</v>
-      </c>
-      <c r="S115" s="25">
-        <f xml:space="preserve"> (1-(Q115/Q113))*100</f>
-        <v>99.966178836779434</v>
-      </c>
-      <c r="T115" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U115" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V115" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W115" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="116" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F116" s="15"/>
-      <c r="G116" s="20">
-        <v>1</v>
-      </c>
-      <c r="H116" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I116" s="25" t="str">
-        <f t="shared" si="43"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J116" s="25" t="str">
-        <f t="shared" si="44"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K116" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L116" s="25">
-        <v>10</v>
-      </c>
-      <c r="M116" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N116" s="25" t="str">
-        <f>"tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)"</f>
-        <v>tcl::(1,1,1,100,2,2), trl:: (1,1,1,50,1,1,10)</v>
-      </c>
-      <c r="O116" s="25" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type2"</f>
-        <v>(2,2,2)-type2</v>
-      </c>
-      <c r="P116" s="25" t="str">
-        <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q116" s="26">
-        <f>25618 + 5607</f>
-        <v>31225</v>
-      </c>
-      <c r="R116" s="26">
-        <f xml:space="preserve"> R115 - Q115 + Q116</f>
-        <v>20055609</v>
-      </c>
-      <c r="S116" s="25">
-        <f xml:space="preserve"> (1-(Q116/Q113))*100</f>
-        <v>99.966178836779434</v>
-      </c>
-      <c r="T116" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U116" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V116" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W116" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F117" s="15"/>
-      <c r="G117" s="20">
-        <v>1</v>
-      </c>
-      <c r="H117" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I117" s="25" t="str">
-        <f t="shared" si="43"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J117" s="25" t="str">
-        <f t="shared" si="44"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K117" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L117" s="25">
-        <v>10</v>
-      </c>
-      <c r="M117" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N117" s="25" t="str">
-        <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)"</f>
-        <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)</v>
-      </c>
-      <c r="O117" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type1"</f>
-        <v>(8,2,2)-type1</v>
-      </c>
-      <c r="P117" s="25" t="str">
-        <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q117" s="26">
-        <f>2592 + 608</f>
-        <v>3200</v>
-      </c>
-      <c r="R117" s="26">
-        <f>R116 -Q116+ Q117</f>
-        <v>20027584</v>
-      </c>
-      <c r="S117" s="25">
-        <f xml:space="preserve"> (1-(Q117/Q113))*100</f>
-        <v>99.996533940038248</v>
-      </c>
-      <c r="T117" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U117" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V117" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W117" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="118" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F118" s="15"/>
-      <c r="G118" s="20">
-        <v>1</v>
-      </c>
-      <c r="H118" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I118" s="25" t="str">
-        <f t="shared" si="43"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J118" s="25" t="str">
-        <f t="shared" si="44"/>
-        <v>CIFAR10</v>
-      </c>
-      <c r="K118" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L118" s="25">
-        <v>10</v>
-      </c>
-      <c r="M118" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N118" s="25" t="str">
-        <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)"</f>
-        <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,10)</v>
-      </c>
-      <c r="O118" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type2"</f>
-        <v>(8,2,2)-type2</v>
-      </c>
-      <c r="P118" s="25" t="str">
-        <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)"</f>
-        <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (10)</v>
-      </c>
-      <c r="Q118" s="26">
-        <f>2592 + 608</f>
-        <v>3200</v>
-      </c>
-      <c r="R118" s="26">
-        <f t="shared" ref="R118" si="45" xml:space="preserve"> R117 - Q117 + Q118</f>
-        <v>20027584</v>
-      </c>
-      <c r="S118" s="25">
-        <f xml:space="preserve"> (1-(Q118/Q113))*100</f>
-        <v>99.996533940038248</v>
-      </c>
-      <c r="T118" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U118" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V118" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W118" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="119" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F119" s="7"/>
-      <c r="G119" s="18"/>
-      <c r="H119" s="17"/>
-      <c r="I119" s="17"/>
-      <c r="J119" s="17"/>
-      <c r="K119" s="17"/>
-      <c r="L119" s="17"/>
-      <c r="M119" s="17"/>
-      <c r="N119" s="17"/>
-      <c r="O119" s="17"/>
-      <c r="P119" s="17"/>
-      <c r="Q119" s="17"/>
-      <c r="R119" s="17"/>
-      <c r="S119" s="17"/>
-      <c r="T119" s="17"/>
-      <c r="U119" s="17"/>
-      <c r="V119" s="17"/>
-      <c r="W119" s="17"/>
-    </row>
-    <row r="120" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F120" s="15"/>
-      <c r="G120" s="23">
-        <v>1</v>
-      </c>
-      <c r="H120" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="I120" s="2" t="str">
-        <f xml:space="preserve"> "VGG19"</f>
-        <v>VGG19</v>
-      </c>
-      <c r="J120" s="2" t="str">
-        <f xml:space="preserve"> "TINY"</f>
-        <v>TINY</v>
-      </c>
-      <c r="K120" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L120" s="2">
-        <v>200</v>
-      </c>
-      <c r="M120" s="2" t="str">
-        <f xml:space="preserve"> "Linear"</f>
-        <v>Linear</v>
-      </c>
-      <c r="N120" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="O120" s="2" t="b">
-        <f xml:space="preserve"> FALSE</f>
-        <v>0</v>
-      </c>
-      <c r="P120" s="2" t="str">
-        <f>"(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (200)"</f>
-        <v>(512,6,6) --&gt; (4096) --&gt; (4096) --&gt; (200)</v>
-      </c>
-      <c r="Q120" s="10">
-        <f>93102280</f>
-        <v>93102280</v>
-      </c>
-      <c r="R120" s="10">
-        <f>113126664</f>
-        <v>113126664</v>
-      </c>
-      <c r="S120" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T120" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U120" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V120" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W120" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="121" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F121" s="15"/>
-      <c r="G121" s="19">
-        <v>1</v>
-      </c>
-      <c r="H121" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I121" s="2" t="str">
-        <f t="shared" ref="I121:I125" si="46" xml:space="preserve"> "VGG19"</f>
-        <v>VGG19</v>
-      </c>
-      <c r="J121" s="2" t="str">
-        <f t="shared" ref="J121:J125" si="47" xml:space="preserve"> "TINY"</f>
-        <v>TINY</v>
-      </c>
-      <c r="K121" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L121" s="2">
-        <v>200</v>
-      </c>
-      <c r="M121" s="2" t="str">
-        <f xml:space="preserve"> "TCL + TRL"</f>
-        <v>TCL + TRL</v>
-      </c>
-      <c r="N121" s="2" t="str">
-        <f>"tcl:: (512,6,6), trl:: (512,6,6,200)"</f>
-        <v>tcl:: (512,6,6), trl:: (512,6,6,200)</v>
-      </c>
-      <c r="O121" s="2" t="b">
-        <f xml:space="preserve"> FALSE</f>
-        <v>0</v>
-      </c>
-      <c r="P121" s="2" t="str">
-        <f>"(512,6,6) --&gt; (512,6,6) --&gt; (200)"</f>
-        <v>(512,6,6) --&gt; (512,6,6) --&gt; (200)</v>
-      </c>
-      <c r="Q121" s="10">
-        <f>4250832</f>
-        <v>4250832</v>
-      </c>
-      <c r="R121" s="10">
-        <f xml:space="preserve"> R120 - Q120 + Q121</f>
-        <v>24275216</v>
-      </c>
-      <c r="S121" s="2">
-        <f xml:space="preserve"> (1-(Q121/Q120))*100</f>
-        <v>95.43423426365068</v>
-      </c>
-      <c r="T121" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U121" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V121" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W121" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="122" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F122" s="15"/>
-      <c r="G122" s="19">
-        <v>1</v>
-      </c>
-      <c r="H122" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="I122" s="2" t="str">
-        <f t="shared" si="46"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J122" s="2" t="str">
-        <f t="shared" si="47"/>
-        <v>TINY</v>
-      </c>
-      <c r="K122" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L122" s="2">
-        <v>200</v>
-      </c>
-      <c r="M122" s="2" t="str">
-        <f>"Reshape+Dropout+TCL+TRL"</f>
-        <v>Reshape+Dropout+TCL+TRL</v>
-      </c>
-      <c r="N122" s="2" t="str">
-        <f>"tcl::(2,2,2,512,1,1), trl:: (1,1,1,512,1,1,200)"</f>
-        <v>tcl::(2,2,2,512,1,1), trl:: (1,1,1,512,1,1,200)</v>
-      </c>
-      <c r="O122" s="2" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type1"</f>
-        <v>(2,2,2)-type1</v>
-      </c>
-      <c r="P122" s="2" t="str">
-        <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (200)"</f>
-        <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (200)</v>
-      </c>
-      <c r="Q122" s="10">
-        <f>666714</f>
-        <v>666714</v>
-      </c>
-      <c r="R122" s="10">
-        <f>R121 -Q121 + Q122</f>
-        <v>20691098</v>
-      </c>
-      <c r="S122" s="2">
-        <f xml:space="preserve"> (1-(Q122/Q120))*100</f>
-        <v>99.283890791933345</v>
-      </c>
-      <c r="T122" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U122" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V122" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W122" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="123" spans="6:23" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F123" s="15"/>
-      <c r="G123" s="19">
-        <v>1</v>
-      </c>
-      <c r="H123" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I123" s="2" t="str">
-        <f t="shared" si="46"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J123" s="2" t="str">
-        <f t="shared" si="47"/>
-        <v>TINY</v>
-      </c>
-      <c r="K123" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L123" s="2">
-        <v>200</v>
-      </c>
-      <c r="M123" s="2" t="str">
-        <f>"Reshape+Dropout+TCL+TRL"</f>
-        <v>Reshape+Dropout+TCL+TRL</v>
-      </c>
-      <c r="N123" s="2" t="str">
-        <f>"tcl::(2,2,2,512,1,1), trl:: (1,1,1,512,1,1,200)"</f>
-        <v>tcl::(2,2,2,512,1,1), trl:: (1,1,1,512,1,1,200)</v>
-      </c>
-      <c r="O123" s="2" t="str">
-        <f xml:space="preserve"> "(2,2,2)-type2"</f>
-        <v>(2,2,2)-type2</v>
-      </c>
-      <c r="P123" s="2" t="str">
-        <f>"(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (200)"</f>
-        <v>(512,6,6) --&gt; (2,2,2,256,3,3) --&gt; (1,1,1,100,2,2) --&gt; (200)</v>
-      </c>
-      <c r="Q123" s="10">
-        <f>666714</f>
-        <v>666714</v>
-      </c>
-      <c r="R123" s="10">
-        <f xml:space="preserve"> R122 - Q122 + Q123</f>
-        <v>20691098</v>
-      </c>
-      <c r="S123" s="2">
-        <f xml:space="preserve"> (1-(Q123/Q120))*100</f>
-        <v>99.283890791933345</v>
-      </c>
-      <c r="T123" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U123" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V123" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W123" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="124" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F124" s="15"/>
-      <c r="G124" s="20">
-        <v>1</v>
-      </c>
-      <c r="H124" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I124" s="25" t="str">
-        <f t="shared" si="46"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J124" s="25" t="str">
-        <f t="shared" si="47"/>
-        <v>TINY</v>
-      </c>
-      <c r="K124" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L124" s="25">
-        <v>200</v>
-      </c>
-      <c r="M124" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N124" s="25" t="str">
-        <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,200)"</f>
-        <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,200)</v>
-      </c>
-      <c r="O124" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type1"</f>
-        <v>(8,2,2)-type1</v>
-      </c>
-      <c r="P124" s="25" t="str">
-        <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (200)"</f>
-        <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (200)</v>
-      </c>
-      <c r="Q124" s="26">
-        <f>2592 + 42408</f>
-        <v>45000</v>
-      </c>
-      <c r="R124" s="26">
-        <f>R123 -Q123+ Q124</f>
-        <v>20069384</v>
-      </c>
-      <c r="S124" s="25">
-        <f xml:space="preserve"> (1-(Q124/Q120))*100</f>
-        <v>99.951666060165238</v>
-      </c>
-      <c r="T124" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U124" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V124" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W124" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="125" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F125" s="15"/>
-      <c r="G125" s="20">
-        <v>1</v>
-      </c>
-      <c r="H125" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I125" s="25" t="str">
-        <f t="shared" si="46"/>
-        <v>VGG19</v>
-      </c>
-      <c r="J125" s="25" t="str">
-        <f t="shared" si="47"/>
-        <v>TINY</v>
-      </c>
-      <c r="K125" s="25" t="str">
-        <f t="shared" si="31"/>
-        <v>(3,192,192)</v>
-      </c>
-      <c r="L125" s="25">
-        <v>200</v>
-      </c>
-      <c r="M125" s="25" t="str">
-        <f>"Reshape+TCL+TRL"</f>
-        <v>Reshape+TCL+TRL</v>
-      </c>
-      <c r="N125" s="25" t="str">
-        <f>"tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,200)"</f>
-        <v>tcl::(2,1,1,40,2,2), trl:: (1,1,1,10,1,1,200)</v>
-      </c>
-      <c r="O125" s="25" t="str">
-        <f xml:space="preserve"> "(8,2,2)-type2"</f>
-        <v>(8,2,2)-type2</v>
-      </c>
-      <c r="P125" s="25" t="str">
-        <f>"(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (200)"</f>
-        <v>(512,6,6) --&gt; (8,2,2,64,3,3) --&gt; (2,1,1,40,2,2) --&gt; (200)</v>
-      </c>
-      <c r="Q125" s="26">
-        <f>2592 + 42408</f>
-        <v>45000</v>
-      </c>
-      <c r="R125" s="26">
-        <f t="shared" ref="R125" si="48" xml:space="preserve"> R124 - Q124 + Q125</f>
-        <v>20069384</v>
-      </c>
-      <c r="S125" s="25">
-        <f xml:space="preserve"> (1-(Q125/Q120))*100</f>
-        <v>99.951666060165238</v>
-      </c>
-      <c r="T125" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U125" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="V125" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W125" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="126" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F126" s="7"/>
-      <c r="G126" s="18"/>
-      <c r="H126" s="17"/>
-      <c r="I126" s="17"/>
-      <c r="J126" s="17"/>
-      <c r="K126" s="17"/>
-      <c r="L126" s="17"/>
-      <c r="M126" s="17"/>
-      <c r="N126" s="17"/>
-      <c r="O126" s="17"/>
-      <c r="P126" s="17"/>
-      <c r="Q126" s="17"/>
-      <c r="R126" s="17"/>
-      <c r="S126" s="17"/>
-      <c r="T126" s="17"/>
-      <c r="U126" s="17"/>
-      <c r="V126" s="17"/>
-      <c r="W126" s="17"/>
-    </row>
-    <row r="127" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F127" s="15"/>
-      <c r="G127" s="16"/>
-      <c r="H127" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="128" spans="6:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F128" s="15"/>
-      <c r="G128" s="16"/>
-      <c r="H128" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="129" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F129" s="15"/>
-      <c r="G129" s="16"/>
-      <c r="H129" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="130" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F130" s="15"/>
-      <c r="G130" s="16"/>
-      <c r="H130" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="131" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F131" s="15"/>
-      <c r="G131" s="16"/>
-      <c r="H131" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="132" spans="6:8" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F132" s="15"/>
-      <c r="G132" s="16"/>
-      <c r="H132" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="133" spans="6:8" ht="21.75" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="H133" s="8"/>
-    </row>
-    <row r="134" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="H134" s="8"/>
+      <c r="U105" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W105" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="X105" s="2">
+        <v>0.78242999300000005</v>
+      </c>
+      <c r="Y105" s="2">
+        <v>0.94028997400000003</v>
+      </c>
+      <c r="Z105" s="2">
+        <v>0.68299996900000004</v>
+      </c>
+      <c r="AA105" s="2">
+        <v>0.88349997999999996</v>
+      </c>
+    </row>
+    <row r="106" spans="6:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="F106" s="7"/>
+      <c r="G106" s="17"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="16"/>
+      <c r="K106" s="16"/>
+      <c r="L106" s="16"/>
+      <c r="M106" s="16"/>
+      <c r="N106" s="16"/>
+      <c r="O106" s="16"/>
+      <c r="P106" s="16"/>
+      <c r="Q106" s="16"/>
+      <c r="R106" s="16"/>
+      <c r="S106" s="16"/>
+      <c r="T106" s="16"/>
+      <c r="U106" s="16"/>
+      <c r="V106" s="16"/>
+      <c r="W106" s="16"/>
+      <c r="X106" s="16"/>
+      <c r="Y106" s="16"/>
+      <c r="Z106" s="16"/>
+      <c r="AA106" s="16"/>
+    </row>
+    <row r="107" spans="6:27" ht="21.6" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="H107" s="8"/>
+    </row>
+    <row r="108" spans="6:27" x14ac:dyDescent="0.4">
+      <c r="H108" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="G1:G134"/>
+  <autoFilter ref="G1:G108" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="H135:H1048576 H1:H85" numberStoredAsText="1"/>
-    <ignoredError sqref="R87 R101 R103 R96 R94 R89 R108 R110 R115 R117 R122 R124" formula="1"/>
+    <ignoredError sqref="H109:H1048576 H1:H85" numberStoredAsText="1"/>
+    <ignoredError sqref="R87 R97 R92 R102" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AAE1C29-907E-475F-BB12-420AFAC48D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8EF809-5673-4EDD-9C06-7FBF7DB5A9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
